--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -10,10 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QBO P&amp;L (2026 YTD)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QBO Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Detail" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward Bookings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro Forma" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward Bookings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro Forma" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -139,11 +138,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5ECD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="004CAF50"/>
       </patternFill>
     </fill>
@@ -160,6 +154,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5ECD7"/>
       </patternFill>
     </fill>
   </fills>
@@ -198,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -228,19 +227,13 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -278,20 +271,20 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1871,418 +1864,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>DCP Wealth Fund, LLC — Yanonali</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Balance Sheet as of April 14, 2026  |  Cash Basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Source: QuickBooks Online, exported April 14, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr"/>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>ASSETS</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Current Assets — Bank Accounts</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Fixed Assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Land</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>596847</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Buildings</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>1890017</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Acquisition Fee</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>49500</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fundraising Fee</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cost Segregation</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>5920</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Furniture &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>73761</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Appliances</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Landscaping</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Photography</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rehab Costs — Hard</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>1405644</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    General Hard Costs</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n">
-        <v>201886</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Contractors/Labor</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="n">
-        <v>1026420</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Materials</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="n">
-        <v>177338</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rehab Costs — Soft</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>159844</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Architectural/Planning</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="n">
-        <v>25391</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Inspection Fees</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="n">
-        <v>4135</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Legal &amp; Professional</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="n">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Permit Fees</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="n">
-        <v>16663</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Rehab Management</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="n">
-        <v>59884</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Survey</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="n">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tenant Relocation</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="n">
-        <v>51150</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>Total Fixed Assets</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="n">
-        <v>4197591</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>TOTAL ASSETS</t>
-        </is>
-      </c>
-      <c r="B32" s="32" t="n">
-        <v>4199048</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>LIABILITIES</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>Long-term Liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CDRBC, LLC</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GFT IRA, LLC</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Total Long-term Debt</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>TOTAL LIABILITIES</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="n">
-        <v>1502064</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n">
-        <v>-343121</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Net Income (YTD 2026)</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n">
-        <v>9280</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="n">
-        <v>-333841</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="00C5A55A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2327,69 +1908,69 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>BOOKED</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="G4" s="35" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="H4" s="35" t="inlineStr">
+      <c r="H4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="I4" s="35" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="J4" s="35" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="K4" s="35" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="L4" s="35" t="inlineStr">
+      <c r="L4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="M4" s="35" t="inlineStr">
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr"/>
+      <c r="A5" s="30" t="inlineStr"/>
       <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Jan</t>
@@ -2457,48 +2038,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="32" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="38" t="n">
+      <c r="C6" s="32" t="n">
         <v>55</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="32" t="n">
         <v>67</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="32" t="n">
         <v>61</v>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="G6" s="32" t="n">
         <v>63</v>
       </c>
-      <c r="H6" s="38" t="n">
+      <c r="H6" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="32" t="n">
         <v>53</v>
       </c>
-      <c r="K6" s="38" t="n">
+      <c r="K6" s="32" t="n">
         <v>52</v>
       </c>
-      <c r="L6" s="38" t="n">
+      <c r="L6" s="32" t="n">
         <v>52</v>
       </c>
-      <c r="M6" s="38" t="n">
+      <c r="M6" s="32" t="n">
         <v>56</v>
       </c>
-      <c r="N6" s="39">
+      <c r="N6" s="33">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2509,90 +2090,90 @@
           <t>Nights Sold</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="34" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="34" t="n">
         <v>136</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="34" t="n">
         <v>164</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="34" t="n">
         <v>149</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="34" t="n">
         <v>158</v>
       </c>
-      <c r="G7" s="40" t="n">
+      <c r="G7" s="34" t="n">
         <v>164</v>
       </c>
-      <c r="H7" s="40" t="n">
+      <c r="H7" s="34" t="n">
         <v>171</v>
       </c>
-      <c r="I7" s="40" t="n">
+      <c r="I7" s="34" t="n">
         <v>169</v>
       </c>
-      <c r="J7" s="40" t="n">
+      <c r="J7" s="34" t="n">
         <v>138</v>
       </c>
-      <c r="K7" s="40" t="n">
+      <c r="K7" s="34" t="n">
         <v>135</v>
       </c>
-      <c r="L7" s="40" t="n">
+      <c r="L7" s="34" t="n">
         <v>135</v>
       </c>
-      <c r="M7" s="40" t="n">
+      <c r="M7" s="34" t="n">
         <v>147</v>
       </c>
-      <c r="N7" s="41">
+      <c r="N7" s="35">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Available Nights</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n">
+      <c r="B8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="32" t="n">
         <v>168</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="32" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="38" t="n">
+      <c r="F8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="G8" s="38" t="n">
+      <c r="G8" s="32" t="n">
         <v>180</v>
       </c>
-      <c r="H8" s="38" t="n">
+      <c r="H8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="I8" s="38" t="n">
+      <c r="I8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="32" t="n">
         <v>180</v>
       </c>
-      <c r="K8" s="38" t="n">
+      <c r="K8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="L8" s="38" t="n">
+      <c r="L8" s="32" t="n">
         <v>180</v>
       </c>
-      <c r="M8" s="38" t="n">
+      <c r="M8" s="32" t="n">
         <v>186</v>
       </c>
-      <c r="N8" s="39">
+      <c r="N8" s="33">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -2603,90 +2184,90 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="36" t="n">
         <v>0.753</v>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="36" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D9" s="42" t="n">
+      <c r="D9" s="36" t="n">
         <v>0.882</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="36" t="n">
         <v>0.828</v>
       </c>
-      <c r="F9" s="42" t="n">
+      <c r="F9" s="36" t="n">
         <v>0.851</v>
       </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="36" t="n">
         <v>0.9109999999999999</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="36" t="n">
         <v>0.92</v>
       </c>
-      <c r="I9" s="42" t="n">
+      <c r="I9" s="36" t="n">
         <v>0.9109999999999999</v>
       </c>
-      <c r="J9" s="42" t="n">
+      <c r="J9" s="36" t="n">
         <v>0.7659999999999999</v>
       </c>
-      <c r="K9" s="42" t="n">
+      <c r="K9" s="36" t="n">
         <v>0.7240000000000001</v>
       </c>
-      <c r="L9" s="42" t="n">
+      <c r="L9" s="36" t="n">
         <v>0.7490000000000001</v>
       </c>
-      <c r="M9" s="42" t="n">
+      <c r="M9" s="36" t="n">
         <v>0.792</v>
       </c>
-      <c r="N9" s="43">
+      <c r="N9" s="37">
         <f>AVERAGE(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="38" t="n">
         <v>286</v>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="38" t="n">
         <v>398</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="38" t="n">
         <v>415</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="38" t="n">
         <v>489</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="38" t="n">
         <v>446</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="38" t="n">
         <v>486</v>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="38" t="n">
         <v>506</v>
       </c>
-      <c r="I10" s="44" t="n">
+      <c r="I10" s="38" t="n">
         <v>486</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="38" t="n">
         <v>385</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="38" t="n">
         <v>365</v>
       </c>
-      <c r="L10" s="44" t="n">
+      <c r="L10" s="38" t="n">
         <v>365</v>
       </c>
-      <c r="M10" s="44" t="n">
+      <c r="M10" s="38" t="n">
         <v>385</v>
       </c>
-      <c r="N10" s="45">
+      <c r="N10" s="39">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -2697,43 +2278,43 @@
           <t>RevPAR</t>
         </is>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="40" t="n">
         <v>215</v>
       </c>
-      <c r="C11" s="46" t="n">
+      <c r="C11" s="40" t="n">
         <v>322</v>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="40" t="n">
         <v>366</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="40" t="n">
         <v>405</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>379</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="40" t="n">
         <v>443</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="40" t="n">
         <v>465</v>
       </c>
-      <c r="I11" s="46" t="n">
+      <c r="I11" s="40" t="n">
         <v>442</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="40" t="n">
         <v>295</v>
       </c>
-      <c r="K11" s="46" t="n">
+      <c r="K11" s="40" t="n">
         <v>265</v>
       </c>
-      <c r="L11" s="46" t="n">
+      <c r="L11" s="40" t="n">
         <v>274</v>
       </c>
-      <c r="M11" s="46" t="n">
+      <c r="M11" s="40" t="n">
         <v>304</v>
       </c>
-      <c r="N11" s="47">
+      <c r="N11" s="41">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -2744,43 +2325,43 @@
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B12" s="48" t="n">
+      <c r="B12" s="42" t="n">
         <v>40041</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="42" t="n">
         <v>54065</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="42" t="n">
         <v>68024</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="42" t="n">
         <v>72871</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="42" t="n">
         <v>70468</v>
       </c>
-      <c r="G12" s="48" t="n">
+      <c r="G12" s="42" t="n">
         <v>79704</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H12" s="42" t="n">
         <v>86526</v>
       </c>
-      <c r="I12" s="48" t="n">
+      <c r="I12" s="42" t="n">
         <v>82134</v>
       </c>
-      <c r="J12" s="48" t="n">
+      <c r="J12" s="42" t="n">
         <v>53130</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="42" t="n">
         <v>49275</v>
       </c>
-      <c r="L12" s="48" t="n">
+      <c r="L12" s="42" t="n">
         <v>49275</v>
       </c>
-      <c r="M12" s="48" t="n">
+      <c r="M12" s="42" t="n">
         <v>56595</v>
       </c>
-      <c r="N12" s="45">
+      <c r="N12" s="39">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -2791,43 +2372,43 @@
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="43" t="n">
         <v>35785</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="43" t="n">
         <v>48880</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="43" t="n">
         <v>61256</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="43" t="n">
         <v>63447</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="43" t="n">
         <v>62485</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="43" t="n">
         <v>70675</v>
       </c>
-      <c r="H13" s="49" t="n">
+      <c r="H13" s="43" t="n">
         <v>76724</v>
       </c>
-      <c r="I13" s="49" t="n">
+      <c r="I13" s="43" t="n">
         <v>72830</v>
       </c>
-      <c r="J13" s="49" t="n">
+      <c r="J13" s="43" t="n">
         <v>47111</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <v>43693</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="L13" s="43" t="n">
         <v>43693</v>
       </c>
-      <c r="M13" s="49" t="n">
+      <c r="M13" s="43" t="n">
         <v>50184</v>
       </c>
-      <c r="N13" s="47">
+      <c r="N13" s="41">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -2841,7 +2422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002196F3"/>
@@ -2906,72 +2487,72 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="B5" s="51" t="n">
+      <c r="B5" s="45" t="n">
         <v>72871</v>
       </c>
-      <c r="C5" s="52" t="n">
+      <c r="C5" s="46" t="n">
         <v>72871</v>
       </c>
-      <c r="D5" s="53" t="n">
+      <c r="D5" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="51" t="n">
+      <c r="E5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="54" t="inlineStr">
+      <c r="F5" s="48" t="inlineStr">
         <is>
           <t>Fully Booked</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="45" t="n">
         <v>70468</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="46" t="n">
         <v>51416</v>
       </c>
-      <c r="D6" s="53" t="n">
+      <c r="D6" s="47" t="n">
         <v>0.73</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="45" t="n">
         <v>19052</v>
       </c>
-      <c r="F6" s="54" t="inlineStr">
+      <c r="F6" s="48" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="50" t="n">
         <v>79704</v>
       </c>
-      <c r="C7" s="57" t="n">
+      <c r="C7" s="51" t="n">
         <v>35242</v>
       </c>
-      <c r="D7" s="58" t="n">
+      <c r="D7" s="52" t="n">
         <v>0.442</v>
       </c>
-      <c r="E7" s="56" t="n">
+      <c r="E7" s="50" t="n">
         <v>44462</v>
       </c>
-      <c r="F7" s="59" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
@@ -2983,16 +2564,16 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B8" s="60" t="n">
+      <c r="B8" s="54" t="n">
         <v>86526</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="41" t="n">
         <v>16926</v>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="37" t="n">
         <v>0.196</v>
       </c>
-      <c r="E8" s="60" t="n">
+      <c r="E8" s="54" t="n">
         <v>69600</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -3007,16 +2588,16 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="B9" s="60" t="n">
+      <c r="B9" s="54" t="n">
         <v>82134</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="41" t="n">
         <v>5324</v>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="37" t="n">
         <v>0.065</v>
       </c>
-      <c r="E9" s="60" t="n">
+      <c r="E9" s="54" t="n">
         <v>76810</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -3026,24 +2607,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="50" t="n">
         <v>53130</v>
       </c>
-      <c r="C10" s="57" t="n">
+      <c r="C10" s="51" t="n">
         <v>15604</v>
       </c>
-      <c r="D10" s="58" t="n">
+      <c r="D10" s="52" t="n">
         <v>0.294</v>
       </c>
-      <c r="E10" s="56" t="n">
+      <c r="E10" s="50" t="n">
         <v>37526</v>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="53" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
@@ -3055,16 +2636,16 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="B11" s="60" t="n">
+      <c r="B11" s="54" t="n">
         <v>49275</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="41" t="n">
         <v>8513</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="37" t="n">
         <v>0.173</v>
       </c>
-      <c r="E11" s="60" t="n">
+      <c r="E11" s="54" t="n">
         <v>40762</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -3079,16 +2660,16 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B12" s="60" t="n">
+      <c r="B12" s="54" t="n">
         <v>49275</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="41" t="n">
         <v>2251</v>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="37" t="n">
         <v>0.046</v>
       </c>
-      <c r="E12" s="60" t="n">
+      <c r="E12" s="54" t="n">
         <v>47024</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -3103,16 +2684,16 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="B13" s="60" t="n">
+      <c r="B13" s="54" t="n">
         <v>56595</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="41" t="n">
         <v>3729</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="37" t="n">
         <v>0.066</v>
       </c>
-      <c r="E13" s="60" t="n">
+      <c r="E13" s="54" t="n">
         <v>52866</v>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -3122,28 +2703,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="62">
+      <c r="B14" s="56">
         <f>SUM(B5:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="62">
+      <c r="C14" s="56">
         <f>SUM(C5:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="57">
         <f>C14/B14</f>
         <v/>
       </c>
-      <c r="E14" s="62">
+      <c r="E14" s="56">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="F14" s="64" t="n"/>
+      <c r="F14" s="58" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3154,7 +2735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007B1FA2"/>
@@ -3218,7 +2799,7 @@
       <c r="B6" s="7" t="n">
         <v>-82760</v>
       </c>
-      <c r="C6" s="65" t="n"/>
+      <c r="C6" s="59" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3229,7 +2810,7 @@
       <c r="B7" s="7" t="n">
         <v>-73018</v>
       </c>
-      <c r="C7" s="65" t="n"/>
+      <c r="C7" s="59" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3240,18 +2821,18 @@
       <c r="B8" s="7" t="n">
         <v>-5215</v>
       </c>
-      <c r="C8" s="65" t="n"/>
+      <c r="C8" s="59" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B9" s="67" t="n">
+      <c r="B9" s="61" t="n">
         <v>676763</v>
       </c>
-      <c r="C9" s="68" t="n">
+      <c r="C9" s="62" t="n">
         <v>0.8880145596162223</v>
       </c>
     </row>
@@ -3264,7 +2845,7 @@
       <c r="B10" s="7" t="n">
         <v>-194628</v>
       </c>
-      <c r="C10" s="65" t="n"/>
+      <c r="C10" s="59" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3275,7 +2856,7 @@
       <c r="B11" s="7" t="n">
         <v>-76211</v>
       </c>
-      <c r="C11" s="65" t="n"/>
+      <c r="C11" s="59" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3286,7 +2867,7 @@
       <c r="B12" s="7" t="n">
         <v>-26679</v>
       </c>
-      <c r="C12" s="65" t="n"/>
+      <c r="C12" s="59" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3297,7 +2878,7 @@
       <c r="B13" s="7" t="n">
         <v>-13500</v>
       </c>
-      <c r="C13" s="65" t="n"/>
+      <c r="C13" s="59" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3308,18 +2889,18 @@
       <c r="B14" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="C14" s="65" t="n"/>
+      <c r="C14" s="59" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="69" t="inlineStr">
+      <c r="A15" s="63" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B15" s="70" t="n">
+      <c r="B15" s="64" t="n">
         <v>341745</v>
       </c>
-      <c r="C15" s="71" t="n">
+      <c r="C15" s="65" t="n">
         <v>0.4484206962792675</v>
       </c>
     </row>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,6 +288,9 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2742,7 +2745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2963,32 +2966,25 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Methodology: Actual monthly ADR and occupancy are divided by their seasonal index to</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>strip out seasonality, revealing baseline performance. Forward months multiply this baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>by the appropriate seasonal index. The model improves with every data upload.</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>METHODOLOGY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="66" t="inlineStr">
+        <is>
+          <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline — meaning projections tighten over time as operating history grows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -2432,15 +2432,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2480,10 +2482,20 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>RevPAR</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2505,9 +2517,15 @@
         <v>1</v>
       </c>
       <c r="E5" s="45" t="n">
+        <v>489</v>
+      </c>
+      <c r="F5" s="45" t="n">
+        <v>405</v>
+      </c>
+      <c r="G5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="48" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
         <is>
           <t>Fully Booked</t>
         </is>
@@ -2529,9 +2547,15 @@
         <v>0.73</v>
       </c>
       <c r="E6" s="45" t="n">
+        <v>443</v>
+      </c>
+      <c r="F6" s="45" t="n">
+        <v>276</v>
+      </c>
+      <c r="G6" s="45" t="n">
         <v>19052</v>
       </c>
-      <c r="F6" s="48" t="inlineStr">
+      <c r="H6" s="48" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
@@ -2553,9 +2577,15 @@
         <v>0.442</v>
       </c>
       <c r="E7" s="50" t="n">
+        <v>526</v>
+      </c>
+      <c r="F7" s="50" t="n">
+        <v>196</v>
+      </c>
+      <c r="G7" s="50" t="n">
         <v>44462</v>
       </c>
-      <c r="F7" s="53" t="inlineStr">
+      <c r="H7" s="53" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
@@ -2577,9 +2607,15 @@
         <v>0.196</v>
       </c>
       <c r="E8" s="54" t="n">
+        <v>513</v>
+      </c>
+      <c r="F8" s="54" t="n">
+        <v>91</v>
+      </c>
+      <c r="G8" s="54" t="n">
         <v>69600</v>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>Early</t>
         </is>
@@ -2601,9 +2637,15 @@
         <v>0.065</v>
       </c>
       <c r="E9" s="54" t="n">
+        <v>410</v>
+      </c>
+      <c r="F9" s="54" t="n">
+        <v>29</v>
+      </c>
+      <c r="G9" s="54" t="n">
         <v>76810</v>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Early</t>
         </is>
@@ -2625,9 +2667,15 @@
         <v>0.294</v>
       </c>
       <c r="E10" s="50" t="n">
+        <v>488</v>
+      </c>
+      <c r="F10" s="50" t="n">
+        <v>87</v>
+      </c>
+      <c r="G10" s="50" t="n">
         <v>37526</v>
       </c>
-      <c r="F10" s="53" t="inlineStr">
+      <c r="H10" s="53" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
@@ -2649,9 +2697,15 @@
         <v>0.173</v>
       </c>
       <c r="E11" s="54" t="n">
+        <v>473</v>
+      </c>
+      <c r="F11" s="54" t="n">
+        <v>46</v>
+      </c>
+      <c r="G11" s="54" t="n">
         <v>40762</v>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Early</t>
         </is>
@@ -2673,9 +2727,15 @@
         <v>0.046</v>
       </c>
       <c r="E12" s="54" t="n">
+        <v>450</v>
+      </c>
+      <c r="F12" s="54" t="n">
+        <v>13</v>
+      </c>
+      <c r="G12" s="54" t="n">
         <v>47024</v>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Early</t>
         </is>
@@ -2697,9 +2757,15 @@
         <v>0.066</v>
       </c>
       <c r="E13" s="54" t="n">
+        <v>339</v>
+      </c>
+      <c r="F13" s="54" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="54" t="n">
         <v>52866</v>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Early</t>
         </is>
@@ -2723,16 +2789,18 @@
         <f>C14/B14</f>
         <v/>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="56">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="F14" s="58" t="n"/>
+      <c r="H14" s="58" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QBO P&amp;L (2026 YTD)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L (2026 YTD)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Detail" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward Bookings" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro Forma" sheetId="6" state="visible" r:id="rId6"/>
@@ -133,6 +133,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F5ECD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
@@ -154,11 +159,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFDE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5ECD7"/>
       </patternFill>
     </fill>
   </fills>
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -220,20 +220,25 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -266,28 +271,26 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1513,352 +1516,384 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>DCP Wealth Fund, LLC — Yanonali</t>
+          <t>Casa Yano — Profit &amp; Loss by Month (2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profit and Loss: January 1 – April 14, 2026  |  Cash Basis</t>
+          <t>Operating data: January – Apr 2026  |  QBO YTD cross-referenced</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Source: QuickBooks Online, exported April 14, 2026</t>
+          <t>Source: PMS booking data + expense reports, reconciled to QuickBooks Online</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr"/>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Amount</t>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>YTD Total</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>INCOME</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n"/>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Gross Booking Revenue</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>170225.3</v>
+        <v>40041</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>54065</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>68024</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>72871</v>
+      </c>
+      <c r="F7" s="9">
+        <f>SUM(B7:E7)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>170225.3</v>
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Net to Owner (after OTA/taxes/fees)</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>35785</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>48880</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>61256</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>63447</v>
+      </c>
+      <c r="F8" s="24">
+        <f>SUM(B8:E8)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="n"/>
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing</t>
+          <t xml:space="preserve">  Cleaning</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>2410</v>
+        <v>8483</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>7028</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>3935</v>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(B11:E11)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Commissions Expense</t>
+          <t xml:space="preserve">  Supplies</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>434.95</v>
+        <v>6140</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>912</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2213</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>371</v>
+      </c>
+      <c r="F12" s="7">
+        <f>SUM(B12:E12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Guest Relations</t>
+          <t xml:space="preserve">  Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>539.5</v>
+        <v>572</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>285</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="F13" s="7">
+        <f>SUM(B13:E13)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hospitality Management Fee</t>
+          <t xml:space="preserve">  Management Fee</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>17365.29</v>
+        <v>4229</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4522</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>5542</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>3546</v>
+      </c>
+      <c r="F14" s="7">
+        <f>SUM(B14:E14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t xml:space="preserve">  Marketing &amp; Advertising</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>450</v>
+        <v>2410</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>325</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(B15:E15)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Taxes &amp; Licenses</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1853</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>5535</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5953</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>8410</v>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(B16:E16)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cleaning Expenses</t>
+          <t xml:space="preserve">  Other</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>23141.28</v>
+        <v>252</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>908</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>285</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="F17" s="7">
+        <f>SUM(B17:E17)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fire Safety</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General Repairs</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>1887</v>
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>26905</v>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>18060</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>23590</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>16908</v>
+      </c>
+      <c r="F18" s="26">
+        <f>SUM(B18:E18)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Pest Control</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>25688.28</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n">
+        <v>8880</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>30820</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>37666</v>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>46539</v>
+      </c>
+      <c r="F20" s="28">
+        <f>SUM(B20:E20)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Supplies</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>6140.12</v>
-      </c>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>QBO RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Supplies &amp; Materials</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>3337.59</v>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>QBO YTD Rental Income (Jan 1 – Apr 14): $170,225</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total Supplies</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>9477.709999999999</v>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>QBO YTD Total Expenses: $89,338  |  QBO YTD NOI: $80,887</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>Taxes Paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  City &amp; County Tax</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>15798.09</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Property Taxes</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>13339.62</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  State Tax</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>1612.76</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total Taxes Paid</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>30750.47</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Disposal &amp; Waste</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Electricity</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>564.3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Internet &amp; TV</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>1163.25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Water &amp; Sewer</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>444.24</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total Utilities</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>2221.79</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="n">
-        <v>89337.99000000001</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="n">
-        <v>80887.31</v>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Note: Minor variances between PMS and QBO are expected due to cash vs accrual timing and partial-month cutoffs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1906,74 +1941,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>BOOKED</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="J4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="L4" s="29" t="inlineStr">
+      <c r="L4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr"/>
+      <c r="A5" s="33" t="inlineStr"/>
       <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Jan</t>
@@ -2041,48 +2076,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="35" t="n">
         <v>67</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="35" t="n">
         <v>61</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="35" t="n">
         <v>63</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H6" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="J6" s="32" t="n">
+      <c r="J6" s="35" t="n">
         <v>53</v>
       </c>
-      <c r="K6" s="32" t="n">
+      <c r="K6" s="35" t="n">
         <v>52</v>
       </c>
-      <c r="L6" s="32" t="n">
+      <c r="L6" s="35" t="n">
         <v>52</v>
       </c>
-      <c r="M6" s="32" t="n">
+      <c r="M6" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="36">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2093,90 +2128,90 @@
           <t>Nights Sold</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="37" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="37" t="n">
         <v>136</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="37" t="n">
         <v>164</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="37" t="n">
         <v>149</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="37" t="n">
         <v>158</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="37" t="n">
         <v>164</v>
       </c>
-      <c r="H7" s="34" t="n">
+      <c r="H7" s="37" t="n">
         <v>171</v>
       </c>
-      <c r="I7" s="34" t="n">
+      <c r="I7" s="37" t="n">
         <v>169</v>
       </c>
-      <c r="J7" s="34" t="n">
+      <c r="J7" s="37" t="n">
         <v>138</v>
       </c>
-      <c r="K7" s="34" t="n">
+      <c r="K7" s="37" t="n">
         <v>135</v>
       </c>
-      <c r="L7" s="34" t="n">
+      <c r="L7" s="37" t="n">
         <v>135</v>
       </c>
-      <c r="M7" s="34" t="n">
+      <c r="M7" s="37" t="n">
         <v>147</v>
       </c>
-      <c r="N7" s="35">
+      <c r="N7" s="38">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Available Nights</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="35" t="n">
         <v>168</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="J8" s="32" t="n">
+      <c r="J8" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="K8" s="32" t="n">
+      <c r="K8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="L8" s="32" t="n">
+      <c r="L8" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="M8" s="32" t="n">
+      <c r="M8" s="35" t="n">
         <v>186</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="36">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -2187,90 +2222,90 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="39" t="n">
         <v>0.753</v>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="39" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="39" t="n">
         <v>0.882</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="39" t="n">
         <v>0.828</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="39" t="n">
         <v>0.851</v>
       </c>
-      <c r="G9" s="36" t="n">
+      <c r="G9" s="39" t="n">
         <v>0.9109999999999999</v>
       </c>
-      <c r="H9" s="36" t="n">
+      <c r="H9" s="39" t="n">
         <v>0.92</v>
       </c>
-      <c r="I9" s="36" t="n">
+      <c r="I9" s="39" t="n">
         <v>0.9109999999999999</v>
       </c>
-      <c r="J9" s="36" t="n">
+      <c r="J9" s="39" t="n">
         <v>0.7659999999999999</v>
       </c>
-      <c r="K9" s="36" t="n">
+      <c r="K9" s="39" t="n">
         <v>0.7240000000000001</v>
       </c>
-      <c r="L9" s="36" t="n">
+      <c r="L9" s="39" t="n">
         <v>0.7490000000000001</v>
       </c>
-      <c r="M9" s="36" t="n">
+      <c r="M9" s="39" t="n">
         <v>0.792</v>
       </c>
-      <c r="N9" s="37">
+      <c r="N9" s="40">
         <f>AVERAGE(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n">
+      <c r="B10" s="41" t="n">
         <v>286</v>
       </c>
-      <c r="C10" s="38" t="n">
+      <c r="C10" s="41" t="n">
         <v>398</v>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="41" t="n">
         <v>415</v>
       </c>
-      <c r="E10" s="38" t="n">
+      <c r="E10" s="41" t="n">
         <v>489</v>
       </c>
-      <c r="F10" s="38" t="n">
+      <c r="F10" s="41" t="n">
         <v>446</v>
       </c>
-      <c r="G10" s="38" t="n">
+      <c r="G10" s="41" t="n">
         <v>486</v>
       </c>
-      <c r="H10" s="38" t="n">
+      <c r="H10" s="41" t="n">
         <v>506</v>
       </c>
-      <c r="I10" s="38" t="n">
+      <c r="I10" s="41" t="n">
         <v>486</v>
       </c>
-      <c r="J10" s="38" t="n">
+      <c r="J10" s="41" t="n">
         <v>385</v>
       </c>
-      <c r="K10" s="38" t="n">
+      <c r="K10" s="41" t="n">
         <v>365</v>
       </c>
-      <c r="L10" s="38" t="n">
+      <c r="L10" s="41" t="n">
         <v>365</v>
       </c>
-      <c r="M10" s="38" t="n">
+      <c r="M10" s="41" t="n">
         <v>385</v>
       </c>
-      <c r="N10" s="39">
+      <c r="N10" s="42">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -2281,137 +2316,137 @@
           <t>RevPAR</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="43" t="n">
         <v>215</v>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="C11" s="43" t="n">
         <v>322</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>366</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="43" t="n">
         <v>405</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="43" t="n">
         <v>379</v>
       </c>
-      <c r="G11" s="40" t="n">
+      <c r="G11" s="43" t="n">
         <v>443</v>
       </c>
-      <c r="H11" s="40" t="n">
+      <c r="H11" s="43" t="n">
         <v>465</v>
       </c>
-      <c r="I11" s="40" t="n">
+      <c r="I11" s="43" t="n">
         <v>442</v>
       </c>
-      <c r="J11" s="40" t="n">
+      <c r="J11" s="43" t="n">
         <v>295</v>
       </c>
-      <c r="K11" s="40" t="n">
+      <c r="K11" s="43" t="n">
         <v>265</v>
       </c>
-      <c r="L11" s="40" t="n">
+      <c r="L11" s="43" t="n">
         <v>274</v>
       </c>
-      <c r="M11" s="40" t="n">
+      <c r="M11" s="43" t="n">
         <v>304</v>
       </c>
-      <c r="N11" s="41">
+      <c r="N11" s="44">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B12" s="42" t="n">
+      <c r="B12" s="45" t="n">
         <v>40041</v>
       </c>
-      <c r="C12" s="42" t="n">
+      <c r="C12" s="45" t="n">
         <v>54065</v>
       </c>
-      <c r="D12" s="42" t="n">
+      <c r="D12" s="45" t="n">
         <v>68024</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E12" s="45" t="n">
         <v>72871</v>
       </c>
-      <c r="F12" s="42" t="n">
+      <c r="F12" s="45" t="n">
         <v>70468</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="45" t="n">
         <v>79704</v>
       </c>
-      <c r="H12" s="42" t="n">
+      <c r="H12" s="45" t="n">
         <v>86526</v>
       </c>
-      <c r="I12" s="42" t="n">
+      <c r="I12" s="45" t="n">
         <v>82134</v>
       </c>
-      <c r="J12" s="42" t="n">
+      <c r="J12" s="45" t="n">
         <v>53130</v>
       </c>
-      <c r="K12" s="42" t="n">
+      <c r="K12" s="45" t="n">
         <v>49275</v>
       </c>
-      <c r="L12" s="42" t="n">
+      <c r="L12" s="45" t="n">
         <v>49275</v>
       </c>
-      <c r="M12" s="42" t="n">
+      <c r="M12" s="45" t="n">
         <v>56595</v>
       </c>
-      <c r="N12" s="39">
+      <c r="N12" s="42">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="46" t="n">
         <v>35785</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="46" t="n">
         <v>48880</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="46" t="n">
         <v>61256</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E13" s="46" t="n">
         <v>63447</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="46" t="n">
         <v>62485</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="46" t="n">
         <v>70675</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="46" t="n">
         <v>76724</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="46" t="n">
         <v>72830</v>
       </c>
-      <c r="J13" s="43" t="n">
+      <c r="J13" s="46" t="n">
         <v>47111</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="46" t="n">
         <v>43693</v>
       </c>
-      <c r="L13" s="43" t="n">
+      <c r="L13" s="46" t="n">
         <v>43693</v>
       </c>
-      <c r="M13" s="43" t="n">
+      <c r="M13" s="46" t="n">
         <v>50184</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="44">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -2502,117 +2537,117 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="48" t="n">
         <v>72871</v>
       </c>
-      <c r="C5" s="46" t="n">
+      <c r="C5" s="49" t="n">
         <v>72871</v>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="45" t="n">
+      <c r="E5" s="48" t="n">
         <v>489</v>
       </c>
-      <c r="F5" s="45" t="n">
+      <c r="F5" s="48" t="n">
         <v>405</v>
       </c>
-      <c r="G5" s="45" t="n">
+      <c r="G5" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Fully Booked</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="48" t="n">
         <v>70468</v>
       </c>
-      <c r="C6" s="46" t="n">
+      <c r="C6" s="49" t="n">
         <v>51416</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="50" t="n">
         <v>0.73</v>
       </c>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="48" t="n">
         <v>443</v>
       </c>
-      <c r="F6" s="45" t="n">
+      <c r="F6" s="48" t="n">
         <v>276</v>
       </c>
-      <c r="G6" s="45" t="n">
+      <c r="G6" s="48" t="n">
         <v>19052</v>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="51" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="53" t="n">
         <v>79704</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="54" t="n">
         <v>35242</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="55" t="n">
         <v>0.442</v>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="53" t="n">
         <v>526</v>
       </c>
-      <c r="F7" s="50" t="n">
+      <c r="F7" s="53" t="n">
         <v>196</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="53" t="n">
         <v>44462</v>
       </c>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B8" s="54" t="n">
+      <c r="B8" s="57" t="n">
         <v>86526</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="44" t="n">
         <v>16926</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="40" t="n">
         <v>0.196</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="57" t="n">
         <v>513</v>
       </c>
-      <c r="F8" s="54" t="n">
+      <c r="F8" s="57" t="n">
         <v>91</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="57" t="n">
         <v>69600</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -2622,27 +2657,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="B9" s="54" t="n">
+      <c r="B9" s="57" t="n">
         <v>82134</v>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="44" t="n">
         <v>5324</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="40" t="n">
         <v>0.065</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="57" t="n">
         <v>410</v>
       </c>
-      <c r="F9" s="54" t="n">
+      <c r="F9" s="57" t="n">
         <v>29</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="57" t="n">
         <v>76810</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -2652,57 +2687,57 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B10" s="50" t="n">
+      <c r="B10" s="53" t="n">
         <v>53130</v>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C10" s="54" t="n">
         <v>15604</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="55" t="n">
         <v>0.294</v>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="53" t="n">
         <v>488</v>
       </c>
-      <c r="F10" s="50" t="n">
+      <c r="F10" s="53" t="n">
         <v>87</v>
       </c>
-      <c r="G10" s="50" t="n">
+      <c r="G10" s="53" t="n">
         <v>37526</v>
       </c>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="H10" s="56" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B11" s="54" t="n">
+      <c r="B11" s="57" t="n">
         <v>49275</v>
       </c>
-      <c r="C11" s="41" t="n">
+      <c r="C11" s="44" t="n">
         <v>8513</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="40" t="n">
         <v>0.173</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="57" t="n">
         <v>473</v>
       </c>
-      <c r="F11" s="54" t="n">
+      <c r="F11" s="57" t="n">
         <v>46</v>
       </c>
-      <c r="G11" s="54" t="n">
+      <c r="G11" s="57" t="n">
         <v>40762</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -2712,27 +2747,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="B12" s="54" t="n">
+      <c r="B12" s="57" t="n">
         <v>49275</v>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="44" t="n">
         <v>2251</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="40" t="n">
         <v>0.046</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="57" t="n">
         <v>450</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="57" t="n">
         <v>13</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="57" t="n">
         <v>47024</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -2742,27 +2777,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B13" s="54" t="n">
+      <c r="B13" s="57" t="n">
         <v>56595</v>
       </c>
-      <c r="C13" s="41" t="n">
+      <c r="C13" s="44" t="n">
         <v>3729</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="40" t="n">
         <v>0.066</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="57" t="n">
         <v>339</v>
       </c>
-      <c r="F13" s="54" t="n">
+      <c r="F13" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="54" t="n">
+      <c r="G13" s="57" t="n">
         <v>52866</v>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -2772,30 +2807,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="56">
+      <c r="B14" s="59">
         <f>SUM(B5:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="56">
+      <c r="C14" s="59">
         <f>SUM(C5:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="60">
         <f>C14/B14</f>
         <v/>
       </c>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="58" t="n"/>
-      <c r="G14" s="56">
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="61" t="n"/>
+      <c r="G14" s="59">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="H14" s="58" t="n"/>
+      <c r="H14" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2870,7 +2905,7 @@
       <c r="B6" s="7" t="n">
         <v>-82760</v>
       </c>
-      <c r="C6" s="59" t="n"/>
+      <c r="C6" s="62" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2881,7 +2916,7 @@
       <c r="B7" s="7" t="n">
         <v>-73018</v>
       </c>
-      <c r="C7" s="59" t="n"/>
+      <c r="C7" s="62" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2892,18 +2927,18 @@
       <c r="B8" s="7" t="n">
         <v>-5215</v>
       </c>
-      <c r="C8" s="59" t="n"/>
+      <c r="C8" s="62" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B9" s="61" t="n">
+      <c r="B9" s="24" t="n">
         <v>676763</v>
       </c>
-      <c r="C9" s="62" t="n">
+      <c r="C9" s="63" t="n">
         <v>0.8880145596162223</v>
       </c>
     </row>
@@ -2916,7 +2951,7 @@
       <c r="B10" s="7" t="n">
         <v>-194628</v>
       </c>
-      <c r="C10" s="59" t="n"/>
+      <c r="C10" s="62" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2927,7 +2962,7 @@
       <c r="B11" s="7" t="n">
         <v>-76211</v>
       </c>
-      <c r="C11" s="59" t="n"/>
+      <c r="C11" s="62" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2938,7 +2973,7 @@
       <c r="B12" s="7" t="n">
         <v>-26679</v>
       </c>
-      <c r="C12" s="59" t="n"/>
+      <c r="C12" s="62" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2949,7 +2984,7 @@
       <c r="B13" s="7" t="n">
         <v>-13500</v>
       </c>
-      <c r="C13" s="59" t="n"/>
+      <c r="C13" s="62" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2960,18 +2995,18 @@
       <c r="B14" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="C14" s="59" t="n"/>
+      <c r="C14" s="62" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="63" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B15" s="64" t="n">
+      <c r="B15" s="65" t="n">
         <v>341745</v>
       </c>
-      <c r="C15" s="65" t="n">
+      <c r="C15" s="66" t="n">
         <v>0.4484206962792675</v>
       </c>
     </row>
@@ -3043,7 +3078,7 @@
       <c r="C24" s="5" t="n"/>
     </row>
     <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="66" t="inlineStr">
+      <c r="A25" s="67" t="inlineStr">
         <is>
           <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline — meaning projections tighten over time as operating history grows.</t>
         </is>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-04-14</t>
+          <t>Prepared 2026-04-21</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>762108</v>
+        <v>761592</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>676763</v>
+        <v>675759</v>
       </c>
     </row>
     <row r="17">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>335018</v>
+        <v>337331</v>
       </c>
     </row>
     <row r="18">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>341745</v>
+        <v>338428</v>
       </c>
     </row>
     <row r="19">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.825</v>
+        <v>0.8240000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -926,14 +926,14 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  April booked at $72,871 gross — highest month to date</t>
+          <t>•  April booked at $72,355 gross — highest month to date</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.7% — efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.5% — efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>341745</v>
+        <v>338428</v>
       </c>
     </row>
     <row r="42">
@@ -1604,7 +1604,7 @@
         <v>68024</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>72871</v>
+        <v>72355</v>
       </c>
       <c r="F7" s="9">
         <f>SUM(B7:E7)</f>
@@ -1627,7 +1627,7 @@
         <v>61256</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>63447</v>
+        <v>63117</v>
       </c>
       <c r="F8" s="24">
         <f>SUM(B8:E8)</f>
@@ -1662,7 +1662,7 @@
         <v>7028</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3935</v>
+        <v>5855</v>
       </c>
       <c r="F11" s="7">
         <f>SUM(B11:E11)</f>
@@ -1685,7 +1685,7 @@
         <v>2213</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>371</v>
+        <v>561</v>
       </c>
       <c r="F12" s="7">
         <f>SUM(B12:E12)</f>
@@ -1731,7 +1731,7 @@
         <v>5542</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3546</v>
+        <v>5081</v>
       </c>
       <c r="F14" s="7">
         <f>SUM(B14:E14)</f>
@@ -1754,7 +1754,7 @@
         <v>325</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F15" s="7">
         <f>SUM(B15:E15)</f>
@@ -1823,7 +1823,7 @@
         <v>23590</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>16908</v>
+        <v>20697</v>
       </c>
       <c r="F18" s="26">
         <f>SUM(B18:E18)</f>
@@ -1846,7 +1846,7 @@
         <v>37666</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>46539</v>
+        <v>42420</v>
       </c>
       <c r="F20" s="28">
         <f>SUM(B20:E20)</f>
@@ -2091,7 +2091,7 @@
         <v>60</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" s="35" t="n">
         <v>61</v>
@@ -2100,7 +2100,7 @@
         <v>63</v>
       </c>
       <c r="H6" s="35" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="35" t="n">
         <v>65</v>
@@ -2138,7 +2138,7 @@
         <v>164</v>
       </c>
       <c r="E7" s="37" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F7" s="37" t="n">
         <v>158</v>
@@ -2232,7 +2232,7 @@
         <v>0.882</v>
       </c>
       <c r="E9" s="39" t="n">
-        <v>0.828</v>
+        <v>0.8170000000000001</v>
       </c>
       <c r="F9" s="39" t="n">
         <v>0.851</v>
@@ -2279,7 +2279,7 @@
         <v>415</v>
       </c>
       <c r="E10" s="41" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F10" s="41" t="n">
         <v>446</v>
@@ -2326,7 +2326,7 @@
         <v>366</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F11" s="43" t="n">
         <v>379</v>
@@ -2373,7 +2373,7 @@
         <v>68024</v>
       </c>
       <c r="E12" s="45" t="n">
-        <v>72871</v>
+        <v>72355</v>
       </c>
       <c r="F12" s="45" t="n">
         <v>70468</v>
@@ -2420,31 +2420,31 @@
         <v>61256</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>63447</v>
+        <v>63117</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>62485</v>
+        <v>62395</v>
       </c>
       <c r="G13" s="46" t="n">
-        <v>70675</v>
+        <v>70573</v>
       </c>
       <c r="H13" s="46" t="n">
-        <v>76724</v>
+        <v>76614</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>72830</v>
+        <v>72725</v>
       </c>
       <c r="J13" s="46" t="n">
-        <v>47111</v>
+        <v>47043</v>
       </c>
       <c r="K13" s="46" t="n">
-        <v>43693</v>
+        <v>43630</v>
       </c>
       <c r="L13" s="46" t="n">
-        <v>43693</v>
+        <v>43630</v>
       </c>
       <c r="M13" s="46" t="n">
-        <v>50184</v>
+        <v>50111</v>
       </c>
       <c r="N13" s="44">
         <f>SUM(B13:M13)</f>
@@ -2490,7 +2490,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-04-14. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-04-21. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2543,19 +2543,19 @@
         </is>
       </c>
       <c r="B5" s="48" t="n">
-        <v>72871</v>
+        <v>72355</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>72871</v>
+        <v>72355</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="48" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F5" s="48" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G5" s="48" t="n">
         <v>0</v>
@@ -2576,19 +2576,19 @@
         <v>70468</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>51416</v>
+        <v>55343</v>
       </c>
       <c r="D6" s="50" t="n">
-        <v>0.73</v>
+        <v>0.785</v>
       </c>
       <c r="E6" s="48" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F6" s="48" t="n">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>19052</v>
+        <v>15125</v>
       </c>
       <c r="H6" s="51" t="inlineStr">
         <is>
@@ -2606,19 +2606,19 @@
         <v>79704</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>35242</v>
+        <v>40169</v>
       </c>
       <c r="D7" s="55" t="n">
-        <v>0.442</v>
+        <v>0.504</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>44462</v>
+        <v>39535</v>
       </c>
       <c r="H7" s="56" t="inlineStr">
         <is>
@@ -2627,32 +2627,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B8" s="57" t="n">
+      <c r="B8" s="53" t="n">
         <v>86526</v>
       </c>
-      <c r="C8" s="44" t="n">
-        <v>16926</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="E8" s="57" t="n">
-        <v>513</v>
-      </c>
-      <c r="F8" s="57" t="n">
-        <v>91</v>
-      </c>
-      <c r="G8" s="57" t="n">
-        <v>69600</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
+      <c r="C8" s="54" t="n">
+        <v>22618</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E8" s="53" t="n">
+        <v>539</v>
+      </c>
+      <c r="F8" s="53" t="n">
+        <v>122</v>
+      </c>
+      <c r="G8" s="53" t="n">
+        <v>63908</v>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>Building</t>
         </is>
       </c>
     </row>
@@ -2666,19 +2666,19 @@
         <v>82134</v>
       </c>
       <c r="C9" s="44" t="n">
-        <v>5324</v>
+        <v>6092</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0.065</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="E9" s="57" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="F9" s="57" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G9" s="57" t="n">
-        <v>76810</v>
+        <v>76042</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>762108</v>
+        <v>761592</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-82760</v>
+        <v>-83523</v>
       </c>
       <c r="C6" s="62" t="n"/>
     </row>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-73018</v>
+        <v>-73238</v>
       </c>
       <c r="C7" s="62" t="n"/>
     </row>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>-5215</v>
+        <v>-5436</v>
       </c>
       <c r="C8" s="62" t="n"/>
     </row>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>676763</v>
+        <v>675759</v>
       </c>
       <c r="C9" s="63" t="n">
-        <v>0.8880145596162223</v>
+        <v>0.8872979232975137</v>
       </c>
     </row>
     <row r="10">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>-194628</v>
+        <v>-196993</v>
       </c>
       <c r="C10" s="62" t="n"/>
     </row>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-76211</v>
+        <v>-76159</v>
       </c>
       <c r="C11" s="62" t="n"/>
     </row>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="B15" s="65" t="n">
-        <v>341745</v>
+        <v>338428</v>
       </c>
       <c r="C15" s="66" t="n">
-        <v>0.4484206962792675</v>
+        <v>0.4443691635416339</v>
       </c>
     </row>
     <row r="17">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -673,7 +673,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Casa Yano — Lender Package</t>
+          <t>Casa Yano - Lender Package</t>
         </is>
       </c>
     </row>
@@ -912,28 +912,28 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>•  Existing debt: $1,500,000 — seeking refinance</t>
+          <t>•  Existing debt: $1,500,000 - seeking refinance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>•  Occupancy trending from 75% (Jan) to 88% (Mar) — strong ramp trajectory</t>
+          <t>•  Occupancy trending from 75% (Jan) to 88% (Mar) - strong ramp trajectory</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  April booked at $72,355 gross — highest month to date</t>
+          <t>•  April booked at $72,355 gross - highest month to date</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.5% — efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.5% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Casa Yano — Project History &amp; Renovation</t>
+          <t>Casa Yano - Project History &amp; Renovation</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Rehab Costs — Hard</t>
+          <t>Rehab Costs - Hard</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
@@ -1243,7 +1243,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Rehab Costs — Soft</t>
+          <t>Rehab Costs - Soft</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Construction begins — full gut renovation</t>
+          <t>Construction begins - full gut renovation</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Construction complete — certificate of occupancy</t>
+          <t>Construction complete - certificate of occupancy</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>First guest booking — STR operations commence</t>
+          <t>First guest booking - STR operations commence</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>First full quarter of operations — strong ramp</t>
+          <t>First full quarter of operations - strong ramp</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Casa Yano — Profit &amp; Loss by Month (2026)</t>
+          <t>Casa Yano - Profit &amp; Loss by Month (2026)</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Casa Yano — Monthly Operating Detail (2026)</t>
+          <t>Casa Yano - Monthly Operating Detail (2026)</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Casa Yano — Forward Bookings on the Books</t>
+          <t>Casa Yano - Forward Bookings on the Books</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Casa Yano — 2026 Pro Forma (Blended Forecast)</t>
+          <t>Casa Yano - 2026 Pro Forma (Blended Forecast)</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="67" t="inlineStr">
         <is>
-          <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline — meaning projections tighten over time as operating history grows.</t>
+          <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline - meaning projections tighten over time as operating history grows.</t>
         </is>
       </c>
     </row>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-04-21</t>
+          <t>Prepared 2026-04-27</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>761592</v>
+        <v>762301</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>675759</v>
+        <v>677170</v>
       </c>
     </row>
     <row r="17">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>337331</v>
+        <v>337514</v>
       </c>
     </row>
     <row r="18">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>338428</v>
+        <v>339656</v>
       </c>
     </row>
     <row r="19">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="22">
@@ -926,14 +926,14 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  April booked at $72,355 gross - highest month to date</t>
+          <t>•  April booked at $73,064 gross - highest month to date</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.5% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.6% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>338428</v>
+        <v>339656</v>
       </c>
     </row>
     <row r="42">
@@ -1604,7 +1604,7 @@
         <v>68024</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>72355</v>
+        <v>73064</v>
       </c>
       <c r="F7" s="9">
         <f>SUM(B7:E7)</f>
@@ -1627,7 +1627,7 @@
         <v>61256</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>63117</v>
+        <v>64216</v>
       </c>
       <c r="F8" s="24">
         <f>SUM(B8:E8)</f>
@@ -1846,7 +1846,7 @@
         <v>37666</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>42420</v>
+        <v>43519</v>
       </c>
       <c r="F20" s="28">
         <f>SUM(B20:E20)</f>
@@ -2091,7 +2091,7 @@
         <v>60</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="35" t="n">
         <v>61</v>
@@ -2115,7 +2115,7 @@
         <v>52</v>
       </c>
       <c r="M6" s="35" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N6" s="36">
         <f>SUM(B6:M6)</f>
@@ -2138,7 +2138,7 @@
         <v>164</v>
       </c>
       <c r="E7" s="37" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F7" s="37" t="n">
         <v>158</v>
@@ -2232,7 +2232,7 @@
         <v>0.882</v>
       </c>
       <c r="E9" s="39" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="F9" s="39" t="n">
         <v>0.851</v>
@@ -2279,7 +2279,7 @@
         <v>415</v>
       </c>
       <c r="E10" s="41" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F10" s="41" t="n">
         <v>446</v>
@@ -2326,7 +2326,7 @@
         <v>366</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F11" s="43" t="n">
         <v>379</v>
@@ -2373,7 +2373,7 @@
         <v>68024</v>
       </c>
       <c r="E12" s="45" t="n">
-        <v>72355</v>
+        <v>73064</v>
       </c>
       <c r="F12" s="45" t="n">
         <v>70468</v>
@@ -2420,31 +2420,31 @@
         <v>61256</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>63117</v>
+        <v>64216</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>62395</v>
+        <v>62437</v>
       </c>
       <c r="G13" s="46" t="n">
-        <v>70573</v>
+        <v>70620</v>
       </c>
       <c r="H13" s="46" t="n">
-        <v>76614</v>
+        <v>76665</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>72725</v>
+        <v>72773</v>
       </c>
       <c r="J13" s="46" t="n">
-        <v>47043</v>
+        <v>47075</v>
       </c>
       <c r="K13" s="46" t="n">
-        <v>43630</v>
+        <v>43659</v>
       </c>
       <c r="L13" s="46" t="n">
-        <v>43630</v>
+        <v>43659</v>
       </c>
       <c r="M13" s="46" t="n">
-        <v>50111</v>
+        <v>50145</v>
       </c>
       <c r="N13" s="44">
         <f>SUM(B13:M13)</f>
@@ -2490,7 +2490,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-04-21. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-04-27. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2543,19 +2543,19 @@
         </is>
       </c>
       <c r="B5" s="48" t="n">
-        <v>72355</v>
+        <v>73064</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>72355</v>
+        <v>73064</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="48" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F5" s="48" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G5" s="48" t="n">
         <v>0</v>
@@ -2576,19 +2576,19 @@
         <v>70468</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>55343</v>
+        <v>60449</v>
       </c>
       <c r="D6" s="50" t="n">
-        <v>0.785</v>
+        <v>0.858</v>
       </c>
       <c r="E6" s="48" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F6" s="48" t="n">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>15125</v>
+        <v>10019</v>
       </c>
       <c r="H6" s="51" t="inlineStr">
         <is>
@@ -2606,19 +2606,19 @@
         <v>79704</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>40169</v>
+        <v>38444</v>
       </c>
       <c r="D7" s="55" t="n">
-        <v>0.504</v>
+        <v>0.482</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>39535</v>
+        <v>41260</v>
       </c>
       <c r="H7" s="56" t="inlineStr">
         <is>
@@ -2636,19 +2636,19 @@
         <v>86526</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>22618</v>
+        <v>22537</v>
       </c>
       <c r="D8" s="55" t="n">
-        <v>0.261</v>
+        <v>0.26</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>63908</v>
+        <v>63989</v>
       </c>
       <c r="H8" s="56" t="inlineStr">
         <is>
@@ -2666,19 +2666,19 @@
         <v>82134</v>
       </c>
       <c r="C9" s="44" t="n">
-        <v>6092</v>
+        <v>10977</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="E9" s="57" t="n">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="F9" s="57" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="G9" s="57" t="n">
-        <v>76042</v>
+        <v>71157</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>761592</v>
+        <v>762301</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-83523</v>
+        <v>-83964</v>
       </c>
       <c r="C6" s="62" t="n"/>
     </row>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-73238</v>
+        <v>-73521</v>
       </c>
       <c r="C7" s="62" t="n"/>
     </row>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>-5436</v>
+        <v>-5307</v>
       </c>
       <c r="C8" s="62" t="n"/>
     </row>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>675759</v>
+        <v>677170</v>
       </c>
       <c r="C9" s="63" t="n">
-        <v>0.8872979232975137</v>
+        <v>0.8883236411863555</v>
       </c>
     </row>
     <row r="10">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>-196993</v>
+        <v>-197105</v>
       </c>
       <c r="C10" s="62" t="n"/>
     </row>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-76159</v>
+        <v>-76230</v>
       </c>
       <c r="C11" s="62" t="n"/>
     </row>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="B15" s="65" t="n">
-        <v>338428</v>
+        <v>339656</v>
       </c>
       <c r="C15" s="66" t="n">
-        <v>0.4443691635416339</v>
+        <v>0.4455667774278139</v>
       </c>
     </row>
     <row r="17">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-04-27</t>
+          <t>Prepared 2026-05-01</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>3 months actuals + seasonal model</t>
+          <t>4 months actuals + seasonal model</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>762301</v>
+        <v>768573</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>677170</v>
+        <v>681979</v>
       </c>
     </row>
     <row r="17">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>337514</v>
+        <v>324510</v>
       </c>
     </row>
     <row r="18">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>339656</v>
+        <v>357469</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.825</v>
+        <v>0.8140000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -926,7 +926,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  April booked at $73,064 gross - highest month to date</t>
+          <t>•  April booked at $73,746 gross - highest month to date</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>339656</v>
+        <v>357469</v>
       </c>
     </row>
     <row r="42">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1525,6 +1525,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1537,7 +1538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating data: January – Apr 2026  |  QBO YTD cross-referenced</t>
+          <t>Operating data: January – May 2026  |  QBO YTD cross-referenced</t>
         </is>
       </c>
     </row>
@@ -1571,6 +1572,11 @@
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -1587,6 +1593,7 @@
       <c r="D6" s="22" t="n"/>
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1604,10 +1611,13 @@
         <v>68024</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>73064</v>
-      </c>
-      <c r="F7" s="9">
-        <f>SUM(B7:E7)</f>
+        <v>73746</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>57908</v>
+      </c>
+      <c r="G7" s="9">
+        <f>SUM(B7:F7)</f>
         <v/>
       </c>
     </row>
@@ -1627,10 +1637,13 @@
         <v>61256</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>64216</v>
-      </c>
-      <c r="F8" s="24">
-        <f>SUM(B8:E8)</f>
+        <v>64772</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>50641</v>
+      </c>
+      <c r="G8" s="24">
+        <f>SUM(B8:F8)</f>
         <v/>
       </c>
     </row>
@@ -1645,6 +1658,7 @@
       <c r="D10" s="22" t="n"/>
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1662,10 +1676,13 @@
         <v>7028</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>5855</v>
-      </c>
-      <c r="F11" s="7">
-        <f>SUM(B11:E11)</f>
+        <v>7020</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(B11:F11)</f>
         <v/>
       </c>
     </row>
@@ -1685,10 +1702,13 @@
         <v>2213</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>561</v>
-      </c>
-      <c r="F12" s="7">
-        <f>SUM(B12:E12)</f>
+        <v>607</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <f>SUM(B12:F12)</f>
         <v/>
       </c>
     </row>
@@ -1710,8 +1730,11 @@
       <c r="E13" s="7" t="n">
         <v>450</v>
       </c>
-      <c r="F13" s="7">
-        <f>SUM(B13:E13)</f>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <f>SUM(B13:F13)</f>
         <v/>
       </c>
     </row>
@@ -1731,10 +1754,13 @@
         <v>5542</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>5081</v>
-      </c>
-      <c r="F14" s="7">
-        <f>SUM(B14:E14)</f>
+        <v>7662</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="G14" s="7">
+        <f>SUM(B14:F14)</f>
         <v/>
       </c>
     </row>
@@ -1756,8 +1782,11 @@
       <c r="E15" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="7">
-        <f>SUM(B15:E15)</f>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(B15:F15)</f>
         <v/>
       </c>
     </row>
@@ -1779,8 +1808,11 @@
       <c r="E16" s="7" t="n">
         <v>8410</v>
       </c>
-      <c r="F16" s="7">
-        <f>SUM(B16:E16)</f>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(B16:F16)</f>
         <v/>
       </c>
     </row>
@@ -1800,10 +1832,13 @@
         <v>285</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>195</v>
-      </c>
-      <c r="F17" s="7">
-        <f>SUM(B17:E17)</f>
+        <v>617</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <f>SUM(B17:F17)</f>
         <v/>
       </c>
     </row>
@@ -1823,10 +1858,13 @@
         <v>23590</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>20697</v>
-      </c>
-      <c r="F18" s="26">
-        <f>SUM(B18:E18)</f>
+        <v>24911</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="G18" s="26">
+        <f>SUM(B18:F18)</f>
         <v/>
       </c>
     </row>
@@ -1846,10 +1884,13 @@
         <v>37666</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>43519</v>
-      </c>
-      <c r="F20" s="28">
-        <f>SUM(B20:E20)</f>
+        <v>39861</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>50583</v>
+      </c>
+      <c r="G20" s="28">
+        <f>SUM(B20:F20)</f>
         <v/>
       </c>
     </row>
@@ -1864,6 +1905,7 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1888,12 +1930,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1961,14 +2003,14 @@
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>ACTUAL</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>BOOKED</t>
-        </is>
-      </c>
-      <c r="F4" s="32" t="inlineStr">
-        <is>
-          <t>PROJECTED</t>
         </is>
       </c>
       <c r="G4" s="32" t="inlineStr">
@@ -2094,16 +2136,16 @@
         <v>69</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G6" s="35" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6" s="35" t="n">
         <v>66</v>
       </c>
       <c r="I6" s="35" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J6" s="35" t="n">
         <v>53</v>
@@ -2138,19 +2180,19 @@
         <v>164</v>
       </c>
       <c r="E7" s="37" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F7" s="37" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37" t="n">
         <v>171</v>
       </c>
       <c r="I7" s="37" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J7" s="37" t="n">
         <v>138</v>
@@ -2162,7 +2204,7 @@
         <v>135</v>
       </c>
       <c r="M7" s="37" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N7" s="38">
         <f>SUM(B7:M7)</f>
@@ -2232,31 +2274,31 @@
         <v>0.882</v>
       </c>
       <c r="E9" s="39" t="n">
-        <v>0.828</v>
+        <v>0.8390000000000001</v>
       </c>
       <c r="F9" s="39" t="n">
-        <v>0.851</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G9" s="39" t="n">
-        <v>0.9109999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="H9" s="39" t="n">
         <v>0.92</v>
       </c>
       <c r="I9" s="39" t="n">
-        <v>0.9109999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="J9" s="39" t="n">
-        <v>0.7659999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="K9" s="39" t="n">
-        <v>0.7240000000000001</v>
+        <v>0.726</v>
       </c>
       <c r="L9" s="39" t="n">
-        <v>0.7490000000000001</v>
+        <v>0.752</v>
       </c>
       <c r="M9" s="39" t="n">
-        <v>0.792</v>
+        <v>0.795</v>
       </c>
       <c r="N9" s="40">
         <f>AVERAGE(B9:M9)</f>
@@ -2279,31 +2321,31 @@
         <v>415</v>
       </c>
       <c r="E10" s="41" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F10" s="41" t="n">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="G10" s="41" t="n">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="H10" s="41" t="n">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="I10" s="41" t="n">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="J10" s="41" t="n">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="K10" s="41" t="n">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="L10" s="41" t="n">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="M10" s="41" t="n">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="N10" s="42">
         <f>SUM(B10:M10)</f>
@@ -2326,31 +2368,31 @@
         <v>366</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="H11" s="43" t="n">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="I11" s="43" t="n">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="J11" s="43" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="K11" s="43" t="n">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="L11" s="43" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M11" s="43" t="n">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="N11" s="44">
         <f>SUM(B11:M11)</f>
@@ -2373,31 +2415,31 @@
         <v>68024</v>
       </c>
       <c r="E12" s="45" t="n">
-        <v>73064</v>
+        <v>73746</v>
       </c>
       <c r="F12" s="45" t="n">
-        <v>70468</v>
+        <v>57908</v>
       </c>
       <c r="G12" s="45" t="n">
-        <v>79704</v>
+        <v>83160</v>
       </c>
       <c r="H12" s="45" t="n">
-        <v>86526</v>
+        <v>89775</v>
       </c>
       <c r="I12" s="45" t="n">
-        <v>82134</v>
+        <v>85680</v>
       </c>
       <c r="J12" s="45" t="n">
-        <v>53130</v>
+        <v>55062</v>
       </c>
       <c r="K12" s="45" t="n">
-        <v>49275</v>
+        <v>51030</v>
       </c>
       <c r="L12" s="45" t="n">
-        <v>49275</v>
+        <v>51030</v>
       </c>
       <c r="M12" s="45" t="n">
-        <v>56595</v>
+        <v>59052</v>
       </c>
       <c r="N12" s="42">
         <f>SUM(B12:M12)</f>
@@ -2420,31 +2462,31 @@
         <v>61256</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>64216</v>
+        <v>64772</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>62437</v>
+        <v>50641</v>
       </c>
       <c r="G13" s="46" t="n">
-        <v>70620</v>
+        <v>73676</v>
       </c>
       <c r="H13" s="46" t="n">
-        <v>76665</v>
+        <v>79537</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>72773</v>
+        <v>75909</v>
       </c>
       <c r="J13" s="46" t="n">
-        <v>47075</v>
+        <v>48783</v>
       </c>
       <c r="K13" s="46" t="n">
-        <v>43659</v>
+        <v>45211</v>
       </c>
       <c r="L13" s="46" t="n">
-        <v>43659</v>
+        <v>45211</v>
       </c>
       <c r="M13" s="46" t="n">
-        <v>50145</v>
+        <v>52318</v>
       </c>
       <c r="N13" s="44">
         <f>SUM(B13:M13)</f>
@@ -2467,7 +2509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2490,7 +2532,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-04-27. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-05-01. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2539,23 +2581,23 @@
     <row r="5">
       <c r="A5" s="47" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B5" s="48" t="n">
-        <v>73064</v>
+        <v>57908</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>73064</v>
+        <v>57908</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="48" t="n">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="F5" s="48" t="n">
-        <v>406</v>
+        <v>311</v>
       </c>
       <c r="G5" s="48" t="n">
         <v>0</v>
@@ -2567,58 +2609,58 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="n">
-        <v>70468</v>
-      </c>
-      <c r="C6" s="49" t="n">
-        <v>60449</v>
-      </c>
-      <c r="D6" s="50" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="E6" s="48" t="n">
-        <v>444</v>
-      </c>
-      <c r="F6" s="48" t="n">
-        <v>325</v>
-      </c>
-      <c r="G6" s="48" t="n">
-        <v>10019</v>
-      </c>
-      <c r="H6" s="51" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="n">
+        <v>83160</v>
+      </c>
+      <c r="C6" s="54" t="n">
+        <v>42530</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="E6" s="53" t="n">
+        <v>552</v>
+      </c>
+      <c r="F6" s="53" t="n">
+        <v>236</v>
+      </c>
+      <c r="G6" s="53" t="n">
+        <v>40630</v>
+      </c>
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>Building</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="B7" s="53" t="n">
-        <v>79704</v>
+        <v>89775</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>38444</v>
+        <v>25414</v>
       </c>
       <c r="D7" s="55" t="n">
-        <v>0.482</v>
+        <v>0.283</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>41260</v>
+        <v>64361</v>
       </c>
       <c r="H7" s="56" t="inlineStr">
         <is>
@@ -2627,118 +2669,118 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B8" s="53" t="n">
-        <v>86526</v>
-      </c>
-      <c r="C8" s="54" t="n">
-        <v>22537</v>
-      </c>
-      <c r="D8" s="55" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E8" s="53" t="n">
-        <v>524</v>
-      </c>
-      <c r="F8" s="53" t="n">
-        <v>121</v>
-      </c>
-      <c r="G8" s="53" t="n">
-        <v>63989</v>
-      </c>
-      <c r="H8" s="56" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>85680</v>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>10977</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>523</v>
+      </c>
+      <c r="F8" s="57" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="57" t="n">
+        <v>74703</v>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="n">
+        <v>55062</v>
+      </c>
+      <c r="C9" s="54" t="n">
+        <v>15604</v>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="E9" s="53" t="n">
+        <v>488</v>
+      </c>
+      <c r="F9" s="53" t="n">
+        <v>87</v>
+      </c>
+      <c r="G9" s="53" t="n">
+        <v>39458</v>
+      </c>
+      <c r="H9" s="56" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B9" s="57" t="n">
-        <v>82134</v>
-      </c>
-      <c r="C9" s="44" t="n">
-        <v>10977</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="E9" s="57" t="n">
-        <v>523</v>
-      </c>
-      <c r="F9" s="57" t="n">
-        <v>59</v>
-      </c>
-      <c r="G9" s="57" t="n">
-        <v>71157</v>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="n">
+        <v>51030</v>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>8513</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E10" s="57" t="n">
+        <v>473</v>
+      </c>
+      <c r="F10" s="57" t="n">
+        <v>46</v>
+      </c>
+      <c r="G10" s="57" t="n">
+        <v>42517</v>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="52" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B10" s="53" t="n">
-        <v>53130</v>
-      </c>
-      <c r="C10" s="54" t="n">
-        <v>15604</v>
-      </c>
-      <c r="D10" s="55" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="E10" s="53" t="n">
-        <v>488</v>
-      </c>
-      <c r="F10" s="53" t="n">
-        <v>87</v>
-      </c>
-      <c r="G10" s="53" t="n">
-        <v>37526</v>
-      </c>
-      <c r="H10" s="56" t="inlineStr">
-        <is>
-          <t>Building</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="B11" s="57" t="n">
-        <v>49275</v>
+        <v>51030</v>
       </c>
       <c r="C11" s="44" t="n">
-        <v>8513</v>
+        <v>2251</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0.173</v>
+        <v>0.044</v>
       </c>
       <c r="E11" s="57" t="n">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="F11" s="57" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G11" s="57" t="n">
-        <v>40762</v>
+        <v>48779</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
@@ -2749,26 +2791,26 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="B12" s="57" t="n">
-        <v>49275</v>
+        <v>59052</v>
       </c>
       <c r="C12" s="44" t="n">
-        <v>2251</v>
+        <v>3729</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="E12" s="57" t="n">
-        <v>450</v>
+        <v>339</v>
       </c>
       <c r="F12" s="57" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G12" s="57" t="n">
-        <v>47024</v>
+        <v>55323</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
@@ -2777,60 +2819,30 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B13" s="57" t="n">
-        <v>56595</v>
-      </c>
-      <c r="C13" s="44" t="n">
-        <v>3729</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="E13" s="57" t="n">
-        <v>339</v>
-      </c>
-      <c r="F13" s="57" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" s="57" t="n">
-        <v>52866</v>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="59">
-        <f>SUM(B5:B13)</f>
+      <c r="B13" s="59">
+        <f>SUM(B5:B12)</f>
         <v/>
       </c>
-      <c r="C14" s="59">
-        <f>SUM(C5:C13)</f>
+      <c r="C13" s="59">
+        <f>SUM(C5:C12)</f>
         <v/>
       </c>
-      <c r="D14" s="60">
-        <f>C14/B14</f>
+      <c r="D13" s="60">
+        <f>C13/B13</f>
         <v/>
       </c>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="59">
-        <f>B14-C14</f>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="61" t="n"/>
+      <c r="G13" s="59">
+        <f>B13-C13</f>
         <v/>
       </c>
-      <c r="H14" s="61" t="n"/>
+      <c r="H13" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2866,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Blends 3 months of closed actuals with seasonal projections calibrated from actual performance</t>
+          <t>Blends 4 months of closed actuals with seasonal projections calibrated from actual performance</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2902,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>762301</v>
+        <v>768573</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -2903,7 +2915,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-83964</v>
+        <v>-84422</v>
       </c>
       <c r="C6" s="62" t="n"/>
     </row>
@@ -2914,7 +2926,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-73521</v>
+        <v>-74231</v>
       </c>
       <c r="C7" s="62" t="n"/>
     </row>
@@ -2925,7 +2937,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>-5307</v>
+        <v>-5609</v>
       </c>
       <c r="C8" s="62" t="n"/>
     </row>
@@ -2936,10 +2948,10 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>677170</v>
+        <v>681979</v>
       </c>
       <c r="C9" s="63" t="n">
-        <v>0.8883236411863555</v>
+        <v>0.887331457128991</v>
       </c>
     </row>
     <row r="10">
@@ -2949,7 +2961,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>-197105</v>
+        <v>-183474</v>
       </c>
       <c r="C10" s="62" t="n"/>
     </row>
@@ -2960,7 +2972,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-76230</v>
+        <v>-76857</v>
       </c>
       <c r="C11" s="62" t="n"/>
     </row>
@@ -3004,10 +3016,10 @@
         </is>
       </c>
       <c r="B15" s="65" t="n">
-        <v>339656</v>
+        <v>357469</v>
       </c>
       <c r="C15" s="66" t="n">
-        <v>0.4455667774278139</v>
+        <v>0.4651074133491548</v>
       </c>
     </row>
     <row r="17">
@@ -3025,7 +3037,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3035,7 +3047,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20">
@@ -3045,7 +3057,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.851</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="21">
@@ -3065,7 +3077,7 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.049</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="24">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-05-01</t>
+          <t>Prepared 2026-05-08</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>768573</v>
+        <v>776028</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>681979</v>
+        <v>686826</v>
       </c>
     </row>
     <row r="17">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>324510</v>
+        <v>325256</v>
       </c>
     </row>
     <row r="18">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>357469</v>
+        <v>361570</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8140000000000001</v>
+        <v>0.8190000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -933,7 +933,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.6% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>357469</v>
+        <v>361570</v>
       </c>
     </row>
     <row r="42">
@@ -1614,7 +1614,7 @@
         <v>73746</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>57908</v>
+        <v>65363</v>
       </c>
       <c r="G7" s="9">
         <f>SUM(B7:F7)</f>
@@ -1637,10 +1637,10 @@
         <v>61256</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>64772</v>
+        <v>64778</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>50641</v>
+        <v>56993</v>
       </c>
       <c r="G8" s="24">
         <f>SUM(B8:F8)</f>
@@ -1884,10 +1884,10 @@
         <v>37666</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>39861</v>
+        <v>39867</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>50583</v>
+        <v>56935</v>
       </c>
       <c r="G20" s="28">
         <f>SUM(B20:F20)</f>
@@ -2136,7 +2136,7 @@
         <v>69</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G6" s="35" t="n">
         <v>64</v>
@@ -2183,7 +2183,7 @@
         <v>151</v>
       </c>
       <c r="F7" s="37" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G7" s="37" t="n">
         <v>165</v>
@@ -2277,7 +2277,7 @@
         <v>0.8390000000000001</v>
       </c>
       <c r="F9" s="39" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.758</v>
       </c>
       <c r="G9" s="39" t="n">
         <v>0.914</v>
@@ -2324,7 +2324,7 @@
         <v>488</v>
       </c>
       <c r="F10" s="41" t="n">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="G10" s="41" t="n">
         <v>504</v>
@@ -2371,7 +2371,7 @@
         <v>410</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>462</v>
@@ -2418,7 +2418,7 @@
         <v>73746</v>
       </c>
       <c r="F12" s="45" t="n">
-        <v>57908</v>
+        <v>65363</v>
       </c>
       <c r="G12" s="45" t="n">
         <v>83160</v>
@@ -2462,31 +2462,31 @@
         <v>61256</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>64772</v>
+        <v>64778</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>50641</v>
+        <v>56993</v>
       </c>
       <c r="G13" s="46" t="n">
-        <v>73676</v>
+        <v>73412</v>
       </c>
       <c r="H13" s="46" t="n">
-        <v>79537</v>
+        <v>79251</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>75909</v>
+        <v>75637</v>
       </c>
       <c r="J13" s="46" t="n">
-        <v>48783</v>
+        <v>48608</v>
       </c>
       <c r="K13" s="46" t="n">
-        <v>45211</v>
+        <v>45048</v>
       </c>
       <c r="L13" s="46" t="n">
-        <v>45211</v>
+        <v>45048</v>
       </c>
       <c r="M13" s="46" t="n">
-        <v>52318</v>
+        <v>52130</v>
       </c>
       <c r="N13" s="44">
         <f>SUM(B13:M13)</f>
@@ -2532,7 +2532,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-05-01. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-05-08. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2585,19 +2585,19 @@
         </is>
       </c>
       <c r="B5" s="48" t="n">
-        <v>57908</v>
+        <v>65363</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>57908</v>
+        <v>65363</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="48" t="n">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="F5" s="48" t="n">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="G5" s="48" t="n">
         <v>0</v>
@@ -2618,19 +2618,19 @@
         <v>83160</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>42530</v>
+        <v>40778</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>0.511</v>
+        <v>0.49</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>40630</v>
+        <v>42382</v>
       </c>
       <c r="H6" s="56" t="inlineStr">
         <is>
@@ -2648,19 +2648,19 @@
         <v>89775</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>25414</v>
+        <v>40625</v>
       </c>
       <c r="D7" s="55" t="n">
-        <v>0.283</v>
+        <v>0.453</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>64361</v>
+        <v>49150</v>
       </c>
       <c r="H7" s="56" t="inlineStr">
         <is>
@@ -2678,19 +2678,19 @@
         <v>85680</v>
       </c>
       <c r="C8" s="44" t="n">
-        <v>10977</v>
+        <v>11830</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0.128</v>
+        <v>0.138</v>
       </c>
       <c r="E8" s="57" t="n">
-        <v>523</v>
+        <v>473</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G8" s="57" t="n">
-        <v>74703</v>
+        <v>73850</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
@@ -2708,19 +2708,19 @@
         <v>55062</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>15604</v>
+        <v>17258</v>
       </c>
       <c r="D9" s="55" t="n">
-        <v>0.283</v>
+        <v>0.313</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>39458</v>
+        <v>37804</v>
       </c>
       <c r="H9" s="56" t="inlineStr">
         <is>
@@ -2738,19 +2738,19 @@
         <v>51030</v>
       </c>
       <c r="C10" s="44" t="n">
-        <v>8513</v>
+        <v>6759</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0.167</v>
+        <v>0.132</v>
       </c>
       <c r="E10" s="57" t="n">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="F10" s="57" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G10" s="57" t="n">
-        <v>42517</v>
+        <v>44271</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>768573</v>
+        <v>776028</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-84422</v>
+        <v>-87452</v>
       </c>
       <c r="C6" s="62" t="n"/>
     </row>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-74231</v>
+        <v>-75151</v>
       </c>
       <c r="C7" s="62" t="n"/>
     </row>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>-5609</v>
+        <v>-5806</v>
       </c>
       <c r="C8" s="62" t="n"/>
     </row>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>681979</v>
+        <v>686826</v>
       </c>
       <c r="C9" s="63" t="n">
-        <v>0.887331457128991</v>
+        <v>0.8850531166401212</v>
       </c>
     </row>
     <row r="10">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-76857</v>
+        <v>-77603</v>
       </c>
       <c r="C11" s="62" t="n"/>
     </row>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="B15" s="65" t="n">
-        <v>357469</v>
+        <v>361570</v>
       </c>
       <c r="C15" s="66" t="n">
-        <v>0.4651074133491548</v>
+        <v>0.4659239099620117</v>
       </c>
     </row>
     <row r="17">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +106,12 @@
       <b val="1"/>
       <color rgb="002D8B2D"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -197,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,14 +237,18 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,11 +296,14 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -298,6 +311,46 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEBEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="002D8B2D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00E53935"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEBEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1516,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1624,7 +1677,7 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Net to Owner (after OTA/taxes/fees)</t>
+          <t>Net to Owner (after OTA &amp; Processing)</t>
         </is>
       </c>
       <c r="B8" s="24" t="n">
@@ -1848,20 +1901,25 @@
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
-        <v>26905</v>
-      </c>
-      <c r="C18" s="26" t="n">
-        <v>18060</v>
-      </c>
-      <c r="D18" s="26" t="n">
-        <v>23590</v>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>24911</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>58</v>
+      <c r="B18" s="26">
+        <f>SUM(B11:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>SUM(C11:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>SUM(D11:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>SUM(E11:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>SUM(F11:F17)</f>
+        <v/>
       </c>
       <c r="G18" s="26">
         <f>SUM(B18:F18)</f>
@@ -1874,55 +1932,91 @@
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B20" s="28" t="n">
-        <v>8880</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>30820</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>37666</v>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>39867</v>
-      </c>
-      <c r="F20" s="28" t="n">
-        <v>56935</v>
+      <c r="B20" s="28">
+        <f>B8-B18</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>C8-C18</f>
+        <v/>
+      </c>
+      <c r="D20" s="28">
+        <f>D8-D18</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>E8-E18</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>F8-F18</f>
+        <v/>
       </c>
       <c r="G20" s="28">
         <f>SUM(B20:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Reconciliation check:</t>
+        </is>
+      </c>
+      <c r="B22" s="30">
+        <f>IF(ROUND(B8-B18-B20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="C22" s="30">
+        <f>IF(ROUND(C8-C18-C20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="D22" s="30">
+        <f>IF(ROUND(D8-D18-D20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="E22" s="30">
+        <f>IF(ROUND(E8-E18-E20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="F22" s="30">
+        <f>IF(ROUND(F8-F18-F20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="G22" s="30">
+        <f>IF(ROUND(G8-G18-G20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>QBO RECONCILIATION</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>QBO YTD Rental Income (Jan 1 – Apr 14): $170,225</t>
-        </is>
-      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Total Expenses: $89,338  |  QBO YTD NOI: $80,887</t>
+          <t>QBO YTD Rental Income (Jan 1 – Apr 14): $170,225</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>QBO YTD Total Expenses: $89,338  |  QBO YTD NOI: $80,887</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Note: Minor variances between PMS and QBO are expected due to cash vs accrual timing and partial-month cutoffs.</t>
         </is>
@@ -1931,12 +2025,60 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
   </mergeCells>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>B22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>B22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>C22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>C22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>D22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>D22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>E22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>E22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>F22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>F22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>G22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="1">
+      <formula>G22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1983,74 +2125,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>BOOKED</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr">
+      <c r="K4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="L4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr"/>
+      <c r="A5" s="35" t="inlineStr"/>
       <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Jan</t>
@@ -2118,48 +2260,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="37" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="37" t="n">
         <v>55</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="37" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="37" t="n">
         <v>69</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="37" t="n">
         <v>59</v>
       </c>
-      <c r="G6" s="35" t="n">
+      <c r="G6" s="37" t="n">
         <v>64</v>
       </c>
-      <c r="H6" s="35" t="n">
+      <c r="H6" s="37" t="n">
         <v>66</v>
       </c>
-      <c r="I6" s="35" t="n">
+      <c r="I6" s="37" t="n">
         <v>66</v>
       </c>
-      <c r="J6" s="35" t="n">
+      <c r="J6" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="K6" s="35" t="n">
+      <c r="K6" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="L6" s="35" t="n">
+      <c r="L6" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="37" t="n">
         <v>57</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="38">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2170,90 +2312,90 @@
           <t>Nights Sold</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="39" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="39" t="n">
         <v>136</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="39" t="n">
         <v>164</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="39" t="n">
         <v>151</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="39" t="n">
         <v>141</v>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G7" s="39" t="n">
         <v>165</v>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="39" t="n">
         <v>171</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="39" t="n">
         <v>170</v>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="39" t="n">
         <v>138</v>
       </c>
-      <c r="K7" s="37" t="n">
+      <c r="K7" s="39" t="n">
         <v>135</v>
       </c>
-      <c r="L7" s="37" t="n">
+      <c r="L7" s="39" t="n">
         <v>135</v>
       </c>
-      <c r="M7" s="37" t="n">
+      <c r="M7" s="39" t="n">
         <v>148</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="40">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Available Nights</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="37" t="n">
         <v>168</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="G8" s="35" t="n">
+      <c r="G8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="H8" s="35" t="n">
+      <c r="H8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="I8" s="35" t="n">
+      <c r="I8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="J8" s="35" t="n">
+      <c r="J8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="K8" s="35" t="n">
+      <c r="K8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="L8" s="35" t="n">
+      <c r="L8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="M8" s="35" t="n">
+      <c r="M8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="38">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -2264,90 +2406,90 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="41" t="n">
         <v>0.753</v>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="41" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="41" t="n">
         <v>0.882</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="41" t="n">
         <v>0.8390000000000001</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="41" t="n">
         <v>0.758</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="41" t="n">
         <v>0.914</v>
       </c>
-      <c r="H9" s="39" t="n">
+      <c r="H9" s="41" t="n">
         <v>0.92</v>
       </c>
-      <c r="I9" s="39" t="n">
+      <c r="I9" s="41" t="n">
         <v>0.914</v>
       </c>
-      <c r="J9" s="39" t="n">
+      <c r="J9" s="41" t="n">
         <v>0.769</v>
       </c>
-      <c r="K9" s="39" t="n">
+      <c r="K9" s="41" t="n">
         <v>0.726</v>
       </c>
-      <c r="L9" s="39" t="n">
+      <c r="L9" s="41" t="n">
         <v>0.752</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="41" t="n">
         <v>0.795</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="42">
         <f>AVERAGE(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="43" t="n">
         <v>286</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="43" t="n">
         <v>398</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="43" t="n">
         <v>415</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="43" t="n">
         <v>488</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="43" t="n">
         <v>464</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="43" t="n">
         <v>504</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="43" t="n">
         <v>525</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I10" s="43" t="n">
         <v>504</v>
       </c>
-      <c r="J10" s="41" t="n">
+      <c r="J10" s="43" t="n">
         <v>399</v>
       </c>
-      <c r="K10" s="41" t="n">
+      <c r="K10" s="43" t="n">
         <v>378</v>
       </c>
-      <c r="L10" s="41" t="n">
+      <c r="L10" s="43" t="n">
         <v>378</v>
       </c>
-      <c r="M10" s="41" t="n">
+      <c r="M10" s="43" t="n">
         <v>399</v>
       </c>
-      <c r="N10" s="42">
+      <c r="N10" s="44">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -2358,43 +2500,43 @@
           <t>RevPAR</t>
         </is>
       </c>
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="45" t="n">
         <v>215</v>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="45" t="n">
         <v>322</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="45" t="n">
         <v>366</v>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="45" t="n">
         <v>410</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="45" t="n">
         <v>351</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="45" t="n">
         <v>462</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="45" t="n">
         <v>483</v>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="45" t="n">
         <v>461</v>
       </c>
-      <c r="J11" s="43" t="n">
+      <c r="J11" s="45" t="n">
         <v>306</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="45" t="n">
         <v>274</v>
       </c>
-      <c r="L11" s="43" t="n">
+      <c r="L11" s="45" t="n">
         <v>284</v>
       </c>
-      <c r="M11" s="43" t="n">
+      <c r="M11" s="45" t="n">
         <v>317</v>
       </c>
-      <c r="N11" s="44">
+      <c r="N11" s="46">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -2405,90 +2547,90 @@
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="47" t="n">
         <v>40041</v>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="47" t="n">
         <v>54065</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="47" t="n">
         <v>68024</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="47" t="n">
         <v>73746</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="47" t="n">
         <v>65363</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="47" t="n">
         <v>83160</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="47" t="n">
         <v>89775</v>
       </c>
-      <c r="I12" s="45" t="n">
+      <c r="I12" s="47" t="n">
         <v>85680</v>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="J12" s="47" t="n">
         <v>55062</v>
       </c>
-      <c r="K12" s="45" t="n">
+      <c r="K12" s="47" t="n">
         <v>51030</v>
       </c>
-      <c r="L12" s="45" t="n">
+      <c r="L12" s="47" t="n">
         <v>51030</v>
       </c>
-      <c r="M12" s="45" t="n">
+      <c r="M12" s="47" t="n">
         <v>59052</v>
       </c>
-      <c r="N12" s="42">
+      <c r="N12" s="44">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="48" t="n">
         <v>35785</v>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="48" t="n">
         <v>48880</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="48" t="n">
         <v>61256</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="48" t="n">
         <v>64778</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="48" t="n">
         <v>56993</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="48" t="n">
         <v>73412</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="48" t="n">
         <v>79251</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="I13" s="48" t="n">
         <v>75637</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="48" t="n">
         <v>48608</v>
       </c>
-      <c r="K13" s="46" t="n">
+      <c r="K13" s="48" t="n">
         <v>45048</v>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="48" t="n">
         <v>45048</v>
       </c>
-      <c r="M13" s="46" t="n">
+      <c r="M13" s="48" t="n">
         <v>52130</v>
       </c>
-      <c r="N13" s="44">
+      <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -2579,117 +2721,117 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="50" t="n">
         <v>65363</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="51" t="n">
         <v>65363</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="50" t="n">
         <v>464</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="50" t="n">
         <v>351</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G5" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="H5" s="53" t="inlineStr">
         <is>
           <t>Fully Booked</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B6" s="53" t="n">
+      <c r="B6" s="55" t="n">
         <v>83160</v>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="56" t="n">
         <v>40778</v>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="57" t="n">
         <v>0.49</v>
       </c>
-      <c r="E6" s="53" t="n">
+      <c r="E6" s="55" t="n">
         <v>551</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="55" t="n">
         <v>227</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="55" t="n">
         <v>42382</v>
       </c>
-      <c r="H6" s="56" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B7" s="53" t="n">
+      <c r="B7" s="55" t="n">
         <v>89775</v>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="56" t="n">
         <v>40625</v>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="57" t="n">
         <v>0.453</v>
       </c>
-      <c r="E7" s="53" t="n">
+      <c r="E7" s="55" t="n">
         <v>557</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="55" t="n">
         <v>218</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="55" t="n">
         <v>49150</v>
       </c>
-      <c r="H7" s="56" t="inlineStr">
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="B8" s="57" t="n">
+      <c r="B8" s="59" t="n">
         <v>85680</v>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="46" t="n">
         <v>11830</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="42" t="n">
         <v>0.138</v>
       </c>
-      <c r="E8" s="57" t="n">
+      <c r="E8" s="59" t="n">
         <v>473</v>
       </c>
-      <c r="F8" s="57" t="n">
+      <c r="F8" s="59" t="n">
         <v>64</v>
       </c>
-      <c r="G8" s="57" t="n">
+      <c r="G8" s="59" t="n">
         <v>73850</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -2699,57 +2841,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B9" s="53" t="n">
+      <c r="B9" s="55" t="n">
         <v>55062</v>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="56" t="n">
         <v>17258</v>
       </c>
-      <c r="D9" s="55" t="n">
+      <c r="D9" s="57" t="n">
         <v>0.313</v>
       </c>
-      <c r="E9" s="53" t="n">
+      <c r="E9" s="55" t="n">
         <v>479</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="55" t="n">
         <v>96</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="55" t="n">
         <v>37804</v>
       </c>
-      <c r="H9" s="56" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B10" s="57" t="n">
+      <c r="B10" s="59" t="n">
         <v>51030</v>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="46" t="n">
         <v>6759</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="42" t="n">
         <v>0.132</v>
       </c>
-      <c r="E10" s="57" t="n">
+      <c r="E10" s="59" t="n">
         <v>483</v>
       </c>
-      <c r="F10" s="57" t="n">
+      <c r="F10" s="59" t="n">
         <v>36</v>
       </c>
-      <c r="G10" s="57" t="n">
+      <c r="G10" s="59" t="n">
         <v>44271</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -2759,27 +2901,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="B11" s="57" t="n">
+      <c r="B11" s="59" t="n">
         <v>51030</v>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="46" t="n">
         <v>2251</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="42" t="n">
         <v>0.044</v>
       </c>
-      <c r="E11" s="57" t="n">
+      <c r="E11" s="59" t="n">
         <v>450</v>
       </c>
-      <c r="F11" s="57" t="n">
+      <c r="F11" s="59" t="n">
         <v>13</v>
       </c>
-      <c r="G11" s="57" t="n">
+      <c r="G11" s="59" t="n">
         <v>48779</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -2789,27 +2931,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B12" s="57" t="n">
+      <c r="B12" s="59" t="n">
         <v>59052</v>
       </c>
-      <c r="C12" s="44" t="n">
+      <c r="C12" s="46" t="n">
         <v>3729</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="42" t="n">
         <v>0.063</v>
       </c>
-      <c r="E12" s="57" t="n">
+      <c r="E12" s="59" t="n">
         <v>339</v>
       </c>
-      <c r="F12" s="57" t="n">
+      <c r="F12" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="G12" s="57" t="n">
+      <c r="G12" s="59" t="n">
         <v>55323</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -2819,30 +2961,30 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="59">
+      <c r="B13" s="61">
         <f>SUM(B5:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="61">
         <f>SUM(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="62">
         <f>C13/B13</f>
         <v/>
       </c>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="59">
+      <c r="E13" s="63" t="n"/>
+      <c r="F13" s="63" t="n"/>
+      <c r="G13" s="61">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="H13" s="61" t="n"/>
+      <c r="H13" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2860,10 +3002,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -2915,193 +3057,369 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-87452</v>
-      </c>
-      <c r="C6" s="62" t="n"/>
+        <v>-83999</v>
+      </c>
+      <c r="C6" s="10">
+        <f>B6/B5</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Taxes (TOT)</t>
+          <t xml:space="preserve">  Processing Fees</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-75151</v>
-      </c>
-      <c r="C7" s="62" t="n"/>
+        <v>-5203</v>
+      </c>
+      <c r="C7" s="10">
+        <f>B7/B5</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Processing Fees</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>-5806</v>
-      </c>
-      <c r="C8" s="62" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
-        <v>686826</v>
-      </c>
-      <c r="C9" s="63" t="n">
-        <v>0.8850531166401212</v>
+      <c r="B8" s="24">
+        <f>B5+B6+B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="64">
+        <f>B8/B5</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Direct OpEx (Cleaning, Supplies, etc.)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>-183474</v>
-      </c>
-      <c r="C10" s="62" t="n"/>
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Management Fee (10%)</t>
+          <t xml:space="preserve">  Cleaning</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-77603</v>
-      </c>
-      <c r="C11" s="62" t="n"/>
+        <v>-72622</v>
+      </c>
+      <c r="C11" s="66">
+        <f>B11/B5</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Property Tax</t>
+          <t xml:space="preserve">  Supplies, Maintenance, Other</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-26679</v>
-      </c>
-      <c r="C12" s="62" t="n"/>
+        <v>-110852</v>
+      </c>
+      <c r="C12" s="66">
+        <f>B12/B5</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Insurance</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>-13500</v>
-      </c>
-      <c r="C13" s="62" t="n"/>
+          <t xml:space="preserve">  Management Fee (10% of Gross)</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>-0.10*B5</f>
+        <v/>
+      </c>
+      <c r="C13" s="66">
+        <f>B13/B5</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Fixed Costs</t>
+          <t xml:space="preserve">  Property Tax</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
+        <v>-26679</v>
+      </c>
+      <c r="C14" s="66">
+        <f>B14/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Insurance</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>-13500</v>
+      </c>
+      <c r="C15" s="66">
+        <f>B15/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Fixed Costs (utilities, internet, etc.)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="C14" s="62" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="C16" s="66">
+        <f>B16/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="68">
+        <f>SUM(B11:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="69">
+        <f>B17/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B15" s="65" t="n">
+      <c r="B19" s="28">
+        <f>B8+B17</f>
+        <v/>
+      </c>
+      <c r="C19" s="70">
+        <f>B19/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>RECONCILIATION CHECK</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Expected NOI (from model)</t>
+        </is>
+      </c>
+      <c r="B22" s="59" t="n">
         <v>361570</v>
       </c>
-      <c r="C15" s="66" t="n">
-        <v>0.4659239099620117</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Calculated NOI (this tab)</t>
+        </is>
+      </c>
+      <c r="B23" s="59">
+        <f>B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+      <c r="B24" s="59">
+        <f>B23-B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B25" s="31">
+        <f>IF(ABS(B24)&lt;=1,"OK - reconciles","REVIEW - variance exceeds $1")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PASS-THROUGH TAXES &amp; FEES (INFORMATIONAL)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>The following amounts are collected from guests at booking and either remitted to the City or</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>offset by corresponding expenses. They are NOT deducted from Net to Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>TOT (Transient Occupancy Tax) collected from guests</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>75275</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Remitted to City of Santa Barbara (12% lodging tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Cleaning fees collected from guests</t>
+        </is>
+      </c>
+      <c r="B32" s="71" t="inlineStr">
+        <is>
+          <t>see Cleaning expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Offset by Cleaning expense above; net-neutral pass-through</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>MODEL INPUTS</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Closed Months Used for Calibration</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B36" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Baseline ADR (de-seasonalized)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B37" s="7" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Baseline Occupancy (de-seasonalized)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B38" s="10" t="n">
         <v>0.855</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Max Occupancy Cap</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B39" s="10" t="n">
         <v>0.92</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Back-test MAPE (Gross Revenue)</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B40" s="10" t="n">
         <v>0.168</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>METHODOLOGY</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="72" t="inlineStr">
         <is>
           <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline - meaning projections tighten over time as operating history grows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>B25="OK - reconciles"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>NOT(B25="OK - reconciles")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-05-08</t>
+          <t>Prepared 2026-05-12</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>776028</v>
+        <v>780043</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>686826</v>
+        <v>689397</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>325256</v>
+        <v>325657</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>361570</v>
+        <v>363740</v>
       </c>
     </row>
     <row r="19">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>361570</v>
+        <v>363740</v>
       </c>
     </row>
     <row r="42">
@@ -1667,7 +1667,7 @@
         <v>73746</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>65363</v>
+        <v>69378</v>
       </c>
       <c r="G7" s="9">
         <f>SUM(B7:F7)</f>
@@ -1693,7 +1693,7 @@
         <v>64778</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>56993</v>
+        <v>60286</v>
       </c>
       <c r="G8" s="24">
         <f>SUM(B8:F8)</f>
@@ -2278,7 +2278,7 @@
         <v>69</v>
       </c>
       <c r="F6" s="37" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G6" s="37" t="n">
         <v>64</v>
@@ -2325,7 +2325,7 @@
         <v>151</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G7" s="39" t="n">
         <v>165</v>
@@ -2419,7 +2419,7 @@
         <v>0.8390000000000001</v>
       </c>
       <c r="F9" s="41" t="n">
-        <v>0.758</v>
+        <v>0.8059999999999999</v>
       </c>
       <c r="G9" s="41" t="n">
         <v>0.914</v>
@@ -2466,7 +2466,7 @@
         <v>488</v>
       </c>
       <c r="F10" s="43" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>504</v>
@@ -2513,7 +2513,7 @@
         <v>410</v>
       </c>
       <c r="F11" s="45" t="n">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G11" s="45" t="n">
         <v>462</v>
@@ -2560,7 +2560,7 @@
         <v>73746</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>65363</v>
+        <v>69378</v>
       </c>
       <c r="G12" s="47" t="n">
         <v>83160</v>
@@ -2607,28 +2607,28 @@
         <v>64778</v>
       </c>
       <c r="F13" s="48" t="n">
-        <v>56993</v>
+        <v>60286</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>73412</v>
+        <v>73285</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79251</v>
+        <v>79115</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>75637</v>
+        <v>75506</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48608</v>
+        <v>48524</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45048</v>
+        <v>44971</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45048</v>
+        <v>44971</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52130</v>
+        <v>52040</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2674,7 +2674,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-05-08. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-05-12. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>65363</v>
+        <v>69378</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>65363</v>
+        <v>69378</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2751,32 +2751,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="50" t="n">
         <v>83160</v>
       </c>
-      <c r="C6" s="56" t="n">
-        <v>40778</v>
-      </c>
-      <c r="D6" s="57" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E6" s="55" t="n">
-        <v>551</v>
-      </c>
-      <c r="F6" s="55" t="n">
-        <v>227</v>
-      </c>
-      <c r="G6" s="55" t="n">
-        <v>42382</v>
-      </c>
-      <c r="H6" s="58" t="inlineStr">
-        <is>
-          <t>Building</t>
+      <c r="C6" s="51" t="n">
+        <v>51891</v>
+      </c>
+      <c r="D6" s="52" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="E6" s="50" t="n">
+        <v>577</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>288</v>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>31269</v>
+      </c>
+      <c r="H6" s="53" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -2790,19 +2790,19 @@
         <v>89775</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>40625</v>
+        <v>42832</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.453</v>
+        <v>0.477</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>49150</v>
+        <v>46943</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>776028</v>
+        <v>780043</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-83999</v>
+        <v>-85402</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5203</v>
+        <v>-5244</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>361570</v>
+        <v>363740</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>75275</v>
+        <v>75664</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-05-12</t>
+          <t>Prepared 2026-05-17</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>780043</v>
+        <v>787438</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>689397</v>
+        <v>697618</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>325657</v>
+        <v>326937</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>363740</v>
+        <v>370681</v>
       </c>
     </row>
     <row r="19">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.823</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>363740</v>
+        <v>370681</v>
       </c>
     </row>
     <row r="42">
@@ -1667,7 +1667,7 @@
         <v>73746</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>69378</v>
+        <v>76773</v>
       </c>
       <c r="G7" s="9">
         <f>SUM(B7:F7)</f>
@@ -1693,7 +1693,7 @@
         <v>64778</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>60286</v>
+        <v>67488</v>
       </c>
       <c r="G8" s="24">
         <f>SUM(B8:F8)</f>
@@ -2278,28 +2278,28 @@
         <v>69</v>
       </c>
       <c r="F6" s="37" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G6" s="37" t="n">
         <v>64</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I6" s="37" t="n">
         <v>66</v>
       </c>
       <c r="J6" s="37" t="n">
+        <v>54</v>
+      </c>
+      <c r="K6" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="K6" s="37" t="n">
-        <v>52</v>
-      </c>
       <c r="L6" s="37" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M6" s="37" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N6" s="38">
         <f>SUM(B6:M6)</f>
@@ -2325,7 +2325,7 @@
         <v>151</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G7" s="39" t="n">
         <v>165</v>
@@ -2419,7 +2419,7 @@
         <v>0.8390000000000001</v>
       </c>
       <c r="F9" s="41" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="G9" s="41" t="n">
         <v>0.914</v>
@@ -2466,7 +2466,7 @@
         <v>488</v>
       </c>
       <c r="F10" s="43" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>504</v>
@@ -2513,7 +2513,7 @@
         <v>410</v>
       </c>
       <c r="F11" s="45" t="n">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="G11" s="45" t="n">
         <v>462</v>
@@ -2560,7 +2560,7 @@
         <v>73746</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>69378</v>
+        <v>76773</v>
       </c>
       <c r="G12" s="47" t="n">
         <v>83160</v>
@@ -2607,28 +2607,28 @@
         <v>64778</v>
       </c>
       <c r="F13" s="48" t="n">
-        <v>60286</v>
+        <v>67488</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>73285</v>
+        <v>73464</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79115</v>
+        <v>79308</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>75506</v>
+        <v>75690</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48524</v>
+        <v>48642</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>44971</v>
+        <v>45080</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>44971</v>
+        <v>45080</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52040</v>
+        <v>52167</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2674,7 +2674,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-05-12. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-05-17. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>69378</v>
+        <v>76773</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>69378</v>
+        <v>76773</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>83160</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>51891</v>
+        <v>50003</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.624</v>
+        <v>0.601</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>577</v>
+        <v>521</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>31269</v>
+        <v>33157</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
@@ -2790,19 +2790,19 @@
         <v>89775</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>42832</v>
+        <v>42231</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.477</v>
+        <v>0.47</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>46943</v>
+        <v>47544</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2820,19 +2820,19 @@
         <v>85680</v>
       </c>
       <c r="C8" s="46" t="n">
-        <v>11830</v>
+        <v>17062</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0.138</v>
+        <v>0.199</v>
       </c>
       <c r="E8" s="59" t="n">
-        <v>473</v>
+        <v>550</v>
       </c>
       <c r="F8" s="59" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G8" s="59" t="n">
-        <v>73850</v>
+        <v>68618</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
@@ -2880,19 +2880,19 @@
         <v>51030</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>6759</v>
+        <v>7115</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0.132</v>
+        <v>0.139</v>
       </c>
       <c r="E10" s="59" t="n">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F10" s="59" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G10" s="59" t="n">
-        <v>44271</v>
+        <v>43915</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>780043</v>
+        <v>787438</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-85402</v>
+        <v>-84536</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5244</v>
+        <v>-5284</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-72622</v>
+        <v>-73162</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>363740</v>
+        <v>370681</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>75664</v>
+        <v>76381</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-05-17</t>
+          <t>Prepared 2026-05-26</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>787438</v>
+        <v>790516</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>697618</v>
+        <v>699271</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>326937</v>
+        <v>346398</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>370681</v>
+        <v>352873</v>
       </c>
     </row>
     <row r="19">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.83</v>
+        <v>0.8320000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>370681</v>
+        <v>352873</v>
       </c>
     </row>
     <row r="42">
@@ -1667,7 +1667,7 @@
         <v>73746</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>76773</v>
+        <v>79851</v>
       </c>
       <c r="G7" s="9">
         <f>SUM(B7:F7)</f>
@@ -1693,7 +1693,7 @@
         <v>64778</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>67488</v>
+        <v>69703</v>
       </c>
       <c r="G8" s="24">
         <f>SUM(B8:F8)</f>
@@ -1732,7 +1732,7 @@
         <v>7020</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0</v>
+        <v>7255</v>
       </c>
       <c r="G11" s="7">
         <f>SUM(B11:F11)</f>
@@ -1758,7 +1758,7 @@
         <v>607</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0</v>
+        <v>1378</v>
       </c>
       <c r="G12" s="7">
         <f>SUM(B12:F12)</f>
@@ -1784,7 +1784,7 @@
         <v>450</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="G13" s="7">
         <f>SUM(B13:F13)</f>
@@ -1810,7 +1810,7 @@
         <v>7662</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>58</v>
+        <v>4517</v>
       </c>
       <c r="G14" s="7">
         <f>SUM(B14:F14)</f>
@@ -1836,7 +1836,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G15" s="7">
         <f>SUM(B15:F15)</f>
@@ -1862,7 +1862,7 @@
         <v>8410</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
+        <v>9620</v>
       </c>
       <c r="G16" s="7">
         <f>SUM(B16:F16)</f>
@@ -1888,7 +1888,7 @@
         <v>617</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G17" s="7">
         <f>SUM(B17:F17)</f>
@@ -2278,16 +2278,16 @@
         <v>69</v>
       </c>
       <c r="F6" s="37" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" s="37" t="n">
         <v>67</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>54</v>
@@ -2325,7 +2325,7 @@
         <v>151</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
         <v>165</v>
@@ -2419,7 +2419,7 @@
         <v>0.8390000000000001</v>
       </c>
       <c r="F9" s="41" t="n">
-        <v>0.882</v>
+        <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
         <v>0.914</v>
@@ -2466,7 +2466,7 @@
         <v>488</v>
       </c>
       <c r="F10" s="43" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>504</v>
@@ -2513,7 +2513,7 @@
         <v>410</v>
       </c>
       <c r="F11" s="45" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="G11" s="45" t="n">
         <v>462</v>
@@ -2560,7 +2560,7 @@
         <v>73746</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>76773</v>
+        <v>79851</v>
       </c>
       <c r="G12" s="47" t="n">
         <v>83160</v>
@@ -2607,28 +2607,28 @@
         <v>64778</v>
       </c>
       <c r="F13" s="48" t="n">
-        <v>67488</v>
+        <v>69703</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>73464</v>
+        <v>73365</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79308</v>
+        <v>79201</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>75690</v>
+        <v>75589</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48642</v>
+        <v>48577</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45080</v>
+        <v>45020</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45080</v>
+        <v>45020</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52167</v>
+        <v>52097</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2674,7 +2674,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-05-17. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-05-26. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>76773</v>
+        <v>79851</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>76773</v>
+        <v>79851</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>83160</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>50003</v>
+        <v>50765</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.601</v>
+        <v>0.61</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>33157</v>
+        <v>32395</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
@@ -2790,19 +2790,19 @@
         <v>89775</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>42231</v>
+        <v>46523</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.47</v>
+        <v>0.518</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>47544</v>
+        <v>43252</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2850,19 +2850,19 @@
         <v>55062</v>
       </c>
       <c r="C9" s="56" t="n">
-        <v>17258</v>
+        <v>15257</v>
       </c>
       <c r="D9" s="57" t="n">
-        <v>0.313</v>
+        <v>0.277</v>
       </c>
       <c r="E9" s="55" t="n">
-        <v>479</v>
+        <v>424</v>
       </c>
       <c r="F9" s="55" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G9" s="55" t="n">
-        <v>37804</v>
+        <v>39805</v>
       </c>
       <c r="H9" s="58" t="inlineStr">
         <is>
@@ -2880,19 +2880,19 @@
         <v>51030</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>7115</v>
+        <v>8176</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0.139</v>
+        <v>0.16</v>
       </c>
       <c r="E10" s="59" t="n">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="F10" s="59" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G10" s="59" t="n">
-        <v>43915</v>
+        <v>42854</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2910,19 +2910,19 @@
         <v>51030</v>
       </c>
       <c r="C11" s="46" t="n">
-        <v>2251</v>
+        <v>3104</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0.044</v>
+        <v>0.061</v>
       </c>
       <c r="E11" s="59" t="n">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F11" s="59" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G11" s="59" t="n">
-        <v>48779</v>
+        <v>47926</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
@@ -2940,19 +2940,19 @@
         <v>59052</v>
       </c>
       <c r="C12" s="46" t="n">
-        <v>3729</v>
+        <v>5822</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0.063</v>
+        <v>0.099</v>
       </c>
       <c r="E12" s="59" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F12" s="59" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G12" s="59" t="n">
-        <v>55323</v>
+        <v>53230</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>787438</v>
+        <v>790516</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-84536</v>
+        <v>-85922</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5284</v>
+        <v>-5323</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-73162</v>
+        <v>-80633</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-110852</v>
+        <v>-122534</v>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>370681</v>
+        <v>352873</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76381</v>
+        <v>76680</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-05-26</t>
+          <t>Prepared 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>4 months actuals + seasonal model</t>
+          <t>5 months actuals + seasonal model</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>790516</v>
+        <v>766860</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>699271</v>
+        <v>678204</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>346398</v>
+        <v>336517</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>352873</v>
+        <v>341687</v>
       </c>
     </row>
     <row r="19">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8320000000000001</v>
+        <v>0.8059999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>352873</v>
+        <v>341687</v>
       </c>
     </row>
     <row r="42">
@@ -1569,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1579,6 +1579,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1591,7 +1592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating data: January – May 2026  |  QBO YTD cross-referenced</t>
+          <t>Operating data: January – Jun 2026  |  QBO YTD cross-referenced</t>
         </is>
       </c>
     </row>
@@ -1630,6 +1631,11 @@
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -1647,6 +1653,7 @@
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="22" t="n"/>
       <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1667,10 +1674,13 @@
         <v>73746</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>79851</v>
-      </c>
-      <c r="G7" s="9">
-        <f>SUM(B7:F7)</f>
+        <v>79700</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>54231</v>
+      </c>
+      <c r="H7" s="9">
+        <f>SUM(B7:G7)</f>
         <v/>
       </c>
     </row>
@@ -1693,10 +1703,13 @@
         <v>64778</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>69703</v>
-      </c>
-      <c r="G8" s="24">
-        <f>SUM(B8:F8)</f>
+        <v>69647</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>47301</v>
+      </c>
+      <c r="H8" s="24">
+        <f>SUM(B8:G8)</f>
         <v/>
       </c>
     </row>
@@ -1712,6 +1725,7 @@
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1734,8 +1748,11 @@
       <c r="F11" s="7" t="n">
         <v>7255</v>
       </c>
-      <c r="G11" s="7">
-        <f>SUM(B11:F11)</f>
+      <c r="G11" s="7" t="n">
+        <v>1565</v>
+      </c>
+      <c r="H11" s="7">
+        <f>SUM(B11:G11)</f>
         <v/>
       </c>
     </row>
@@ -1760,8 +1777,11 @@
       <c r="F12" s="7" t="n">
         <v>1378</v>
       </c>
-      <c r="G12" s="7">
-        <f>SUM(B12:F12)</f>
+      <c r="G12" s="7" t="n">
+        <v>263</v>
+      </c>
+      <c r="H12" s="7">
+        <f>SUM(B12:G12)</f>
         <v/>
       </c>
     </row>
@@ -1786,8 +1806,11 @@
       <c r="F13" s="7" t="n">
         <v>284</v>
       </c>
-      <c r="G13" s="7">
-        <f>SUM(B13:F13)</f>
+      <c r="G13" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="H13" s="7">
+        <f>SUM(B13:G13)</f>
         <v/>
       </c>
     </row>
@@ -1810,10 +1833,13 @@
         <v>7662</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>4517</v>
-      </c>
-      <c r="G14" s="7">
-        <f>SUM(B14:F14)</f>
+        <v>5832</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>318</v>
+      </c>
+      <c r="H14" s="7">
+        <f>SUM(B14:G14)</f>
         <v/>
       </c>
     </row>
@@ -1838,8 +1864,11 @@
       <c r="F15" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="7">
-        <f>SUM(B15:F15)</f>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(B15:G15)</f>
         <v/>
       </c>
     </row>
@@ -1864,8 +1893,11 @@
       <c r="F16" s="7" t="n">
         <v>9620</v>
       </c>
-      <c r="G16" s="7">
-        <f>SUM(B16:F16)</f>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(B16:G16)</f>
         <v/>
       </c>
     </row>
@@ -1890,8 +1922,11 @@
       <c r="F17" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="G17" s="7">
-        <f>SUM(B17:F17)</f>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
+        <f>SUM(B17:G17)</f>
         <v/>
       </c>
     </row>
@@ -1922,7 +1957,11 @@
         <v/>
       </c>
       <c r="G18" s="26">
-        <f>SUM(B18:F18)</f>
+        <f>SUM(G11:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="26">
+        <f>SUM(B18:G18)</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1992,11 @@
         <v/>
       </c>
       <c r="G20" s="28">
-        <f>SUM(B20:F20)</f>
+        <f>G8-G18</f>
+        <v/>
+      </c>
+      <c r="H20" s="28">
+        <f>SUM(B20:G20)</f>
         <v/>
       </c>
     </row>
@@ -1985,6 +2028,10 @@
       </c>
       <c r="G22" s="30">
         <f>IF(ROUND(G8-G18-G20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="H22" s="30">
+        <f>IF(ROUND(H8-H18-H20,0)=0,"OK","ERR")</f>
         <v/>
       </c>
     </row>
@@ -2000,6 +2047,7 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2024,12 +2072,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <conditionalFormatting sqref="B22">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2079,6 +2127,14 @@
       <formula>G22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>H22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="1">
+      <formula>H22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2150,14 +2206,14 @@
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>ACTUAL</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
         <is>
           <t>BOOKED</t>
-        </is>
-      </c>
-      <c r="G4" s="34" t="inlineStr">
-        <is>
-          <t>PROJECTED</t>
         </is>
       </c>
       <c r="H4" s="34" t="inlineStr">
@@ -2278,10 +2334,10 @@
         <v>69</v>
       </c>
       <c r="F6" s="37" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H6" s="37" t="n">
         <v>67</v>
@@ -2290,16 +2346,16 @@
         <v>67</v>
       </c>
       <c r="J6" s="37" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" s="37" t="n">
         <v>54</v>
       </c>
-      <c r="K6" s="37" t="n">
-        <v>53</v>
-      </c>
       <c r="L6" s="37" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M6" s="37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N6" s="38">
         <f>SUM(B6:M6)</f>
@@ -2328,25 +2384,25 @@
         <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>171</v>
       </c>
       <c r="I7" s="39" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J7" s="39" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L7" s="39" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M7" s="39" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N7" s="40">
         <f>SUM(B7:M7)</f>
@@ -2422,25 +2478,25 @@
         <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
-        <v>0.914</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>0.92</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>0.914</v>
+        <v>0.92</v>
       </c>
       <c r="J9" s="41" t="n">
-        <v>0.769</v>
+        <v>0.779</v>
       </c>
       <c r="K9" s="41" t="n">
-        <v>0.726</v>
+        <v>0.736</v>
       </c>
       <c r="L9" s="41" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="M9" s="41" t="n">
-        <v>0.795</v>
+        <v>0.805</v>
       </c>
       <c r="N9" s="42">
         <f>AVERAGE(B9:M9)</f>
@@ -2469,25 +2525,25 @@
         <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="H10" s="43" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I10" s="43" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J10" s="43" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K10" s="43" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L10" s="43" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M10" s="43" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N10" s="44">
         <f>SUM(B10:M10)</f>
@@ -2513,28 +2569,28 @@
         <v>410</v>
       </c>
       <c r="F11" s="45" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>462</v>
+        <v>301</v>
       </c>
       <c r="H11" s="45" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I11" s="45" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="J11" s="45" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="K11" s="45" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L11" s="45" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M11" s="45" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N11" s="46">
         <f>SUM(B11:M11)</f>
@@ -2560,28 +2616,28 @@
         <v>73746</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>79851</v>
+        <v>79700</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>83160</v>
+        <v>54231</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>89775</v>
+        <v>90117</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>85680</v>
+        <v>86526</v>
       </c>
       <c r="J12" s="47" t="n">
-        <v>55062</v>
+        <v>56140</v>
       </c>
       <c r="K12" s="47" t="n">
-        <v>51030</v>
+        <v>52060</v>
       </c>
       <c r="L12" s="47" t="n">
-        <v>51030</v>
+        <v>52060</v>
       </c>
       <c r="M12" s="47" t="n">
-        <v>59052</v>
+        <v>60150</v>
       </c>
       <c r="N12" s="44">
         <f>SUM(B12:M12)</f>
@@ -2607,28 +2663,28 @@
         <v>64778</v>
       </c>
       <c r="F13" s="48" t="n">
-        <v>69703</v>
+        <v>69647</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>73365</v>
+        <v>47301</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79201</v>
+        <v>79564</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>75589</v>
+        <v>76393</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48577</v>
+        <v>49566</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45020</v>
+        <v>45964</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45020</v>
+        <v>45964</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52097</v>
+        <v>53106</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2651,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2674,7 +2730,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-05-26. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-06-01. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2723,23 +2779,23 @@
     <row r="5">
       <c r="A5" s="49" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>79851</v>
+        <v>54231</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>79851</v>
+        <v>54231</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>472</v>
+        <v>537</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>429</v>
+        <v>301</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2751,148 +2807,148 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B6" s="50" t="n">
-        <v>83160</v>
-      </c>
-      <c r="C6" s="51" t="n">
-        <v>50765</v>
-      </c>
-      <c r="D6" s="52" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E6" s="50" t="n">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>90117</v>
+      </c>
+      <c r="C6" s="56" t="n">
+        <v>50295</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>0.5579999999999999</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>592</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>270</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>39822</v>
+      </c>
+      <c r="H6" s="58" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B7" s="59" t="n">
+        <v>86526</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>18520</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="E7" s="59" t="n">
         <v>529</v>
       </c>
-      <c r="F6" s="50" t="n">
-        <v>282</v>
-      </c>
-      <c r="G6" s="50" t="n">
-        <v>32395</v>
-      </c>
-      <c r="H6" s="53" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="54" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B7" s="55" t="n">
-        <v>89775</v>
-      </c>
-      <c r="C7" s="56" t="n">
-        <v>46523</v>
-      </c>
-      <c r="D7" s="57" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>589</v>
-      </c>
-      <c r="F7" s="55" t="n">
-        <v>250</v>
-      </c>
-      <c r="G7" s="55" t="n">
-        <v>43252</v>
-      </c>
-      <c r="H7" s="58" t="inlineStr">
+      <c r="F7" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="59" t="n">
+        <v>68006</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>56140</v>
+      </c>
+      <c r="C8" s="56" t="n">
+        <v>15257</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>424</v>
+      </c>
+      <c r="F8" s="55" t="n">
+        <v>85</v>
+      </c>
+      <c r="G8" s="55" t="n">
+        <v>40883</v>
+      </c>
+      <c r="H8" s="58" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B8" s="59" t="n">
-        <v>85680</v>
-      </c>
-      <c r="C8" s="46" t="n">
-        <v>17062</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="E8" s="59" t="n">
-        <v>550</v>
-      </c>
-      <c r="F8" s="59" t="n">
-        <v>92</v>
-      </c>
-      <c r="G8" s="59" t="n">
-        <v>68618</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B9" s="59" t="n">
+        <v>52060</v>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>8885</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="E9" s="59" t="n">
+        <v>444</v>
+      </c>
+      <c r="F9" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G9" s="59" t="n">
+        <v>43175</v>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="54" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B9" s="55" t="n">
-        <v>55062</v>
-      </c>
-      <c r="C9" s="56" t="n">
-        <v>15257</v>
-      </c>
-      <c r="D9" s="57" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="E9" s="55" t="n">
-        <v>424</v>
-      </c>
-      <c r="F9" s="55" t="n">
-        <v>85</v>
-      </c>
-      <c r="G9" s="55" t="n">
-        <v>39805</v>
-      </c>
-      <c r="H9" s="58" t="inlineStr">
-        <is>
-          <t>Building</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="B10" s="59" t="n">
-        <v>51030</v>
+        <v>52060</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>8176</v>
+        <v>3104</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="E10" s="59" t="n">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F10" s="59" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="G10" s="59" t="n">
-        <v>42854</v>
+        <v>48956</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2903,26 +2959,26 @@
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="B11" s="59" t="n">
-        <v>51030</v>
+        <v>60150</v>
       </c>
       <c r="C11" s="46" t="n">
-        <v>3104</v>
+        <v>5822</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0.061</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="E11" s="59" t="n">
-        <v>443</v>
+        <v>342</v>
       </c>
       <c r="F11" s="59" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G11" s="59" t="n">
-        <v>47926</v>
+        <v>54328</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
@@ -2931,60 +2987,30 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B12" s="59" t="n">
-        <v>59052</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>5822</v>
-      </c>
-      <c r="D12" s="42" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="E12" s="59" t="n">
-        <v>342</v>
-      </c>
-      <c r="F12" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="G12" s="59" t="n">
-        <v>53230</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="61">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="61">
-        <f>SUM(C5:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="62">
-        <f>C13/B13</f>
-        <v/>
-      </c>
-      <c r="E13" s="63" t="n"/>
-      <c r="F13" s="63" t="n"/>
-      <c r="G13" s="61">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="H13" s="63" t="n"/>
+      <c r="B12" s="61">
+        <f>SUM(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="61">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="62">
+        <f>C12/B12</f>
+        <v/>
+      </c>
+      <c r="E12" s="63" t="n"/>
+      <c r="F12" s="63" t="n"/>
+      <c r="G12" s="61">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="H12" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3020,7 +3046,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Blends 4 months of closed actuals with seasonal projections calibrated from actual performance</t>
+          <t>Blends 5 months of closed actuals with seasonal projections calibrated from actual performance</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3070,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>790516</v>
+        <v>766860</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3057,7 +3083,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-85922</v>
+        <v>-83441</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3071,7 +3097,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5323</v>
+        <v>-5215</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3109,7 +3135,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-80633</v>
+        <v>-74377</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3123,7 +3149,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-122534</v>
+        <v>-121275</v>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3233,7 +3259,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>352873</v>
+        <v>341687</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3325,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76680</v>
+        <v>74385</v>
       </c>
     </row>
     <row r="31">
@@ -3343,7 +3369,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -3353,7 +3379,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="38">
@@ -3363,7 +3389,7 @@
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.855</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="39">
@@ -3383,7 +3409,7 @@
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>0.168</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="42">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-06-01</t>
+          <t>Prepared 2026-06-06</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>766860</v>
+        <v>771952</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>678204</v>
+        <v>683142</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>336517</v>
+        <v>337234</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>341687</v>
+        <v>345908</v>
       </c>
     </row>
     <row r="19">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.4% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>341687</v>
+        <v>345908</v>
       </c>
     </row>
     <row r="42">
@@ -1677,7 +1677,7 @@
         <v>79700</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>54231</v>
+        <v>59323</v>
       </c>
       <c r="H7" s="9">
         <f>SUM(B7:G7)</f>
@@ -1703,10 +1703,10 @@
         <v>64778</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>69647</v>
+        <v>69654</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>47301</v>
+        <v>51991</v>
       </c>
       <c r="H8" s="24">
         <f>SUM(B8:G8)</f>
@@ -2337,13 +2337,13 @@
         <v>77</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>55</v>
@@ -2384,7 +2384,7 @@
         <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>171</v>
@@ -2478,7 +2478,7 @@
         <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>0.92</v>
@@ -2525,7 +2525,7 @@
         <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="H10" s="43" t="n">
         <v>527</v>
@@ -2572,7 +2572,7 @@
         <v>428</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="H11" s="45" t="n">
         <v>484</v>
@@ -2619,7 +2619,7 @@
         <v>79700</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>54231</v>
+        <v>59323</v>
       </c>
       <c r="H12" s="47" t="n">
         <v>90117</v>
@@ -2663,28 +2663,28 @@
         <v>64778</v>
       </c>
       <c r="F13" s="48" t="n">
-        <v>69647</v>
+        <v>69654</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>47301</v>
+        <v>51991</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79564</v>
+        <v>79619</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>76393</v>
+        <v>76446</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49566</v>
+        <v>49600</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45964</v>
+        <v>45995</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45964</v>
+        <v>45995</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53106</v>
+        <v>53143</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2730,7 +2730,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-06-01. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-06-06. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2783,19 +2783,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>54231</v>
+        <v>59323</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>54231</v>
+        <v>59323</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2807,62 +2807,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="50" t="n">
         <v>90117</v>
       </c>
-      <c r="C6" s="56" t="n">
-        <v>50295</v>
-      </c>
-      <c r="D6" s="57" t="n">
-        <v>0.5579999999999999</v>
-      </c>
-      <c r="E6" s="55" t="n">
-        <v>592</v>
-      </c>
-      <c r="F6" s="55" t="n">
-        <v>270</v>
-      </c>
-      <c r="G6" s="55" t="n">
-        <v>39822</v>
-      </c>
-      <c r="H6" s="58" t="inlineStr">
+      <c r="C6" s="51" t="n">
+        <v>58248</v>
+      </c>
+      <c r="D6" s="52" t="n">
+        <v>0.6459999999999999</v>
+      </c>
+      <c r="E6" s="50" t="n">
+        <v>640</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>313</v>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>31869</v>
+      </c>
+      <c r="H6" s="53" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>86526</v>
+      </c>
+      <c r="C7" s="56" t="n">
+        <v>22376</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>546</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>120</v>
+      </c>
+      <c r="G7" s="55" t="n">
+        <v>64150</v>
+      </c>
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>Building</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B7" s="59" t="n">
-        <v>86526</v>
-      </c>
-      <c r="C7" s="46" t="n">
-        <v>18520</v>
-      </c>
-      <c r="D7" s="42" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="E7" s="59" t="n">
-        <v>529</v>
-      </c>
-      <c r="F7" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" s="59" t="n">
-        <v>68006</v>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
         </is>
       </c>
     </row>
@@ -2906,19 +2906,19 @@
         <v>52060</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>8885</v>
+        <v>8517</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0.171</v>
+        <v>0.164</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>43175</v>
+        <v>43543</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2936,19 +2936,19 @@
         <v>52060</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>3104</v>
+        <v>4267</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0.06</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E10" s="59" t="n">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="F10" s="59" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G10" s="59" t="n">
-        <v>48956</v>
+        <v>47793</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>766860</v>
+        <v>771952</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-83441</v>
+        <v>-83542</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5215</v>
+        <v>-5268</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-74377</v>
+        <v>-74585</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>341687</v>
+        <v>345908</v>
       </c>
     </row>
     <row r="23">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>74385</v>
+        <v>74879</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-06-06</t>
+          <t>Prepared 2026-06-12</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>176</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>771952</v>
+        <v>786051</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>683142</v>
+        <v>695039</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>337234</v>
+        <v>353242</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>345908</v>
+        <v>341797</v>
       </c>
     </row>
     <row r="19">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.4% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>345908</v>
+        <v>341797</v>
       </c>
     </row>
     <row r="42">
@@ -1677,7 +1677,7 @@
         <v>79700</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>59323</v>
+        <v>73422</v>
       </c>
       <c r="H7" s="9">
         <f>SUM(B7:G7)</f>
@@ -1706,7 +1706,7 @@
         <v>69654</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>51991</v>
+        <v>64270</v>
       </c>
       <c r="H8" s="24">
         <f>SUM(B8:G8)</f>
@@ -1749,7 +1749,7 @@
         <v>7255</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1565</v>
+        <v>3285</v>
       </c>
       <c r="H11" s="7">
         <f>SUM(B11:G11)</f>
@@ -1778,7 +1778,7 @@
         <v>1378</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>263</v>
+        <v>2724</v>
       </c>
       <c r="H12" s="7">
         <f>SUM(B12:G12)</f>
@@ -1836,7 +1836,7 @@
         <v>5832</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>318</v>
+        <v>2946</v>
       </c>
       <c r="H14" s="7">
         <f>SUM(B14:G14)</f>
@@ -1865,7 +1865,7 @@
         <v>60</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H15" s="7">
         <f>SUM(B15:G15)</f>
@@ -1894,7 +1894,7 @@
         <v>9620</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>9858</v>
       </c>
       <c r="H16" s="7">
         <f>SUM(B16:G16)</f>
@@ -1923,7 +1923,7 @@
         <v>124</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(B17:G17)</f>
@@ -2337,13 +2337,13 @@
         <v>77</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>55</v>
@@ -2384,7 +2384,7 @@
         <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>171</v>
@@ -2478,7 +2478,7 @@
         <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
-        <v>0.633</v>
+        <v>0.7390000000000001</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>0.92</v>
@@ -2525,7 +2525,7 @@
         <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="H10" s="43" t="n">
         <v>527</v>
@@ -2572,7 +2572,7 @@
         <v>428</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>330</v>
+        <v>408</v>
       </c>
       <c r="H11" s="45" t="n">
         <v>484</v>
@@ -2619,7 +2619,7 @@
         <v>79700</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>59323</v>
+        <v>73422</v>
       </c>
       <c r="H12" s="47" t="n">
         <v>90117</v>
@@ -2666,25 +2666,25 @@
         <v>69654</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>51991</v>
+        <v>64270</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79619</v>
+        <v>79532</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>76446</v>
+        <v>76363</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49600</v>
+        <v>49546</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45995</v>
+        <v>45945</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45995</v>
+        <v>45945</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53143</v>
+        <v>53085</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2730,7 +2730,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-06-06. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-06-12. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2783,19 +2783,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>59323</v>
+        <v>73422</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>59323</v>
+        <v>73422</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>330</v>
+        <v>408</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2816,19 +2816,19 @@
         <v>90117</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>58248</v>
+        <v>67956</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.754</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>31869</v>
+        <v>22161</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
@@ -2846,19 +2846,19 @@
         <v>86526</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>22376</v>
+        <v>30639</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.259</v>
+        <v>0.354</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>64150</v>
+        <v>55887</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2906,19 +2906,19 @@
         <v>52060</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>8517</v>
+        <v>5147</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0.164</v>
+        <v>0.099</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>448</v>
+        <v>396</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>43543</v>
+        <v>46913</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2936,19 +2936,19 @@
         <v>52060</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>4267</v>
+        <v>5590</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="E10" s="59" t="n">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="F10" s="59" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G10" s="59" t="n">
-        <v>47793</v>
+        <v>46470</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>771952</v>
+        <v>786051</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-83542</v>
+        <v>-85658</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5268</v>
+        <v>-5354</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-74585</v>
+        <v>-76097</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-121275</v>
+        <v>-134361</v>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>345908</v>
+        <v>341797</v>
       </c>
     </row>
     <row r="23">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>74879</v>
+        <v>76247</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Jan 1 – Apr 14, 2026</t>
+          <t>Jan 1 – May 31, 2026</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>170225.3</v>
+        <v>273154.41</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>89337.99000000001</v>
+        <v>129044.74</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>80887.31</v>
+        <v>144109.67</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -972,14 +972,14 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>•  Occupancy trending from 75% (Jan) to 88% (Mar) - strong ramp trajectory</t>
+          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - May) - strong operating performance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  April booked at $73,746 gross - highest month to date</t>
+          <t>•  Best month to date: May at $79,700 gross</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>•  QBO YTD NOI of $80,887 in first 3.5 months of operations</t>
+          <t>•  QBO YTD NOI of $144,110 through May 31 (5 months of operations)</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1579,7 +1579,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1592,7 +1591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating data: January – Jun 2026  |  QBO YTD cross-referenced</t>
+          <t>Operating data: January – May 2026  |  QBO YTD cross-referenced</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1630,6 @@
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -1653,7 +1647,6 @@
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="22" t="n"/>
       <c r="G6" s="22" t="n"/>
-      <c r="H6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1676,11 +1669,8 @@
       <c r="F7" s="9" t="n">
         <v>79700</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>73422</v>
-      </c>
-      <c r="H7" s="9">
-        <f>SUM(B7:G7)</f>
+      <c r="G7" s="9">
+        <f>SUM(B7:F7)</f>
         <v/>
       </c>
     </row>
@@ -1705,11 +1695,8 @@
       <c r="F8" s="24" t="n">
         <v>69654</v>
       </c>
-      <c r="G8" s="24" t="n">
-        <v>64270</v>
-      </c>
-      <c r="H8" s="24">
-        <f>SUM(B8:G8)</f>
+      <c r="G8" s="24">
+        <f>SUM(B8:F8)</f>
         <v/>
       </c>
     </row>
@@ -1725,7 +1712,6 @@
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1748,11 +1734,8 @@
       <c r="F11" s="7" t="n">
         <v>7255</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>3285</v>
-      </c>
-      <c r="H11" s="7">
-        <f>SUM(B11:G11)</f>
+      <c r="G11" s="7">
+        <f>SUM(B11:F11)</f>
         <v/>
       </c>
     </row>
@@ -1777,11 +1760,8 @@
       <c r="F12" s="7" t="n">
         <v>1378</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>2724</v>
-      </c>
-      <c r="H12" s="7">
-        <f>SUM(B12:G12)</f>
+      <c r="G12" s="7">
+        <f>SUM(B12:F12)</f>
         <v/>
       </c>
     </row>
@@ -1806,11 +1786,8 @@
       <c r="F13" s="7" t="n">
         <v>284</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>270</v>
-      </c>
-      <c r="H13" s="7">
-        <f>SUM(B13:G13)</f>
+      <c r="G13" s="7">
+        <f>SUM(B13:F13)</f>
         <v/>
       </c>
     </row>
@@ -1835,11 +1812,8 @@
       <c r="F14" s="7" t="n">
         <v>5832</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>2946</v>
-      </c>
-      <c r="H14" s="7">
-        <f>SUM(B14:G14)</f>
+      <c r="G14" s="7">
+        <f>SUM(B14:F14)</f>
         <v/>
       </c>
     </row>
@@ -1864,11 +1838,8 @@
       <c r="F15" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(B15:G15)</f>
+      <c r="G15" s="7">
+        <f>SUM(B15:F15)</f>
         <v/>
       </c>
     </row>
@@ -1893,11 +1864,8 @@
       <c r="F16" s="7" t="n">
         <v>9620</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>9858</v>
-      </c>
-      <c r="H16" s="7">
-        <f>SUM(B16:G16)</f>
+      <c r="G16" s="7">
+        <f>SUM(B16:F16)</f>
         <v/>
       </c>
     </row>
@@ -1922,11 +1890,8 @@
       <c r="F17" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>429</v>
-      </c>
-      <c r="H17" s="7">
-        <f>SUM(B17:G17)</f>
+      <c r="G17" s="7">
+        <f>SUM(B17:F17)</f>
         <v/>
       </c>
     </row>
@@ -1957,11 +1922,7 @@
         <v/>
       </c>
       <c r="G18" s="26">
-        <f>SUM(G11:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
-        <f>SUM(B18:G18)</f>
+        <f>SUM(B18:F18)</f>
         <v/>
       </c>
     </row>
@@ -1992,11 +1953,7 @@
         <v/>
       </c>
       <c r="G20" s="28">
-        <f>G8-G18</f>
-        <v/>
-      </c>
-      <c r="H20" s="28">
-        <f>SUM(B20:G20)</f>
+        <f>SUM(B20:F20)</f>
         <v/>
       </c>
     </row>
@@ -2028,10 +1985,6 @@
       </c>
       <c r="G22" s="30">
         <f>IF(ROUND(G8-G18-G20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="H22" s="30">
-        <f>IF(ROUND(H8-H18-H20,0)=0,"OK","ERR")</f>
         <v/>
       </c>
     </row>
@@ -2047,19 +2000,18 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Rental Income (Jan 1 – Apr 14): $170,225</t>
+          <t>QBO YTD Rental Income (Jan 1 – May 31): $273,154</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Total Expenses: $89,338  |  QBO YTD NOI: $80,887</t>
+          <t>QBO YTD Total Expenses: $129,045  |  QBO YTD NOI: $144,110</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2024,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="B22">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2127,14 +2079,6 @@
       <formula>G22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="expression" priority="13" dxfId="0">
-      <formula>H22="OK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="1">
-      <formula>H22="ERR"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-06-12</t>
+          <t>Prepared 2026-06-19</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>786051</v>
+        <v>788540</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>695039</v>
+        <v>697653</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>353242</v>
+        <v>353491</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>341797</v>
+        <v>344162</v>
       </c>
     </row>
     <row r="19">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.821</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="22">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>341797</v>
+        <v>344162</v>
       </c>
     </row>
     <row r="42">
@@ -2281,7 +2281,7 @@
         <v>77</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H6" s="37" t="n">
         <v>67</v>
@@ -2328,7 +2328,7 @@
         <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>171</v>
@@ -2422,7 +2422,7 @@
         <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
-        <v>0.7390000000000001</v>
+        <v>0.7609999999999999</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>0.92</v>
@@ -2469,7 +2469,7 @@
         <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H10" s="43" t="n">
         <v>527</v>
@@ -2516,7 +2516,7 @@
         <v>428</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="H11" s="45" t="n">
         <v>484</v>
@@ -2563,7 +2563,7 @@
         <v>79700</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>73422</v>
+        <v>75911</v>
       </c>
       <c r="H12" s="47" t="n">
         <v>90117</v>
@@ -2610,25 +2610,25 @@
         <v>69654</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>64270</v>
+        <v>66563</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79532</v>
+        <v>79605</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>76363</v>
+        <v>76433</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49546</v>
+        <v>49591</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45945</v>
+        <v>45987</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45945</v>
+        <v>45987</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53085</v>
+        <v>53134</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2674,7 +2674,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-06-12. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-06-19. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>73422</v>
+        <v>75911</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>73422</v>
+        <v>75911</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>90117</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>67956</v>
+        <v>72150</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.754</v>
+        <v>0.8009999999999999</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>22161</v>
+        <v>17967</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
@@ -2790,19 +2790,19 @@
         <v>86526</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>30639</v>
+        <v>32209</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.354</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>557</v>
+        <v>586</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>55887</v>
+        <v>54317</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2820,19 +2820,19 @@
         <v>56140</v>
       </c>
       <c r="C8" s="56" t="n">
-        <v>15257</v>
+        <v>16628</v>
       </c>
       <c r="D8" s="57" t="n">
-        <v>0.272</v>
+        <v>0.296</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F8" s="55" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G8" s="55" t="n">
-        <v>40883</v>
+        <v>39512</v>
       </c>
       <c r="H8" s="58" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>786051</v>
+        <v>788540</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-85658</v>
+        <v>-85495</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5354</v>
+        <v>-5392</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>341797</v>
+        <v>344162</v>
       </c>
     </row>
     <row r="23">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76247</v>
+        <v>76488</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-06-19</t>
+          <t>Prepared 2026-06-23</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>788540</v>
+        <v>786509</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>697653</v>
+        <v>695948</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>353491</v>
+        <v>353288</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>344162</v>
+        <v>342660</v>
       </c>
     </row>
     <row r="19">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.823</v>
+        <v>0.8220000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>344162</v>
+        <v>342660</v>
       </c>
     </row>
     <row r="42">
@@ -2281,7 +2281,7 @@
         <v>77</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" s="37" t="n">
         <v>67</v>
@@ -2328,7 +2328,7 @@
         <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>171</v>
@@ -2422,7 +2422,7 @@
         <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
-        <v>0.7609999999999999</v>
+        <v>0.7440000000000001</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>0.92</v>
@@ -2469,7 +2469,7 @@
         <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H10" s="43" t="n">
         <v>527</v>
@@ -2516,7 +2516,7 @@
         <v>428</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="H11" s="45" t="n">
         <v>484</v>
@@ -2563,7 +2563,7 @@
         <v>79700</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>75911</v>
+        <v>73880</v>
       </c>
       <c r="H12" s="47" t="n">
         <v>90117</v>
@@ -2610,25 +2610,25 @@
         <v>69654</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>66563</v>
+        <v>64898</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79605</v>
+        <v>79596</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>76433</v>
+        <v>76424</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49591</v>
+        <v>49586</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45987</v>
+        <v>45982</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45987</v>
+        <v>45982</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53134</v>
+        <v>53127</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2674,7 +2674,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-06-19. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-06-23. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>75911</v>
+        <v>73880</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>75911</v>
+        <v>73880</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>90117</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>72150</v>
+        <v>82492</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.8009999999999999</v>
+        <v>0.915</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>388</v>
+        <v>444</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>17967</v>
+        <v>7625</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
@@ -2790,19 +2790,19 @@
         <v>86526</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>32209</v>
+        <v>33579</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.388</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>54317</v>
+        <v>52947</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>788540</v>
+        <v>786509</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-85495</v>
+        <v>-85234</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5392</v>
+        <v>-5327</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>344162</v>
+        <v>342660</v>
       </c>
     </row>
     <row r="23">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76488</v>
+        <v>76291</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-06-23</t>
+          <t>Prepared 2026-06-30</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>786509</v>
+        <v>789675</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>695948</v>
+        <v>697366</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>353288</v>
+        <v>359906</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>342660</v>
+        <v>337460</v>
       </c>
     </row>
     <row r="19">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8220000000000001</v>
+        <v>0.8240000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.3% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>342660</v>
+        <v>337460</v>
       </c>
     </row>
     <row r="42">
@@ -2281,13 +2281,13 @@
         <v>77</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>55</v>
@@ -2328,7 +2328,7 @@
         <v>169</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>171</v>
@@ -2422,7 +2422,7 @@
         <v>0.909</v>
       </c>
       <c r="G9" s="41" t="n">
-        <v>0.7440000000000001</v>
+        <v>0.778</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>0.92</v>
@@ -2469,7 +2469,7 @@
         <v>472</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H10" s="43" t="n">
         <v>527</v>
@@ -2516,7 +2516,7 @@
         <v>428</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="H11" s="45" t="n">
         <v>484</v>
@@ -2563,7 +2563,7 @@
         <v>79700</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>73880</v>
+        <v>77046</v>
       </c>
       <c r="H12" s="47" t="n">
         <v>90117</v>
@@ -2610,25 +2610,25 @@
         <v>69654</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>64898</v>
+        <v>66938</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>79596</v>
+        <v>79455</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>76424</v>
+        <v>76289</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49586</v>
+        <v>49498</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45982</v>
+        <v>45900</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45982</v>
+        <v>45900</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53127</v>
+        <v>53033</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2674,7 +2674,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-06-23. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-06-30. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>73880</v>
+        <v>77046</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>73880</v>
+        <v>77046</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2760,23 +2760,23 @@
         <v>90117</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>82492</v>
+        <v>86728</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.915</v>
+        <v>0.9620000000000001</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>7625</v>
+        <v>3389</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Fully Booked</t>
         </is>
       </c>
     </row>
@@ -2790,19 +2790,19 @@
         <v>86526</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>33579</v>
+        <v>37411</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.388</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>52947</v>
+        <v>49115</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2820,19 +2820,19 @@
         <v>56140</v>
       </c>
       <c r="C8" s="56" t="n">
-        <v>16628</v>
+        <v>21175</v>
       </c>
       <c r="D8" s="57" t="n">
-        <v>0.296</v>
+        <v>0.377</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="F8" s="55" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="G8" s="55" t="n">
-        <v>39512</v>
+        <v>34965</v>
       </c>
       <c r="H8" s="58" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>786509</v>
+        <v>789675</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-85234</v>
+        <v>-86833</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5327</v>
+        <v>-5476</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-76097</v>
+        <v>-80960</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-134361</v>
+        <v>-135799</v>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>342660</v>
+        <v>337460</v>
       </c>
     </row>
     <row r="23">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76291</v>
+        <v>76598</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -120,7 +120,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -150,11 +150,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004CAF50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002196F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -248,9 +243,6 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -286,11 +278,11 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -856,7 +848,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>5 months actuals + seasonal model</t>
+          <t>6 months actuals + seasonal model</t>
         </is>
       </c>
     </row>
@@ -875,7 +867,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>789675</v>
+        <v>787475</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +885,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>697366</v>
+        <v>695427</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +903,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>359906</v>
+        <v>364968</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +913,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>337460</v>
+        <v>330459</v>
       </c>
     </row>
     <row r="19">
@@ -931,7 +923,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +933,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +964,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - May) - strong operating performance</t>
+          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - Jun) - strong operating performance</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1379,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>337460</v>
+        <v>330459</v>
       </c>
     </row>
     <row r="42">
@@ -1569,7 +1561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1579,6 +1571,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1591,7 +1584,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating data: January – May 2026  |  QBO YTD cross-referenced</t>
+          <t>Operating data: January – Jun 2026  |  QBO YTD cross-referenced</t>
         </is>
       </c>
     </row>
@@ -1630,6 +1623,11 @@
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -1647,6 +1645,7 @@
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="22" t="n"/>
       <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1669,8 +1668,11 @@
       <c r="F7" s="9" t="n">
         <v>79700</v>
       </c>
-      <c r="G7" s="9">
-        <f>SUM(B7:F7)</f>
+      <c r="G7" s="9" t="n">
+        <v>77046</v>
+      </c>
+      <c r="H7" s="9">
+        <f>SUM(B7:G7)</f>
         <v/>
       </c>
     </row>
@@ -1695,8 +1697,11 @@
       <c r="F8" s="24" t="n">
         <v>69654</v>
       </c>
-      <c r="G8" s="24">
-        <f>SUM(B8:F8)</f>
+      <c r="G8" s="24" t="n">
+        <v>66938</v>
+      </c>
+      <c r="H8" s="24">
+        <f>SUM(B8:G8)</f>
         <v/>
       </c>
     </row>
@@ -1712,6 +1717,7 @@
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1734,8 +1740,11 @@
       <c r="F11" s="7" t="n">
         <v>7255</v>
       </c>
-      <c r="G11" s="7">
-        <f>SUM(B11:F11)</f>
+      <c r="G11" s="7" t="n">
+        <v>7940</v>
+      </c>
+      <c r="H11" s="7">
+        <f>SUM(B11:G11)</f>
         <v/>
       </c>
     </row>
@@ -1760,8 +1769,11 @@
       <c r="F12" s="7" t="n">
         <v>1378</v>
       </c>
-      <c r="G12" s="7">
-        <f>SUM(B12:F12)</f>
+      <c r="G12" s="7" t="n">
+        <v>4189</v>
+      </c>
+      <c r="H12" s="7">
+        <f>SUM(B12:G12)</f>
         <v/>
       </c>
     </row>
@@ -1786,8 +1798,11 @@
       <c r="F13" s="7" t="n">
         <v>284</v>
       </c>
-      <c r="G13" s="7">
-        <f>SUM(B13:F13)</f>
+      <c r="G13" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="H13" s="7">
+        <f>SUM(B13:G13)</f>
         <v/>
       </c>
     </row>
@@ -1812,8 +1827,11 @@
       <c r="F14" s="7" t="n">
         <v>5832</v>
       </c>
-      <c r="G14" s="7">
-        <f>SUM(B14:F14)</f>
+      <c r="G14" s="7" t="n">
+        <v>6718</v>
+      </c>
+      <c r="H14" s="7">
+        <f>SUM(B14:G14)</f>
         <v/>
       </c>
     </row>
@@ -1838,8 +1856,11 @@
       <c r="F15" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="7">
-        <f>SUM(B15:F15)</f>
+      <c r="G15" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(B15:G15)</f>
         <v/>
       </c>
     </row>
@@ -1864,8 +1885,11 @@
       <c r="F16" s="7" t="n">
         <v>9620</v>
       </c>
-      <c r="G16" s="7">
-        <f>SUM(B16:F16)</f>
+      <c r="G16" s="7" t="n">
+        <v>9858</v>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(B16:G16)</f>
         <v/>
       </c>
     </row>
@@ -1890,8 +1914,11 @@
       <c r="F17" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="G17" s="7">
-        <f>SUM(B17:F17)</f>
+      <c r="G17" s="7" t="n">
+        <v>402</v>
+      </c>
+      <c r="H17" s="7">
+        <f>SUM(B17:G17)</f>
         <v/>
       </c>
     </row>
@@ -1922,7 +1949,11 @@
         <v/>
       </c>
       <c r="G18" s="26">
-        <f>SUM(B18:F18)</f>
+        <f>SUM(G11:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="26">
+        <f>SUM(B18:G18)</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1984,11 @@
         <v/>
       </c>
       <c r="G20" s="28">
-        <f>SUM(B20:F20)</f>
+        <f>G8-G18</f>
+        <v/>
+      </c>
+      <c r="H20" s="28">
+        <f>SUM(B20:G20)</f>
         <v/>
       </c>
     </row>
@@ -1985,6 +2020,10 @@
       </c>
       <c r="G22" s="30">
         <f>IF(ROUND(G8-G18-G20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="H22" s="30">
+        <f>IF(ROUND(H8-H18-H20,0)=0,"OK","ERR")</f>
         <v/>
       </c>
     </row>
@@ -2000,6 +2039,7 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2024,12 +2064,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <conditionalFormatting sqref="B22">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2079,6 +2119,14 @@
       <formula>G22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>H22="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="1">
+      <formula>H22="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2155,44 +2203,44 @@
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="G4" s="33" t="inlineStr">
-        <is>
-          <t>BOOKED</t>
-        </is>
-      </c>
-      <c r="H4" s="34" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>ACTUAL</t>
+        </is>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="I4" s="34" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="K4" s="33" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="L4" s="34" t="inlineStr">
+      <c r="L4" s="33" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="33" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr"/>
+      <c r="A5" s="34" t="inlineStr"/>
       <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Jan</t>
@@ -2260,48 +2308,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="36" t="n">
         <v>55</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="F6" s="37" t="n">
+      <c r="F6" s="36" t="n">
         <v>77</v>
       </c>
-      <c r="G6" s="37" t="n">
+      <c r="G6" s="36" t="n">
         <v>61</v>
       </c>
-      <c r="H6" s="37" t="n">
+      <c r="H6" s="36" t="n">
         <v>68</v>
       </c>
-      <c r="I6" s="37" t="n">
-        <v>68</v>
-      </c>
-      <c r="J6" s="37" t="n">
-        <v>55</v>
-      </c>
-      <c r="K6" s="37" t="n">
+      <c r="I6" s="36" t="n">
+        <v>66</v>
+      </c>
+      <c r="J6" s="36" t="n">
         <v>54</v>
       </c>
-      <c r="L6" s="37" t="n">
-        <v>54</v>
-      </c>
-      <c r="M6" s="37" t="n">
-        <v>59</v>
-      </c>
-      <c r="N6" s="38">
+      <c r="K6" s="36" t="n">
+        <v>53</v>
+      </c>
+      <c r="L6" s="36" t="n">
+        <v>53</v>
+      </c>
+      <c r="M6" s="36" t="n">
+        <v>58</v>
+      </c>
+      <c r="N6" s="37">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2312,90 +2360,90 @@
           <t>Nights Sold</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="38" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="38" t="n">
         <v>136</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="38" t="n">
         <v>164</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="38" t="n">
         <v>151</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="38" t="n">
         <v>169</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="38" t="n">
         <v>140</v>
       </c>
-      <c r="H7" s="39" t="n">
+      <c r="H7" s="38" t="n">
         <v>171</v>
       </c>
-      <c r="I7" s="39" t="n">
-        <v>171</v>
-      </c>
-      <c r="J7" s="39" t="n">
-        <v>140</v>
-      </c>
-      <c r="K7" s="39" t="n">
-        <v>137</v>
-      </c>
-      <c r="L7" s="39" t="n">
-        <v>137</v>
-      </c>
-      <c r="M7" s="39" t="n">
-        <v>150</v>
-      </c>
-      <c r="N7" s="40">
+      <c r="I7" s="38" t="n">
+        <v>168</v>
+      </c>
+      <c r="J7" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="K7" s="38" t="n">
+        <v>133</v>
+      </c>
+      <c r="L7" s="38" t="n">
+        <v>133</v>
+      </c>
+      <c r="M7" s="38" t="n">
+        <v>146</v>
+      </c>
+      <c r="N7" s="39">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Available Nights</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="36" t="n">
         <v>168</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="36" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="G8" s="37" t="n">
+      <c r="G8" s="36" t="n">
         <v>180</v>
       </c>
-      <c r="H8" s="37" t="n">
+      <c r="H8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="I8" s="37" t="n">
+      <c r="I8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="J8" s="37" t="n">
+      <c r="J8" s="36" t="n">
         <v>180</v>
       </c>
-      <c r="K8" s="37" t="n">
+      <c r="K8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="L8" s="37" t="n">
+      <c r="L8" s="36" t="n">
         <v>180</v>
       </c>
-      <c r="M8" s="37" t="n">
+      <c r="M8" s="36" t="n">
         <v>186</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="37">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -2406,90 +2454,90 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="40" t="n">
         <v>0.753</v>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="40" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="40" t="n">
         <v>0.882</v>
       </c>
-      <c r="E9" s="41" t="n">
+      <c r="E9" s="40" t="n">
         <v>0.8390000000000001</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="40" t="n">
         <v>0.909</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="40" t="n">
         <v>0.778</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="40" t="n">
         <v>0.92</v>
       </c>
-      <c r="I9" s="41" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J9" s="41" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="K9" s="41" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="L9" s="41" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="M9" s="41" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="N9" s="42">
+      <c r="I9" s="40" t="n">
+        <v>0.9009999999999999</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="L9" s="40" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="M9" s="40" t="n">
+        <v>0.7829999999999999</v>
+      </c>
+      <c r="N9" s="41">
         <f>AVERAGE(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="B10" s="43" t="n">
+      <c r="B10" s="42" t="n">
         <v>286</v>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="42" t="n">
         <v>398</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="42" t="n">
         <v>415</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="42" t="n">
         <v>488</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="42" t="n">
         <v>472</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="42" t="n">
         <v>550</v>
       </c>
-      <c r="H10" s="43" t="n">
-        <v>527</v>
-      </c>
-      <c r="I10" s="43" t="n">
-        <v>506</v>
-      </c>
-      <c r="J10" s="43" t="n">
-        <v>401</v>
-      </c>
-      <c r="K10" s="43" t="n">
-        <v>380</v>
-      </c>
-      <c r="L10" s="43" t="n">
-        <v>380</v>
-      </c>
-      <c r="M10" s="43" t="n">
-        <v>401</v>
-      </c>
-      <c r="N10" s="44">
+      <c r="H10" s="42" t="n">
+        <v>535</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>513</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>407</v>
+      </c>
+      <c r="K10" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="L10" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="M10" s="42" t="n">
+        <v>407</v>
+      </c>
+      <c r="N10" s="43">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -2500,43 +2548,43 @@
           <t>RevPAR</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="44" t="n">
         <v>215</v>
       </c>
-      <c r="C11" s="45" t="n">
+      <c r="C11" s="44" t="n">
         <v>322</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="44" t="n">
         <v>366</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="44" t="n">
         <v>410</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="44" t="n">
         <v>428</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="44" t="n">
         <v>428</v>
       </c>
-      <c r="H11" s="45" t="n">
-        <v>484</v>
-      </c>
-      <c r="I11" s="45" t="n">
-        <v>465</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>312</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>280</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>289</v>
-      </c>
-      <c r="M11" s="45" t="n">
-        <v>323</v>
-      </c>
-      <c r="N11" s="46">
+      <c r="H11" s="44" t="n">
+        <v>492</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>463</v>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>308</v>
+      </c>
+      <c r="K11" s="44" t="n">
+        <v>275</v>
+      </c>
+      <c r="L11" s="44" t="n">
+        <v>284</v>
+      </c>
+      <c r="M11" s="44" t="n">
+        <v>319</v>
+      </c>
+      <c r="N11" s="45">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -2547,43 +2595,43 @@
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="46" t="n">
         <v>40041</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="46" t="n">
         <v>54065</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="46" t="n">
         <v>68024</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="46" t="n">
         <v>73746</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="46" t="n">
         <v>79700</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="46" t="n">
         <v>77046</v>
       </c>
-      <c r="H12" s="47" t="n">
-        <v>90117</v>
-      </c>
-      <c r="I12" s="47" t="n">
-        <v>86526</v>
-      </c>
-      <c r="J12" s="47" t="n">
-        <v>56140</v>
-      </c>
-      <c r="K12" s="47" t="n">
-        <v>52060</v>
-      </c>
-      <c r="L12" s="47" t="n">
-        <v>52060</v>
-      </c>
-      <c r="M12" s="47" t="n">
-        <v>60150</v>
-      </c>
-      <c r="N12" s="44">
+      <c r="H12" s="46" t="n">
+        <v>91485</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>86184</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>55352</v>
+      </c>
+      <c r="K12" s="46" t="n">
+        <v>51205</v>
+      </c>
+      <c r="L12" s="46" t="n">
+        <v>51205</v>
+      </c>
+      <c r="M12" s="46" t="n">
+        <v>59422</v>
+      </c>
+      <c r="N12" s="43">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -2594,43 +2642,43 @@
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="47" t="n">
         <v>35785</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="47" t="n">
         <v>48880</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="47" t="n">
         <v>61256</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="47" t="n">
         <v>64778</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="47" t="n">
         <v>69654</v>
       </c>
-      <c r="G13" s="48" t="n">
+      <c r="G13" s="47" t="n">
         <v>66938</v>
       </c>
-      <c r="H13" s="48" t="n">
-        <v>79455</v>
-      </c>
-      <c r="I13" s="48" t="n">
-        <v>76289</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <v>49498</v>
-      </c>
-      <c r="K13" s="48" t="n">
-        <v>45900</v>
-      </c>
-      <c r="L13" s="48" t="n">
-        <v>45900</v>
-      </c>
-      <c r="M13" s="48" t="n">
-        <v>53033</v>
-      </c>
-      <c r="N13" s="46">
+      <c r="H13" s="47" t="n">
+        <v>80661</v>
+      </c>
+      <c r="I13" s="47" t="n">
+        <v>75987</v>
+      </c>
+      <c r="J13" s="47" t="n">
+        <v>48803</v>
+      </c>
+      <c r="K13" s="47" t="n">
+        <v>45147</v>
+      </c>
+      <c r="L13" s="47" t="n">
+        <v>45147</v>
+      </c>
+      <c r="M13" s="47" t="n">
+        <v>52391</v>
+      </c>
+      <c r="N13" s="45">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -2651,7 +2699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2721,148 +2769,148 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B5" s="50" t="n">
-        <v>77046</v>
-      </c>
-      <c r="C5" s="51" t="n">
-        <v>77046</v>
-      </c>
-      <c r="D5" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="50" t="n">
-        <v>550</v>
-      </c>
-      <c r="F5" s="50" t="n">
-        <v>428</v>
-      </c>
-      <c r="G5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="53" t="inlineStr">
-        <is>
-          <t>Fully Booked</t>
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="n">
+        <v>91485</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>86728</v>
+      </c>
+      <c r="D5" s="51" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="E5" s="49" t="n">
+        <v>657</v>
+      </c>
+      <c r="F5" s="49" t="n">
+        <v>466</v>
+      </c>
+      <c r="G5" s="49" t="n">
+        <v>4757</v>
+      </c>
+      <c r="H5" s="52" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B6" s="50" t="n">
-        <v>90117</v>
-      </c>
-      <c r="C6" s="51" t="n">
-        <v>86728</v>
-      </c>
-      <c r="D6" s="52" t="n">
-        <v>0.9620000000000001</v>
-      </c>
-      <c r="E6" s="50" t="n">
-        <v>657</v>
-      </c>
-      <c r="F6" s="50" t="n">
-        <v>466</v>
-      </c>
-      <c r="G6" s="50" t="n">
-        <v>3389</v>
-      </c>
-      <c r="H6" s="53" t="inlineStr">
-        <is>
-          <t>Fully Booked</t>
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>86184</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>37411</v>
+      </c>
+      <c r="D6" s="56" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="E6" s="54" t="n">
+        <v>576</v>
+      </c>
+      <c r="F6" s="54" t="n">
+        <v>201</v>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>48773</v>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>Building</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="54" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B7" s="55" t="n">
-        <v>86526</v>
-      </c>
-      <c r="C7" s="56" t="n">
-        <v>37411</v>
-      </c>
-      <c r="D7" s="57" t="n">
-        <v>0.4320000000000001</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>576</v>
-      </c>
-      <c r="F7" s="55" t="n">
-        <v>201</v>
-      </c>
-      <c r="G7" s="55" t="n">
-        <v>49115</v>
-      </c>
-      <c r="H7" s="58" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="n">
+        <v>55352</v>
+      </c>
+      <c r="C7" s="55" t="n">
+        <v>21175</v>
+      </c>
+      <c r="D7" s="56" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="E7" s="54" t="n">
+        <v>471</v>
+      </c>
+      <c r="F7" s="54" t="n">
+        <v>118</v>
+      </c>
+      <c r="G7" s="54" t="n">
+        <v>34177</v>
+      </c>
+      <c r="H7" s="57" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B8" s="55" t="n">
-        <v>56140</v>
-      </c>
-      <c r="C8" s="56" t="n">
-        <v>21175</v>
-      </c>
-      <c r="D8" s="57" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="E8" s="55" t="n">
-        <v>471</v>
-      </c>
-      <c r="F8" s="55" t="n">
-        <v>118</v>
-      </c>
-      <c r="G8" s="55" t="n">
-        <v>34965</v>
-      </c>
-      <c r="H8" s="58" t="inlineStr">
-        <is>
-          <t>Building</t>
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="n">
+        <v>51205</v>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>5147</v>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="E8" s="58" t="n">
+        <v>396</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <v>46058</v>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B9" s="59" t="n">
-        <v>52060</v>
-      </c>
-      <c r="C9" s="46" t="n">
-        <v>5147</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="E9" s="59" t="n">
-        <v>396</v>
-      </c>
-      <c r="F9" s="59" t="n">
-        <v>28</v>
-      </c>
-      <c r="G9" s="59" t="n">
-        <v>46913</v>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="n">
+        <v>51205</v>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>5590</v>
+      </c>
+      <c r="D9" s="41" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="E9" s="58" t="n">
+        <v>508</v>
+      </c>
+      <c r="F9" s="58" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" s="58" t="n">
+        <v>45615</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2873,26 +2921,26 @@
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B10" s="59" t="n">
-        <v>52060</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>5590</v>
-      </c>
-      <c r="D10" s="42" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="E10" s="59" t="n">
-        <v>508</v>
-      </c>
-      <c r="F10" s="59" t="n">
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="n">
+        <v>59422</v>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>5822</v>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E10" s="58" t="n">
+        <v>342</v>
+      </c>
+      <c r="F10" s="58" t="n">
         <v>31</v>
       </c>
-      <c r="G10" s="59" t="n">
-        <v>46470</v>
+      <c r="G10" s="58" t="n">
+        <v>53600</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2901,60 +2949,30 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B11" s="59" t="n">
-        <v>60150</v>
-      </c>
-      <c r="C11" s="46" t="n">
-        <v>5822</v>
-      </c>
-      <c r="D11" s="42" t="n">
-        <v>0.09699999999999999</v>
-      </c>
-      <c r="E11" s="59" t="n">
-        <v>342</v>
-      </c>
-      <c r="F11" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="G11" s="59" t="n">
-        <v>54328</v>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="61">
-        <f>SUM(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="61">
-        <f>SUM(C5:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="62">
-        <f>C12/B12</f>
-        <v/>
-      </c>
-      <c r="E12" s="63" t="n"/>
-      <c r="F12" s="63" t="n"/>
-      <c r="G12" s="61">
-        <f>B12-C12</f>
-        <v/>
-      </c>
-      <c r="H12" s="63" t="n"/>
+      <c r="B11" s="60">
+        <f>SUM(B5:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="60">
+        <f>SUM(C5:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="61">
+        <f>C11/B11</f>
+        <v/>
+      </c>
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="62" t="n"/>
+      <c r="G11" s="60">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="H11" s="62" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2990,7 +3008,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Blends 5 months of closed actuals with seasonal projections calibrated from actual performance</t>
+          <t>Blends 6 months of closed actuals with seasonal projections calibrated from actual performance</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3032,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>789675</v>
+        <v>787475</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3027,7 +3045,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-86833</v>
+        <v>-86588</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3041,7 +3059,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5476</v>
+        <v>-5460</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3058,13 +3076,13 @@
         <f>B5+B6+B7</f>
         <v/>
       </c>
-      <c r="C8" s="64">
+      <c r="C8" s="63">
         <f>B8/B5</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
@@ -3079,9 +3097,9 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-80960</v>
-      </c>
-      <c r="C11" s="66">
+        <v>-82132</v>
+      </c>
+      <c r="C11" s="65">
         <f>B11/B5</f>
         <v/>
       </c>
@@ -3093,9 +3111,9 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-135799</v>
-      </c>
-      <c r="C12" s="66">
+        <v>-139909</v>
+      </c>
+      <c r="C12" s="65">
         <f>B12/B5</f>
         <v/>
       </c>
@@ -3110,7 +3128,7 @@
         <f>-0.10*B5</f>
         <v/>
       </c>
-      <c r="C13" s="66">
+      <c r="C13" s="65">
         <f>B13/B5</f>
         <v/>
       </c>
@@ -3124,7 +3142,7 @@
       <c r="B14" s="7" t="n">
         <v>-26679</v>
       </c>
-      <c r="C14" s="66">
+      <c r="C14" s="65">
         <f>B14/B5</f>
         <v/>
       </c>
@@ -3138,7 +3156,7 @@
       <c r="B15" s="7" t="n">
         <v>-13500</v>
       </c>
-      <c r="C15" s="66">
+      <c r="C15" s="65">
         <f>B15/B5</f>
         <v/>
       </c>
@@ -3152,22 +3170,22 @@
       <c r="B16" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="C16" s="66">
+      <c r="C16" s="65">
         <f>B16/B5</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B17" s="68">
+      <c r="B17" s="67">
         <f>SUM(B11:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="69">
+      <c r="C17" s="68">
         <f>B17/B5</f>
         <v/>
       </c>
@@ -3182,7 +3200,7 @@
         <f>B8+B17</f>
         <v/>
       </c>
-      <c r="C19" s="70">
+      <c r="C19" s="69">
         <f>B19/B5</f>
         <v/>
       </c>
@@ -3202,8 +3220,8 @@
           <t>Expected NOI (from model)</t>
         </is>
       </c>
-      <c r="B22" s="59" t="n">
-        <v>337460</v>
+      <c r="B22" s="58" t="n">
+        <v>330459</v>
       </c>
     </row>
     <row r="23">
@@ -3212,7 +3230,7 @@
           <t>Calculated NOI (this tab)</t>
         </is>
       </c>
-      <c r="B23" s="59">
+      <c r="B23" s="58">
         <f>B19</f>
         <v/>
       </c>
@@ -3223,7 +3241,7 @@
           <t>Variance</t>
         </is>
       </c>
-      <c r="B24" s="59">
+      <c r="B24" s="58">
         <f>B23-B22</f>
         <v/>
       </c>
@@ -3269,7 +3287,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76598</v>
+        <v>76385</v>
       </c>
     </row>
     <row r="31">
@@ -3285,7 +3303,7 @@
           <t>Cleaning fees collected from guests</t>
         </is>
       </c>
-      <c r="B32" s="71" t="inlineStr">
+      <c r="B32" s="70" t="inlineStr">
         <is>
           <t>see Cleaning expense</t>
         </is>
@@ -3313,7 +3331,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -3323,7 +3341,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38">
@@ -3333,7 +3351,7 @@
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.866</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3353,7 +3371,7 @@
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>0.156</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="42">
@@ -3366,7 +3384,7 @@
       <c r="C42" s="5" t="n"/>
     </row>
     <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="72" t="inlineStr">
+      <c r="A43" s="71" t="inlineStr">
         <is>
           <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline - meaning projections tighten over time as operating history grows.</t>
         </is>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Jan 1 – May 31, 2026</t>
+          <t>Jan 1 – Jun 30, 2026</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>273154.41</v>
+        <v>341945.84</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>129044.74</v>
+        <v>159686.64</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>144109.67</v>
+        <v>182259.2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>•  QBO YTD NOI of $144,110 through May 31 (5 months of operations)</t>
+          <t>•  QBO YTD NOI of $182,259 through June 30 (6 months of operations, annualizes to ~$364,518)</t>
         </is>
       </c>
     </row>
@@ -2044,14 +2044,14 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Rental Income (Jan 1 – May 31): $273,154</t>
+          <t>QBO YTD Rental Income (Jan 1 – Jun 30): $341,946</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Total Expenses: $129,045  |  QBO YTD NOI: $144,110</t>
+          <t>QBO YTD Total Expenses: $159,687  |  QBO YTD NOI: $182,259</t>
         </is>
       </c>
     </row>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -120,7 +120,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -150,6 +150,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004CAF50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002196F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -198,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,6 +248,9 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -278,11 +286,11 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -732,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-06-30</t>
+          <t>Prepared 2026-07-07</t>
         </is>
       </c>
     </row>
@@ -800,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -867,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>787475</v>
+        <v>786592</v>
       </c>
     </row>
     <row r="16">
@@ -885,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>695427</v>
+        <v>693722</v>
       </c>
     </row>
     <row r="17">
@@ -903,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>364968</v>
+        <v>345869</v>
       </c>
     </row>
     <row r="18">
@@ -913,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>330459</v>
+        <v>347853</v>
       </c>
     </row>
     <row r="19">
@@ -923,7 +931,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20">
@@ -933,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="22">
@@ -1379,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>330459</v>
+        <v>347853</v>
       </c>
     </row>
     <row r="42">
@@ -1698,7 +1706,7 @@
         <v>69654</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>66938</v>
+        <v>67076</v>
       </c>
       <c r="H8" s="24">
         <f>SUM(B8:G8)</f>
@@ -2210,37 +2218,37 @@
       </c>
       <c r="H4" s="33" t="inlineStr">
         <is>
+          <t>BOOKED</t>
+        </is>
+      </c>
+      <c r="I4" s="34" t="inlineStr">
+        <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="J4" s="33" t="inlineStr">
+      <c r="K4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="K4" s="33" t="inlineStr">
+      <c r="L4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="L4" s="33" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr">
         <is>
           <t>PROJECTED</t>
         </is>
       </c>
-      <c r="M4" s="33" t="inlineStr">
-        <is>
-          <t>PROJECTED</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr"/>
+      <c r="A5" s="35" t="inlineStr"/>
       <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Jan</t>
@@ -2308,48 +2316,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="37" t="n">
         <v>55</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="37" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="37" t="n">
         <v>69</v>
       </c>
-      <c r="F6" s="36" t="n">
+      <c r="F6" s="37" t="n">
         <v>77</v>
       </c>
-      <c r="G6" s="36" t="n">
+      <c r="G6" s="37" t="n">
         <v>61</v>
       </c>
-      <c r="H6" s="36" t="n">
-        <v>68</v>
-      </c>
-      <c r="I6" s="36" t="n">
-        <v>66</v>
-      </c>
-      <c r="J6" s="36" t="n">
+      <c r="H6" s="37" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="37" t="n">
+        <v>67</v>
+      </c>
+      <c r="J6" s="37" t="n">
         <v>54</v>
       </c>
-      <c r="K6" s="36" t="n">
+      <c r="K6" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="L6" s="36" t="n">
+      <c r="L6" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="M6" s="36" t="n">
+      <c r="M6" s="37" t="n">
         <v>58</v>
       </c>
-      <c r="N6" s="37">
+      <c r="N6" s="38">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2360,90 +2368,90 @@
           <t>Nights Sold</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
+      <c r="B7" s="39" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="39" t="n">
         <v>136</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="39" t="n">
         <v>164</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="39" t="n">
         <v>151</v>
       </c>
-      <c r="F7" s="38" t="n">
+      <c r="F7" s="39" t="n">
         <v>169</v>
       </c>
-      <c r="G7" s="38" t="n">
+      <c r="G7" s="39" t="n">
         <v>140</v>
       </c>
-      <c r="H7" s="38" t="n">
-        <v>171</v>
-      </c>
-      <c r="I7" s="38" t="n">
+      <c r="H7" s="39" t="n">
+        <v>141</v>
+      </c>
+      <c r="I7" s="39" t="n">
         <v>168</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="39" t="n">
         <v>136</v>
       </c>
-      <c r="K7" s="38" t="n">
+      <c r="K7" s="39" t="n">
         <v>133</v>
       </c>
-      <c r="L7" s="38" t="n">
+      <c r="L7" s="39" t="n">
         <v>133</v>
       </c>
-      <c r="M7" s="38" t="n">
+      <c r="M7" s="39" t="n">
         <v>146</v>
       </c>
-      <c r="N7" s="39">
+      <c r="N7" s="40">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Available Nights</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="37" t="n">
         <v>168</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="E8" s="36" t="n">
+      <c r="E8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="G8" s="36" t="n">
+      <c r="G8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="H8" s="36" t="n">
+      <c r="H8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="I8" s="36" t="n">
+      <c r="I8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="J8" s="36" t="n">
+      <c r="J8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="K8" s="36" t="n">
+      <c r="K8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="L8" s="36" t="n">
+      <c r="L8" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="M8" s="36" t="n">
+      <c r="M8" s="37" t="n">
         <v>186</v>
       </c>
-      <c r="N8" s="37">
+      <c r="N8" s="38">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -2454,90 +2462,90 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="41" t="n">
         <v>0.753</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="41" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="41" t="n">
         <v>0.882</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="41" t="n">
         <v>0.8390000000000001</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="41" t="n">
         <v>0.909</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G9" s="41" t="n">
         <v>0.778</v>
       </c>
-      <c r="H9" s="40" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I9" s="40" t="n">
+      <c r="H9" s="41" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="I9" s="41" t="n">
         <v>0.9009999999999999</v>
       </c>
-      <c r="J9" s="40" t="n">
+      <c r="J9" s="41" t="n">
         <v>0.758</v>
       </c>
-      <c r="K9" s="40" t="n">
+      <c r="K9" s="41" t="n">
         <v>0.716</v>
       </c>
-      <c r="L9" s="40" t="n">
+      <c r="L9" s="41" t="n">
         <v>0.741</v>
       </c>
-      <c r="M9" s="40" t="n">
+      <c r="M9" s="41" t="n">
         <v>0.7829999999999999</v>
       </c>
-      <c r="N9" s="41">
+      <c r="N9" s="42">
         <f>AVERAGE(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>ADR</t>
         </is>
       </c>
-      <c r="B10" s="42" t="n">
+      <c r="B10" s="43" t="n">
         <v>286</v>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="43" t="n">
         <v>398</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="43" t="n">
         <v>415</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="43" t="n">
         <v>488</v>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="43" t="n">
         <v>472</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="43" t="n">
         <v>550</v>
       </c>
-      <c r="H10" s="42" t="n">
-        <v>535</v>
-      </c>
-      <c r="I10" s="42" t="n">
+      <c r="H10" s="43" t="n">
+        <v>643</v>
+      </c>
+      <c r="I10" s="43" t="n">
         <v>513</v>
       </c>
-      <c r="J10" s="42" t="n">
+      <c r="J10" s="43" t="n">
         <v>407</v>
       </c>
-      <c r="K10" s="42" t="n">
+      <c r="K10" s="43" t="n">
         <v>385</v>
       </c>
-      <c r="L10" s="42" t="n">
+      <c r="L10" s="43" t="n">
         <v>385</v>
       </c>
-      <c r="M10" s="42" t="n">
+      <c r="M10" s="43" t="n">
         <v>407</v>
       </c>
-      <c r="N10" s="43">
+      <c r="N10" s="44">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -2548,43 +2556,43 @@
           <t>RevPAR</t>
         </is>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B11" s="45" t="n">
         <v>215</v>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="45" t="n">
         <v>322</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="45" t="n">
         <v>366</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="45" t="n">
         <v>410</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>428</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="45" t="n">
         <v>428</v>
       </c>
-      <c r="H11" s="44" t="n">
-        <v>492</v>
-      </c>
-      <c r="I11" s="44" t="n">
+      <c r="H11" s="45" t="n">
+        <v>487</v>
+      </c>
+      <c r="I11" s="45" t="n">
         <v>463</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="45" t="n">
         <v>308</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="45" t="n">
         <v>275</v>
       </c>
-      <c r="L11" s="44" t="n">
+      <c r="L11" s="45" t="n">
         <v>284</v>
       </c>
-      <c r="M11" s="44" t="n">
+      <c r="M11" s="45" t="n">
         <v>319</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="46">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -2595,43 +2603,43 @@
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="47" t="n">
         <v>40041</v>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="47" t="n">
         <v>54065</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="47" t="n">
         <v>68024</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="47" t="n">
         <v>73746</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="47" t="n">
         <v>79700</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="47" t="n">
         <v>77046</v>
       </c>
-      <c r="H12" s="46" t="n">
-        <v>91485</v>
-      </c>
-      <c r="I12" s="46" t="n">
+      <c r="H12" s="47" t="n">
+        <v>90602</v>
+      </c>
+      <c r="I12" s="47" t="n">
         <v>86184</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="47" t="n">
         <v>55352</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="47" t="n">
         <v>51205</v>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="47" t="n">
         <v>51205</v>
       </c>
-      <c r="M12" s="46" t="n">
+      <c r="M12" s="47" t="n">
         <v>59422</v>
       </c>
-      <c r="N12" s="43">
+      <c r="N12" s="44">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -2642,43 +2650,43 @@
           <t>Net to Owner</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="48" t="n">
         <v>35785</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="48" t="n">
         <v>48880</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="48" t="n">
         <v>61256</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="48" t="n">
         <v>64778</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="48" t="n">
         <v>69654</v>
       </c>
-      <c r="G13" s="47" t="n">
-        <v>66938</v>
-      </c>
-      <c r="H13" s="47" t="n">
-        <v>80661</v>
-      </c>
-      <c r="I13" s="47" t="n">
-        <v>75987</v>
-      </c>
-      <c r="J13" s="47" t="n">
-        <v>48803</v>
-      </c>
-      <c r="K13" s="47" t="n">
-        <v>45147</v>
-      </c>
-      <c r="L13" s="47" t="n">
-        <v>45147</v>
-      </c>
-      <c r="M13" s="47" t="n">
-        <v>52391</v>
-      </c>
-      <c r="N13" s="45">
+      <c r="G13" s="48" t="n">
+        <v>67076</v>
+      </c>
+      <c r="H13" s="48" t="n">
+        <v>78839</v>
+      </c>
+      <c r="I13" s="48" t="n">
+        <v>75981</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>48799</v>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>45143</v>
+      </c>
+      <c r="L13" s="48" t="n">
+        <v>45143</v>
+      </c>
+      <c r="M13" s="48" t="n">
+        <v>52388</v>
+      </c>
+      <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -2722,7 +2730,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-06-30. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-07-07. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2769,90 +2777,90 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
-        <v>91485</v>
-      </c>
-      <c r="C5" s="50" t="n">
-        <v>86728</v>
-      </c>
-      <c r="D5" s="51" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="E5" s="49" t="n">
-        <v>657</v>
-      </c>
-      <c r="F5" s="49" t="n">
-        <v>466</v>
-      </c>
-      <c r="G5" s="49" t="n">
-        <v>4757</v>
-      </c>
-      <c r="H5" s="52" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="B5" s="50" t="n">
+        <v>90602</v>
+      </c>
+      <c r="C5" s="51" t="n">
+        <v>90602</v>
+      </c>
+      <c r="D5" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="50" t="n">
+        <v>643</v>
+      </c>
+      <c r="F5" s="50" t="n">
+        <v>487</v>
+      </c>
+      <c r="G5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="53" t="inlineStr">
+        <is>
+          <t>Fully Booked</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="B6" s="54" t="n">
+      <c r="B6" s="55" t="n">
         <v>86184</v>
       </c>
-      <c r="C6" s="55" t="n">
-        <v>37411</v>
-      </c>
-      <c r="D6" s="56" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="E6" s="54" t="n">
-        <v>576</v>
-      </c>
-      <c r="F6" s="54" t="n">
-        <v>201</v>
-      </c>
-      <c r="G6" s="54" t="n">
-        <v>48773</v>
-      </c>
-      <c r="H6" s="57" t="inlineStr">
+      <c r="C6" s="56" t="n">
+        <v>39876</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>578</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>214</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B7" s="54" t="n">
+      <c r="B7" s="55" t="n">
         <v>55352</v>
       </c>
-      <c r="C7" s="55" t="n">
-        <v>21175</v>
-      </c>
-      <c r="D7" s="56" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="E7" s="54" t="n">
-        <v>471</v>
-      </c>
-      <c r="F7" s="54" t="n">
-        <v>118</v>
-      </c>
-      <c r="G7" s="54" t="n">
-        <v>34177</v>
-      </c>
-      <c r="H7" s="57" t="inlineStr">
+      <c r="C7" s="56" t="n">
+        <v>18604</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>454</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>103</v>
+      </c>
+      <c r="G7" s="55" t="n">
+        <v>36748</v>
+      </c>
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
@@ -2864,23 +2872,23 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="59" t="n">
         <v>51205</v>
       </c>
-      <c r="C8" s="45" t="n">
-        <v>5147</v>
-      </c>
-      <c r="D8" s="41" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="E8" s="58" t="n">
-        <v>396</v>
-      </c>
-      <c r="F8" s="58" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="58" t="n">
-        <v>46058</v>
+      <c r="C8" s="46" t="n">
+        <v>6608</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="E8" s="59" t="n">
+        <v>441</v>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>36</v>
+      </c>
+      <c r="G8" s="59" t="n">
+        <v>44597</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
@@ -2894,22 +2902,22 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B9" s="58" t="n">
+      <c r="B9" s="59" t="n">
         <v>51205</v>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="46" t="n">
         <v>5590</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="42" t="n">
         <v>0.109</v>
       </c>
-      <c r="E9" s="58" t="n">
+      <c r="E9" s="59" t="n">
         <v>508</v>
       </c>
-      <c r="F9" s="58" t="n">
+      <c r="F9" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="G9" s="58" t="n">
+      <c r="G9" s="59" t="n">
         <v>45615</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -2924,23 +2932,23 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="59" t="n">
         <v>59422</v>
       </c>
-      <c r="C10" s="45" t="n">
-        <v>5822</v>
-      </c>
-      <c r="D10" s="41" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="E10" s="58" t="n">
-        <v>342</v>
-      </c>
-      <c r="F10" s="58" t="n">
-        <v>31</v>
-      </c>
-      <c r="G10" s="58" t="n">
-        <v>53600</v>
+      <c r="C10" s="46" t="n">
+        <v>5384</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>336</v>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" s="59" t="n">
+        <v>54038</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2949,30 +2957,30 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="61">
         <f>SUM(B5:B10)</f>
         <v/>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="61">
         <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="62">
         <f>C11/B11</f>
         <v/>
       </c>
-      <c r="E11" s="62" t="n"/>
-      <c r="F11" s="62" t="n"/>
-      <c r="G11" s="60">
+      <c r="E11" s="63" t="n"/>
+      <c r="F11" s="63" t="n"/>
+      <c r="G11" s="61">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="H11" s="62" t="n"/>
+      <c r="H11" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3032,7 +3040,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>787475</v>
+        <v>786592</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3045,7 +3053,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-86588</v>
+        <v>-87361</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3059,7 +3067,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5460</v>
+        <v>-5509</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3076,13 +3084,13 @@
         <f>B5+B6+B7</f>
         <v/>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="64">
         <f>B8/B5</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="64" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
@@ -3097,9 +3105,9 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-82132</v>
-      </c>
-      <c r="C11" s="65">
+        <v>-74781</v>
+      </c>
+      <c r="C11" s="66">
         <f>B11/B5</f>
         <v/>
       </c>
@@ -3111,9 +3119,9 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-139909</v>
-      </c>
-      <c r="C12" s="65">
+        <v>-128250</v>
+      </c>
+      <c r="C12" s="66">
         <f>B12/B5</f>
         <v/>
       </c>
@@ -3128,7 +3136,7 @@
         <f>-0.10*B5</f>
         <v/>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="66">
         <f>B13/B5</f>
         <v/>
       </c>
@@ -3142,7 +3150,7 @@
       <c r="B14" s="7" t="n">
         <v>-26679</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="66">
         <f>B14/B5</f>
         <v/>
       </c>
@@ -3156,7 +3164,7 @@
       <c r="B15" s="7" t="n">
         <v>-13500</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="66">
         <f>B15/B5</f>
         <v/>
       </c>
@@ -3170,22 +3178,22 @@
       <c r="B16" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="66">
         <f>B16/B5</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="66" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B17" s="67">
+      <c r="B17" s="68">
         <f>SUM(B11:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="68">
+      <c r="C17" s="69">
         <f>B17/B5</f>
         <v/>
       </c>
@@ -3200,7 +3208,7 @@
         <f>B8+B17</f>
         <v/>
       </c>
-      <c r="C19" s="69">
+      <c r="C19" s="70">
         <f>B19/B5</f>
         <v/>
       </c>
@@ -3220,8 +3228,8 @@
           <t>Expected NOI (from model)</t>
         </is>
       </c>
-      <c r="B22" s="58" t="n">
-        <v>330459</v>
+      <c r="B22" s="59" t="n">
+        <v>347853</v>
       </c>
     </row>
     <row r="23">
@@ -3230,7 +3238,7 @@
           <t>Calculated NOI (this tab)</t>
         </is>
       </c>
-      <c r="B23" s="58">
+      <c r="B23" s="59">
         <f>B19</f>
         <v/>
       </c>
@@ -3241,7 +3249,7 @@
           <t>Variance</t>
         </is>
       </c>
-      <c r="B24" s="58">
+      <c r="B24" s="59">
         <f>B23-B22</f>
         <v/>
       </c>
@@ -3287,7 +3295,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76385</v>
+        <v>76299</v>
       </c>
     </row>
     <row r="31">
@@ -3303,7 +3311,7 @@
           <t>Cleaning fees collected from guests</t>
         </is>
       </c>
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="71" t="inlineStr">
         <is>
           <t>see Cleaning expense</t>
         </is>
@@ -3384,7 +3392,7 @@
       <c r="C42" s="5" t="n"/>
     </row>
     <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="71" t="inlineStr">
+      <c r="A43" s="72" t="inlineStr">
         <is>
           <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline - meaning projections tighten over time as operating history grows.</t>
         </is>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>345869</v>
+        <v>361916</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>347853</v>
+        <v>331806</v>
       </c>
     </row>
     <row r="19">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>347853</v>
+        <v>331806</v>
       </c>
     </row>
     <row r="42">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-74781</v>
+        <v>-79169</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-128250</v>
+        <v>-139909</v>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>347853</v>
+        <v>331806</v>
       </c>
     </row>
     <row r="23">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-07-07</t>
+          <t>Prepared 2026-07-20</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>786592</v>
+        <v>793867</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>693722</v>
+        <v>700054</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>361916</v>
+        <v>363084</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>331806</v>
+        <v>336970</v>
       </c>
     </row>
     <row r="19">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.802</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>331806</v>
+        <v>336970</v>
       </c>
     </row>
     <row r="42">
@@ -2340,10 +2340,10 @@
         <v>61</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>54</v>
@@ -2387,7 +2387,7 @@
         <v>140</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>168</v>
@@ -2481,7 +2481,7 @@
         <v>0.778</v>
       </c>
       <c r="H9" s="41" t="n">
-        <v>0.758</v>
+        <v>0.828</v>
       </c>
       <c r="I9" s="41" t="n">
         <v>0.9009999999999999</v>
@@ -2528,7 +2528,7 @@
         <v>550</v>
       </c>
       <c r="H10" s="43" t="n">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="I10" s="43" t="n">
         <v>513</v>
@@ -2575,7 +2575,7 @@
         <v>428</v>
       </c>
       <c r="H11" s="45" t="n">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="I11" s="45" t="n">
         <v>463</v>
@@ -2622,7 +2622,7 @@
         <v>77046</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>90602</v>
+        <v>97877</v>
       </c>
       <c r="I12" s="47" t="n">
         <v>86184</v>
@@ -2669,22 +2669,22 @@
         <v>67076</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>78839</v>
+        <v>85227</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>75981</v>
+        <v>75965</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48799</v>
+        <v>48789</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45143</v>
+        <v>45134</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45143</v>
+        <v>45134</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52388</v>
+        <v>52376</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2730,7 +2730,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-07-07. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-07-20. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2783,19 +2783,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>90602</v>
+        <v>97877</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>90602</v>
+        <v>97877</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2816,19 +2816,19 @@
         <v>86184</v>
       </c>
       <c r="C6" s="56" t="n">
-        <v>39876</v>
+        <v>39273</v>
       </c>
       <c r="D6" s="57" t="n">
-        <v>0.463</v>
+        <v>0.456</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F6" s="55" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>46308</v>
+        <v>46911</v>
       </c>
       <c r="H6" s="58" t="inlineStr">
         <is>
@@ -2846,19 +2846,19 @@
         <v>55352</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>18604</v>
+        <v>23042</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.336</v>
+        <v>0.416</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>454</v>
+        <v>524</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>36748</v>
+        <v>32310</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>51205</v>
       </c>
       <c r="C8" s="46" t="n">
-        <v>6608</v>
+        <v>9175</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0.129</v>
+        <v>0.179</v>
       </c>
       <c r="E8" s="59" t="n">
-        <v>441</v>
+        <v>540</v>
       </c>
       <c r="F8" s="59" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G8" s="59" t="n">
-        <v>44597</v>
+        <v>42030</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>786592</v>
+        <v>793867</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-87361</v>
+        <v>-88295</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5509</v>
+        <v>-5518</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-79169</v>
+        <v>-79609</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>331806</v>
+        <v>336970</v>
       </c>
     </row>
     <row r="23">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76299</v>
+        <v>77005</v>
       </c>
     </row>
     <row r="31">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -740,7 +740,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-07-20</t>
+          <t>Prepared 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>363084</v>
+        <v>349168</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>336970</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="19">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>336970</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="42">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>6140</v>
+        <v>6034</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>912</v>
+        <v>859</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2213</v>
@@ -1798,16 +1798,16 @@
         <v>285</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1240</v>
+        <v>1290</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>450</v>
+        <v>570</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>284</v>
+        <v>2303</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>270</v>
+        <v>586</v>
       </c>
       <c r="H13" s="7">
         <f>SUM(B13:G13)</f>
@@ -1856,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>25</v>
+        <v>515</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>60</v>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1853</v>
+        <v>1866</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>5535</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>5953</v>
+        <v>14940</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>8410</v>
@@ -1908,22 +1908,22 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>908</v>
+        <v>649</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>617</v>
+        <v>450</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(B17:G17)</f>
@@ -2730,7 +2730,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-07-20. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-07-22. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-79609</v>
+        <v>-97176</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-139909</v>
+        <v>-145765</v>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>-26679</v>
+        <v>-13340</v>
       </c>
       <c r="C14" s="66">
         <f>B14/B5</f>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="C16" s="66">
         <f>B16/B5</f>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="B22" s="59" t="n">
-        <v>336970</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="23">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -203,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -302,6 +302,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -713,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -907,105 +910,115 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Total OpEx + Fixed</t>
+          <t>Total OpEx + Mgmt + PT</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>349168</v>
+        <v>318590</v>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>NOI (After Known Fixed)</t>
+          <t>NOI Cash (matches QBO)</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>350886</v>
+        <v>381464</v>
       </c>
     </row>
     <row r="19">
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Avg ADR (Blended)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>445</v>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>NOI Normalized (Underwriting)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>367964</v>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="6" t="inlineStr">
         <is>
+          <t>Avg ADR (Blended)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
           <t>Avg Occupancy (Blended)</t>
         </is>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E21" s="10" t="n">
         <v>0.8079999999999999</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>KEY HIGHLIGHTS</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>•  Total project basis: $4,197,591 (per QBO balance sheet)</t>
-        </is>
-      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>•  Existing debt: $1,500,000 - seeking refinance</t>
+          <t>•  Total project basis: $4,197,591 (per QBO balance sheet)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - Jun) - strong operating performance</t>
+          <t>•  Existing debt: $1,500,000 - seeking refinance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  Best month to date: May at $79,700 gross</t>
+          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - Jun) - strong operating performance</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
+          <t>•  Best month to date: May at $79,700 gross</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>•  QBO YTD NOI of $182,259 through June 30 (6 months of operations, annualizes to ~$364,518)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
@@ -1387,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>350886</v>
+        <v>367964</v>
       </c>
     </row>
     <row r="42">
@@ -1763,7 +1776,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>6034</v>
+        <v>-106</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>859</v>
@@ -1850,7 +1863,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>2410</v>
+        <v>10</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -2998,7 +3011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3101,11 +3114,11 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cleaning</t>
+          <t xml:space="preserve">  Operating Expenses (QBO-driven, all-in)</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-97176</v>
+        <v>-225863</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3115,11 +3128,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Supplies, Maintenance, Other</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>-145765</v>
+          <t xml:space="preserve">  Management Fee (10% of Gross)</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>-0.10*B5</f>
+        <v/>
       </c>
       <c r="C12" s="66">
         <f>B12/B5</f>
@@ -3129,12 +3143,11 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Management Fee (10% of Gross)</t>
-        </is>
-      </c>
-      <c r="B13" s="7">
-        <f>-0.10*B5</f>
-        <v/>
+          <t xml:space="preserve">  November Property Tax 2nd Installment</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>-13340</v>
       </c>
       <c r="C13" s="66">
         <f>B13/B5</f>
@@ -3142,278 +3155,363 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Property Tax</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>-13340</v>
-      </c>
-      <c r="C14" s="66">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="68">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="69">
         <f>B14/B5</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Insurance</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
+    <row r="16">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>Net Operating Income (Cash - matches QBO)</t>
+        </is>
+      </c>
+      <c r="B16" s="71">
+        <f>B8+B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="72">
+        <f>B16/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>Normalization Adjustment</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Insurance (annual premium, prepaid Dec 2025)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
         <v>-13500</v>
       </c>
-      <c r="C15" s="66">
-        <f>B15/B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other Fixed Costs (utilities, internet, etc.)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="66">
-        <f>B16/B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="67" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B17" s="68">
-        <f>SUM(B11:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="69">
-        <f>B17/B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="B19" s="28">
-        <f>B8+B17</f>
-        <v/>
-      </c>
-      <c r="C19" s="70">
+      <c r="C19" s="66">
         <f>B19/B5</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Net Operating Income (Normalized - for Underwriting)</t>
+        </is>
+      </c>
+      <c r="B21" s="28">
+        <f>B16+B19</f>
+        <v/>
+      </c>
+      <c r="C21" s="73">
+        <f>B21/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>RECONCILIATION CHECK</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Expected NOI (from model)</t>
-        </is>
-      </c>
-      <c r="B22" s="59" t="n">
-        <v>350886</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Calculated NOI (this tab)</t>
-        </is>
-      </c>
-      <c r="B23" s="59">
-        <f>B19</f>
-        <v/>
-      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Variance</t>
-        </is>
-      </c>
-      <c r="B24" s="59">
-        <f>B23-B22</f>
-        <v/>
+          <t>Expected NOI Cash (from source model)</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="n">
+        <v>381464</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Calculated NOI Cash (this tab)</t>
+        </is>
+      </c>
+      <c r="B25" s="59">
+        <f>B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Expected NOI Normalized (from source model)</t>
+        </is>
+      </c>
+      <c r="B26" s="59" t="n">
+        <v>367964</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Calculated NOI Normalized (this tab)</t>
+        </is>
+      </c>
+      <c r="B27" s="59">
+        <f>B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Cash Variance</t>
+        </is>
+      </c>
+      <c r="B28" s="59">
+        <f>B25-B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Normalized Variance</t>
+        </is>
+      </c>
+      <c r="B29" s="59">
+        <f>B27-B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B25" s="31">
-        <f>IF(ABS(B24)&lt;=1,"OK - reconciles","REVIEW - variance exceeds $1")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>PASS-THROUGH TAXES &amp; FEES (INFORMATIONAL)</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>The following amounts are collected from guests at booking and either remitted to the City or</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>offset by corresponding expenses. They are NOT deducted from Net to Owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>TOT (Transient Occupancy Tax) collected from guests</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>77005</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Remitted to City of Santa Barbara (12% lodging tax)</t>
-        </is>
+      <c r="B30" s="31">
+        <f>IF(AND(ABS(B28)&lt;=1,ABS(B29)&lt;=1),"OK - reconciles","REVIEW - variance exceeds $1")</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Cleaning fees collected from guests</t>
-        </is>
-      </c>
-      <c r="B32" s="71" t="inlineStr">
-        <is>
-          <t>see Cleaning expense</t>
-        </is>
-      </c>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>DATA SOURCES</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>Operating Expenses: QuickBooks Online monthly P&amp;L for closed months (6 months so far); trailing 3-month average for projected months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Management Fee: 10% of gross revenue per management agreement with ZenStay Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>November Property Tax: Second SB County installment projection ($13,340); first installment paid in March.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Insurance: Annual premium of $13,500 was prepaid in December 2025, so does not appear in 2026 cash-basis QBO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shown as normalization adjustment for underwriting purposes to reflect true ongoing cost structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Bookkeeping: Paid through DCP parent entity; not a property-level expense (excluded).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>PASS-THROUGH TAXES &amp; FEES (INFORMATIONAL)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>The following amounts are collected from guests at booking and either remitted to the City or</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>offset by corresponding expenses. They are NOT deducted from Net to Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>TOT (Transient Occupancy Tax) collected from guests</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>77005</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Remitted to City of Santa Barbara (12% lodging tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Cleaning fees collected from guests</t>
+        </is>
+      </c>
+      <c r="B45" s="74" t="inlineStr">
+        <is>
+          <t>see Cleaning expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Offset by Cleaning expense above; net-neutral pass-through</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>MODEL INPUTS</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="B48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Closed Months Used for Calibration</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B49" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Baseline ADR (de-seasonalized)</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B50" s="7" t="n">
         <v>428</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Baseline Occupancy (de-seasonalized)</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
+      <c r="B51" s="10" t="n">
         <v>0.8420000000000001</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Max Occupancy Cap</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n">
+      <c r="B52" s="10" t="n">
         <v>0.92</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Back-test MAPE (Gross Revenue)</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
+      <c r="B53" s="10" t="n">
         <v>0.105</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>METHODOLOGY</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="72" t="inlineStr">
-        <is>
-          <t>Pro forma projections blend closed-month actuals (sourced from PMS booking data and QuickBooks) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. Operating expenses are projected from trailing actuals, with cleaning costs scaled per turnover and fixed costs (management, property tax, insurance) carried at known annual amounts. The model recalibrates automatically as each month closes, incorporating new actuals into the baseline - meaning projections tighten over time as operating history grows.</t>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="75" t="inlineStr">
+        <is>
+          <t>REVENUE: Pro forma projections blend closed-month actuals (from PMS booking data) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. EXPENSES: Operating expenses flow directly from QuickBooks Online monthly P&amp;L for closed months (audited source of truth); future months use a trailing 3-month average by category. Management fee is calculated separately as 10% of gross revenue. Property tax second installment projected for November. Insurance is shown as a normalization adjustment (annual premium was prepaid in Dec 2025 and is not in the 2026 cash-basis books). The model recalibrates automatically as each month closes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A28:C28"/>
+  <mergeCells count="13">
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B25">
+  <conditionalFormatting sqref="B30">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>B25="OK - reconciles"</formula>
+      <formula>B30="OK - reconciles"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>NOT(B25="OK - reconciles")</formula>
+      <formula>NOT(B30="OK - reconciles")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -743,7 +743,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-07-22</t>
+          <t>Prepared 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>318590</v>
+        <v>335668</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>381464</v>
+        <v>364386</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>367964</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="20">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>367964</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="42">
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1669,100 +1669,100 @@
       <c r="H6" s="22" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Gross Booking Revenue</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>40041</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>54065</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>68024</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>73746</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>79700</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>77046</v>
-      </c>
-      <c r="H7" s="9">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Rental Income (QBO cash basis)</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>39064.63</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>43259.78</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>56098.15</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>76088.88</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>58642.97</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>68791.42999999999</v>
+      </c>
+      <c r="H7" s="24">
         <f>SUM(B7:G7)</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Net to Owner (after OTA &amp; Processing)</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n">
-        <v>35785</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <v>48880</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>61256</v>
-      </c>
-      <c r="E8" s="24" t="n">
-        <v>64778</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>69654</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>67076</v>
-      </c>
-      <c r="H8" s="24">
-        <f>SUM(B8:G8)</f>
-        <v/>
-      </c>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cleaning</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>8483</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>7028</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>7020</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>7255</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>7940</v>
+      </c>
+      <c r="H10" s="7">
+        <f>SUM(B10:G10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cleaning</t>
+          <t xml:space="preserve">  Supplies</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>8483</v>
+        <v>6034</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>5790</v>
+        <v>859</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>7028</v>
+        <v>2213</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7020</v>
+        <v>607</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7255</v>
+        <v>1378</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>7940</v>
+        <v>4189</v>
       </c>
       <c r="H11" s="7">
         <f>SUM(B11:G11)</f>
@@ -1772,26 +1772,26 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Supplies</t>
+          <t xml:space="preserve">  Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-106</v>
+        <v>572</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>859</v>
+        <v>285</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2213</v>
+        <v>1290</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>607</v>
+        <v>570</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1378</v>
+        <v>2303</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>4189</v>
+        <v>586</v>
       </c>
       <c r="H12" s="7">
         <f>SUM(B12:G12)</f>
@@ -1801,26 +1801,26 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Repairs &amp; Maintenance</t>
+          <t xml:space="preserve">  Management Fee</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>572</v>
+        <v>4229</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>285</v>
+        <v>4522</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1290</v>
+        <v>5542</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>570</v>
+        <v>7662</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2303</v>
+        <v>5832</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>586</v>
+        <v>6718</v>
       </c>
       <c r="H13" s="7">
         <f>SUM(B13:G13)</f>
@@ -1830,26 +1830,26 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Management Fee</t>
+          <t xml:space="preserve">  Marketing &amp; Advertising</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>4229</v>
+        <v>2410</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>4522</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5542</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>7662</v>
+        <v>515</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>5832</v>
+        <v>60</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>6718</v>
+        <v>50</v>
       </c>
       <c r="H14" s="7">
         <f>SUM(B14:G14)</f>
@@ -1859,26 +1859,26 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Marketing &amp; Advertising</t>
+          <t xml:space="preserve">  Taxes &amp; Licenses</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>10</v>
+        <v>1866</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0</v>
+        <v>5535</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>14940</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>515</v>
+        <v>8410</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>60</v>
+        <v>9620</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>50</v>
+        <v>9858</v>
       </c>
       <c r="H15" s="7">
         <f>SUM(B15:G15)</f>
@@ -1888,26 +1888,26 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Taxes &amp; Licenses</t>
+          <t xml:space="preserve">  Other</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1866</v>
+        <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>5535</v>
+        <v>649</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>14940</v>
+        <v>325</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>8410</v>
+        <v>450</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>9620</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>9858</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7">
         <f>SUM(B16:G16)</f>
@@ -1915,237 +1915,208 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>649</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>325</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>SUM(B10:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>SUM(C10:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>SUM(D10:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>SUM(E10:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>SUM(F10:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
+        <f>SUM(G10:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="26">
         <f>SUM(B17:G17)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B18" s="26">
-        <f>SUM(B11:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="26">
-        <f>SUM(C11:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>SUM(D11:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="26">
-        <f>SUM(E11:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="26">
-        <f>SUM(F11:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>SUM(G11:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
-        <f>SUM(B18:G18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B20" s="28">
-        <f>B8-B18</f>
-        <v/>
-      </c>
-      <c r="C20" s="28">
-        <f>C8-C18</f>
-        <v/>
-      </c>
-      <c r="D20" s="28">
-        <f>D8-D18</f>
-        <v/>
-      </c>
-      <c r="E20" s="28">
-        <f>E8-E18</f>
-        <v/>
-      </c>
-      <c r="F20" s="28">
-        <f>F8-F18</f>
-        <v/>
-      </c>
-      <c r="G20" s="28">
-        <f>G8-G18</f>
-        <v/>
-      </c>
-      <c r="H20" s="28">
-        <f>SUM(B20:G20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="B19" s="28">
+        <f>B7-B17</f>
+        <v/>
+      </c>
+      <c r="C19" s="28">
+        <f>C7-C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="28">
+        <f>D7-D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="28">
+        <f>E7-E17</f>
+        <v/>
+      </c>
+      <c r="F19" s="28">
+        <f>F7-F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="28">
+        <f>G7-G17</f>
+        <v/>
+      </c>
+      <c r="H19" s="28">
+        <f>SUM(B19:G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Reconciliation check:</t>
         </is>
       </c>
-      <c r="B22" s="30">
-        <f>IF(ROUND(B8-B18-B20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="C22" s="30">
-        <f>IF(ROUND(C8-C18-C20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="D22" s="30">
-        <f>IF(ROUND(D8-D18-D20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="E22" s="30">
-        <f>IF(ROUND(E8-E18-E20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="F22" s="30">
-        <f>IF(ROUND(F8-F18-F20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="G22" s="30">
-        <f>IF(ROUND(G8-G18-G20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="H22" s="30">
-        <f>IF(ROUND(H8-H18-H20,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
+      <c r="B21" s="30">
+        <f>IF(ROUND(B7-B17-B19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="C21" s="30">
+        <f>IF(ROUND(C7-C17-C19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="D21" s="30">
+        <f>IF(ROUND(D7-D17-D19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="E21" s="30">
+        <f>IF(ROUND(E7-E17-E19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="F21" s="30">
+        <f>IF(ROUND(F7-F17-F19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="G21" s="30">
+        <f>IF(ROUND(G7-G17-G19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="H21" s="30">
+        <f>IF(ROUND(H7-H17-H19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>QBO RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>QBO RECONCILIATION</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>QBO YTD Rental Income (Jan 1 – Jun 30): $341,946</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Rental Income (Jan 1 – Jun 30): $341,946</t>
+          <t>QBO YTD Total Expenses: $159,687  |  QBO YTD NOI: $182,259</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Total Expenses: $159,687  |  QBO YTD NOI: $182,259</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
           <t>Note: Minor variances between PMS and QBO are expected due to cash vs accrual timing and partial-month cutoffs.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
   </mergeCells>
-  <conditionalFormatting sqref="B22">
+  <conditionalFormatting sqref="B21">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B22="OK"</formula>
+      <formula>B21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>B22="ERR"</formula>
+      <formula>B21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
+  <conditionalFormatting sqref="C21">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>C22="OK"</formula>
+      <formula>C21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>C22="ERR"</formula>
+      <formula>C21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22">
+  <conditionalFormatting sqref="D21">
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>D22="OK"</formula>
+      <formula>D21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>D22="ERR"</formula>
+      <formula>D21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
+  <conditionalFormatting sqref="E21">
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>E22="OK"</formula>
+      <formula>E21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="1">
-      <formula>E22="ERR"</formula>
+      <formula>E21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
+  <conditionalFormatting sqref="F21">
     <cfRule type="expression" priority="9" dxfId="0">
-      <formula>F22="OK"</formula>
+      <formula>F21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="1">
-      <formula>F22="ERR"</formula>
+      <formula>F21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
+  <conditionalFormatting sqref="G21">
     <cfRule type="expression" priority="11" dxfId="0">
-      <formula>G22="OK"</formula>
+      <formula>G21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="1">
-      <formula>G22="ERR"</formula>
+      <formula>G21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
+  <conditionalFormatting sqref="H21">
     <cfRule type="expression" priority="13" dxfId="0">
-      <formula>H22="OK"</formula>
+      <formula>H21="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="1">
-      <formula>H22="ERR"</formula>
+      <formula>H21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2743,7 +2714,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-07-22. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-07-23. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3089,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-225863</v>
+        <v>-242941</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3238,7 +3209,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>381464</v>
+        <v>364386</v>
       </c>
     </row>
     <row r="25">
@@ -3259,7 +3230,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>367964</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="27">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>793867</v>
+        <v>795902</v>
       </c>
     </row>
     <row r="16">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>700054</v>
+        <v>701948</v>
       </c>
     </row>
     <row r="17">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>335668</v>
+        <v>335980</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>364386</v>
+        <v>365968</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>350886</v>
+        <v>352468</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.8079999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -999,7 +999,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>350886</v>
+        <v>352468</v>
       </c>
     </row>
     <row r="42">
@@ -2324,7 +2324,7 @@
         <v>61</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="37" t="n">
         <v>66</v>
@@ -2371,7 +2371,7 @@
         <v>140</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>168</v>
@@ -2465,7 +2465,7 @@
         <v>0.778</v>
       </c>
       <c r="H9" s="41" t="n">
-        <v>0.828</v>
+        <v>0.8390000000000001</v>
       </c>
       <c r="I9" s="41" t="n">
         <v>0.9009999999999999</v>
@@ -2512,7 +2512,7 @@
         <v>550</v>
       </c>
       <c r="H10" s="43" t="n">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="I10" s="43" t="n">
         <v>513</v>
@@ -2559,7 +2559,7 @@
         <v>428</v>
       </c>
       <c r="H11" s="45" t="n">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="I11" s="45" t="n">
         <v>463</v>
@@ -2606,7 +2606,7 @@
         <v>77046</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>97877</v>
+        <v>99912</v>
       </c>
       <c r="I12" s="47" t="n">
         <v>86184</v>
@@ -2653,22 +2653,22 @@
         <v>67076</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>85227</v>
+        <v>86996</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>75965</v>
+        <v>76000</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48789</v>
+        <v>48812</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45134</v>
+        <v>45155</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45134</v>
+        <v>45155</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52376</v>
+        <v>52401</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2767,19 +2767,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>97877</v>
+        <v>99912</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>97877</v>
+        <v>99912</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2800,19 +2800,19 @@
         <v>86184</v>
       </c>
       <c r="C6" s="56" t="n">
-        <v>39273</v>
+        <v>44037</v>
       </c>
       <c r="D6" s="57" t="n">
-        <v>0.456</v>
+        <v>0.511</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="F6" s="55" t="n">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>46911</v>
+        <v>42147</v>
       </c>
       <c r="H6" s="58" t="inlineStr">
         <is>
@@ -2890,19 +2890,19 @@
         <v>51205</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>5590</v>
+        <v>6380</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0.109</v>
+        <v>0.125</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>45615</v>
+        <v>44825</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2920,19 +2920,19 @@
         <v>59422</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>5384</v>
+        <v>8473</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0.091</v>
+        <v>0.143</v>
       </c>
       <c r="E10" s="59" t="n">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="F10" s="59" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G10" s="59" t="n">
-        <v>54038</v>
+        <v>50949</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>793867</v>
+        <v>795902</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-88295</v>
+        <v>-88380</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5518</v>
+        <v>-5574</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-242941</v>
+        <v>-243050</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>364386</v>
+        <v>365968</v>
       </c>
     </row>
     <row r="25">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>350886</v>
+        <v>352468</v>
       </c>
     </row>
     <row r="27">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>77005</v>
+        <v>77202</v>
       </c>
     </row>
     <row r="44">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -743,7 +743,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-07-23</t>
+          <t>Prepared 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>6 months actuals + seasonal model</t>
+          <t>7 months actuals + seasonal model</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>795902</v>
+        <v>772304</v>
       </c>
     </row>
     <row r="16">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>701948</v>
+        <v>680765</v>
       </c>
     </row>
     <row r="17">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>335980</v>
+        <v>331925</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>365968</v>
+        <v>348840</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>352468</v>
+        <v>335340</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="23">
@@ -985,14 +985,14 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - Jun) - strong operating performance</t>
+          <t>•  Occupancy ranging from 75% to 91% across closed months (Jan - Jul) - strong operating performance</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>•  Best month to date: May at $79,700 gross</t>
+          <t>•  Best month to date: Jul at $106,439 gross</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>352468</v>
+        <v>335340</v>
       </c>
     </row>
     <row r="42">
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1593,6 +1593,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1605,7 +1606,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating data: January – Jun 2026  |  QBO YTD cross-referenced</t>
+          <t>Operating data: January – Jul 2026  |  QBO YTD cross-referenced</t>
         </is>
       </c>
     </row>
@@ -1649,6 +1650,11 @@
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -1667,6 +1673,7 @@
       <c r="F6" s="22" t="n"/>
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
+      <c r="I6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
@@ -1692,8 +1699,11 @@
       <c r="G7" s="24" t="n">
         <v>68791.42999999999</v>
       </c>
-      <c r="H7" s="24">
-        <f>SUM(B7:G7)</f>
+      <c r="H7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="24">
+        <f>SUM(B7:H7)</f>
         <v/>
       </c>
     </row>
@@ -1710,6 +1720,7 @@
       <c r="F9" s="22" t="n"/>
       <c r="G9" s="22" t="n"/>
       <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1735,8 +1746,11 @@
       <c r="G10" s="7" t="n">
         <v>7940</v>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(B10:G10)</f>
+      <c r="H10" s="7" t="n">
+        <v>5384</v>
+      </c>
+      <c r="I10" s="7">
+        <f>SUM(B10:H10)</f>
         <v/>
       </c>
     </row>
@@ -1764,8 +1778,11 @@
       <c r="G11" s="7" t="n">
         <v>4189</v>
       </c>
-      <c r="H11" s="7">
-        <f>SUM(B11:G11)</f>
+      <c r="H11" s="7" t="n">
+        <v>1489</v>
+      </c>
+      <c r="I11" s="7">
+        <f>SUM(B11:H11)</f>
         <v/>
       </c>
     </row>
@@ -1793,8 +1810,11 @@
       <c r="G12" s="7" t="n">
         <v>586</v>
       </c>
-      <c r="H12" s="7">
-        <f>SUM(B12:G12)</f>
+      <c r="H12" s="7" t="n">
+        <v>916</v>
+      </c>
+      <c r="I12" s="7">
+        <f>SUM(B12:H12)</f>
         <v/>
       </c>
     </row>
@@ -1822,8 +1842,11 @@
       <c r="G13" s="7" t="n">
         <v>6718</v>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(B13:G13)</f>
+      <c r="H13" s="7" t="n">
+        <v>8917</v>
+      </c>
+      <c r="I13" s="7">
+        <f>SUM(B13:H13)</f>
         <v/>
       </c>
     </row>
@@ -1851,8 +1874,11 @@
       <c r="G14" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="H14" s="7">
-        <f>SUM(B14:G14)</f>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <f>SUM(B14:H14)</f>
         <v/>
       </c>
     </row>
@@ -1880,8 +1906,11 @@
       <c r="G15" s="7" t="n">
         <v>9858</v>
       </c>
-      <c r="H15" s="7">
-        <f>SUM(B15:G15)</f>
+      <c r="H15" s="7" t="n">
+        <v>11045</v>
+      </c>
+      <c r="I15" s="7">
+        <f>SUM(B15:H15)</f>
         <v/>
       </c>
     </row>
@@ -1909,8 +1938,11 @@
       <c r="G16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="7">
-        <f>SUM(B16:G16)</f>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7">
+        <f>SUM(B16:H16)</f>
         <v/>
       </c>
     </row>
@@ -1945,7 +1977,11 @@
         <v/>
       </c>
       <c r="H17" s="26">
-        <f>SUM(B17:G17)</f>
+        <f>SUM(H10:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="26">
+        <f>SUM(B17:H17)</f>
         <v/>
       </c>
     </row>
@@ -1980,7 +2016,11 @@
         <v/>
       </c>
       <c r="H19" s="28">
-        <f>SUM(B19:G19)</f>
+        <f>H7-H17</f>
+        <v/>
+      </c>
+      <c r="I19" s="28">
+        <f>SUM(B19:H19)</f>
         <v/>
       </c>
     </row>
@@ -2016,6 +2056,10 @@
       </c>
       <c r="H21" s="30">
         <f>IF(ROUND(H7-H17-H19,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="I21" s="30">
+        <f>IF(ROUND(I7-I17-I19,0)=0,"OK","ERR")</f>
         <v/>
       </c>
     </row>
@@ -2032,6 +2076,7 @@
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -2056,12 +2101,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <conditionalFormatting sqref="B21">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2119,6 +2164,14 @@
       <formula>H21="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="expression" priority="15" dxfId="0">
+      <formula>I21="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="1">
+      <formula>I21="ERR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2200,14 +2253,14 @@
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="H4" s="33" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
+        <is>
+          <t>ACTUAL</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>BOOKED</t>
-        </is>
-      </c>
-      <c r="I4" s="34" t="inlineStr">
-        <is>
-          <t>PROJECTED</t>
         </is>
       </c>
       <c r="J4" s="34" t="inlineStr">
@@ -2324,10 +2377,10 @@
         <v>61</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>54</v>
@@ -2371,22 +2424,22 @@
         <v>140</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I7" s="39" t="n">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="J7" s="39" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L7" s="39" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M7" s="39" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N7" s="40">
         <f>SUM(B7:M7)</f>
@@ -2465,22 +2518,22 @@
         <v>0.778</v>
       </c>
       <c r="H9" s="41" t="n">
-        <v>0.8390000000000001</v>
+        <v>0.8759999999999999</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>0.9009999999999999</v>
+        <v>0.457</v>
       </c>
       <c r="J9" s="41" t="n">
-        <v>0.758</v>
+        <v>0.752</v>
       </c>
       <c r="K9" s="41" t="n">
-        <v>0.716</v>
+        <v>0.71</v>
       </c>
       <c r="L9" s="41" t="n">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
       <c r="M9" s="41" t="n">
-        <v>0.7829999999999999</v>
+        <v>0.777</v>
       </c>
       <c r="N9" s="42">
         <f>AVERAGE(B9:M9)</f>
@@ -2512,22 +2565,22 @@
         <v>550</v>
       </c>
       <c r="H10" s="43" t="n">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="I10" s="43" t="n">
-        <v>513</v>
+        <v>601</v>
       </c>
       <c r="J10" s="43" t="n">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="K10" s="43" t="n">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="L10" s="43" t="n">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="M10" s="43" t="n">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="N10" s="44">
         <f>SUM(B10:M10)</f>
@@ -2559,22 +2612,22 @@
         <v>428</v>
       </c>
       <c r="H11" s="45" t="n">
-        <v>537</v>
+        <v>572</v>
       </c>
       <c r="I11" s="45" t="n">
-        <v>463</v>
+        <v>275</v>
       </c>
       <c r="J11" s="45" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="K11" s="45" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="L11" s="45" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M11" s="45" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="N11" s="46">
         <f>SUM(B11:M11)</f>
@@ -2606,22 +2659,22 @@
         <v>77046</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>99912</v>
+        <v>106439</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>86184</v>
+        <v>51115</v>
       </c>
       <c r="J12" s="47" t="n">
-        <v>55352</v>
+        <v>56565</v>
       </c>
       <c r="K12" s="47" t="n">
-        <v>51205</v>
+        <v>52404</v>
       </c>
       <c r="L12" s="47" t="n">
-        <v>51205</v>
+        <v>52404</v>
       </c>
       <c r="M12" s="47" t="n">
-        <v>59422</v>
+        <v>60755</v>
       </c>
       <c r="N12" s="44">
         <f>SUM(B12:M12)</f>
@@ -2653,22 +2706,22 @@
         <v>67076</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>86996</v>
+        <v>92664</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>76000</v>
+        <v>44789</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>48812</v>
+        <v>49882</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>45155</v>
+        <v>46212</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>45155</v>
+        <v>46212</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>52401</v>
+        <v>53577</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2691,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2714,7 +2767,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-07-23. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-08-02. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2763,23 +2816,23 @@
     <row r="5">
       <c r="A5" s="49" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>99912</v>
+        <v>51115</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>99912</v>
+        <v>51115</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>640</v>
+        <v>601</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>537</v>
+        <v>275</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2793,26 +2846,26 @@
     <row r="6">
       <c r="A6" s="54" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="B6" s="55" t="n">
-        <v>86184</v>
+        <v>56565</v>
       </c>
       <c r="C6" s="56" t="n">
-        <v>44037</v>
+        <v>26595</v>
       </c>
       <c r="D6" s="57" t="n">
-        <v>0.511</v>
+        <v>0.47</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>603</v>
+        <v>521</v>
       </c>
       <c r="F6" s="55" t="n">
-        <v>237</v>
+        <v>148</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>42147</v>
+        <v>29970</v>
       </c>
       <c r="H6" s="58" t="inlineStr">
         <is>
@@ -2821,58 +2874,58 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="54" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B7" s="55" t="n">
-        <v>55352</v>
-      </c>
-      <c r="C7" s="56" t="n">
-        <v>23042</v>
-      </c>
-      <c r="D7" s="57" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>524</v>
-      </c>
-      <c r="F7" s="55" t="n">
-        <v>128</v>
-      </c>
-      <c r="G7" s="55" t="n">
-        <v>32310</v>
-      </c>
-      <c r="H7" s="58" t="inlineStr">
-        <is>
-          <t>Building</t>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B7" s="59" t="n">
+        <v>52404</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>11258</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <v>593</v>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>61</v>
+      </c>
+      <c r="G7" s="59" t="n">
+        <v>41146</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="B8" s="59" t="n">
-        <v>51205</v>
+        <v>52404</v>
       </c>
       <c r="C8" s="46" t="n">
-        <v>9175</v>
+        <v>5528</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0.179</v>
+        <v>0.105</v>
       </c>
       <c r="E8" s="59" t="n">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="F8" s="59" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G8" s="59" t="n">
-        <v>42030</v>
+        <v>46876</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
@@ -2883,26 +2936,26 @@
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="B9" s="59" t="n">
-        <v>51205</v>
+        <v>60755</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>6380</v>
+        <v>8473</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0.125</v>
+        <v>0.139</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>491</v>
+        <v>368</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>44825</v>
+        <v>52282</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -2911,60 +2964,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B10" s="59" t="n">
-        <v>59422</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>8473</v>
-      </c>
-      <c r="D10" s="42" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="E10" s="59" t="n">
-        <v>368</v>
-      </c>
-      <c r="F10" s="59" t="n">
-        <v>46</v>
-      </c>
-      <c r="G10" s="59" t="n">
-        <v>50949</v>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="61">
-        <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="61">
-        <f>SUM(C5:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="62">
-        <f>C11/B11</f>
-        <v/>
-      </c>
-      <c r="E11" s="63" t="n"/>
-      <c r="F11" s="63" t="n"/>
-      <c r="G11" s="61">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="H11" s="63" t="n"/>
+      <c r="B10" s="61">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="61">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="62">
+        <f>C10/B10</f>
+        <v/>
+      </c>
+      <c r="E10" s="63" t="n"/>
+      <c r="F10" s="63" t="n"/>
+      <c r="G10" s="61">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="H10" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3000,7 +3023,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Blends 6 months of closed actuals with seasonal projections calibrated from actual performance</t>
+          <t>Blends 7 months of closed actuals with seasonal projections calibrated from actual performance</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3047,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>795902</v>
+        <v>772304</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3037,7 +3060,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-88380</v>
+        <v>-86109</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3051,7 +3074,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5574</v>
+        <v>-5430</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3089,7 +3112,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-243050</v>
+        <v>-241355</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3209,7 +3232,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>365968</v>
+        <v>348840</v>
       </c>
     </row>
     <row r="25">
@@ -3230,7 +3253,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>352468</v>
+        <v>335340</v>
       </c>
     </row>
     <row r="27">
@@ -3289,7 +3312,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Operating Expenses: QuickBooks Online monthly P&amp;L for closed months (6 months so far); trailing 3-month average for projected months.</t>
+          <t>Operating Expenses: QuickBooks Online monthly P&amp;L for closed months (7 months so far); trailing 3-month average for projected months.</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3381,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>77202</v>
+        <v>74913</v>
       </c>
     </row>
     <row r="44">
@@ -3402,7 +3425,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -3412,7 +3435,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>428</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51">
@@ -3422,7 +3445,7 @@
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>0.8420000000000001</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="52">
@@ -3442,7 +3465,7 @@
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>0.105</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="55">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -743,7 +743,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-08-02</t>
+          <t>Prepared 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Jan 1 – Jun 30, 2026</t>
+          <t>Jan 1 – Jul 31, 2026</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>341945.84</v>
+        <v>430847.17</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>159686.64</v>
+        <v>190570.21</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>182259.2</v>
+        <v>240276.96</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>331925</v>
+        <v>335069</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>348840</v>
+        <v>345696</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>335340</v>
+        <v>332196</v>
       </c>
     </row>
     <row r="20">
@@ -1006,7 +1006,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>•  QBO YTD NOI of $182,259 through June 30 (6 months of operations, annualizes to ~$364,518)</t>
+          <t>•  QBO YTD NOI of $240,277 through Jul 31 (7 months, annualizes to ~$411,903)</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>335340</v>
+        <v>332196</v>
       </c>
     </row>
     <row r="42">
@@ -1700,7 +1700,7 @@
         <v>68791.42999999999</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>0</v>
+        <v>88901.33</v>
       </c>
       <c r="I7" s="24">
         <f>SUM(B7:H7)</f>
@@ -1779,7 +1779,7 @@
         <v>4189</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1489</v>
+        <v>2538</v>
       </c>
       <c r="I11" s="7">
         <f>SUM(B11:H11)</f>
@@ -1875,7 +1875,7 @@
         <v>50</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="I14" s="7">
         <f>SUM(B14:H14)</f>
@@ -1907,7 +1907,7 @@
         <v>9858</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>11045</v>
+        <v>11137</v>
       </c>
       <c r="I15" s="7">
         <f>SUM(B15:H15)</f>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I16" s="7">
         <f>SUM(B16:H16)</f>
@@ -2081,14 +2081,14 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Rental Income (Jan 1 – Jun 30): $341,946</t>
+          <t>QBO YTD Rental Income (Jan 1 – Jul 31, 2026): $430,847</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Total Expenses: $159,687  |  QBO YTD NOI: $182,259</t>
+          <t>QBO YTD Total Expenses: $190,570  |  QBO YTD NOI: $240,277</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-08-02. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-08-04. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-241355</v>
+        <v>-244499</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>348840</v>
+        <v>345696</v>
       </c>
     </row>
     <row r="25">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>335340</v>
+        <v>332196</v>
       </c>
     </row>
     <row r="27">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>8483</v>
+        <v>8483.15</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>5790</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>7028</v>
+        <v>7028.13</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>7020</v>
@@ -1747,7 +1747,7 @@
         <v>7940</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>5384</v>
+        <v>5384.29</v>
       </c>
       <c r="I10" s="7">
         <f>SUM(B10:H10)</f>
@@ -1761,25 +1761,25 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>6034</v>
+        <v>6034.38</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>859</v>
+        <v>859.39</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2213</v>
+        <v>2212.8</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>607</v>
+        <v>606.83</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1378</v>
+        <v>1377.59</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4189</v>
+        <v>4189.08</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2538</v>
+        <v>2537.55</v>
       </c>
       <c r="I11" s="7">
         <f>SUM(B11:H11)</f>
@@ -1802,13 +1802,13 @@
         <v>1290</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>570</v>
+        <v>570.16</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2303</v>
+        <v>2302.74</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>586</v>
+        <v>585.91</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>916</v>
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4229</v>
+        <v>4229.06</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>4522</v>
+        <v>4521.53</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5542</v>
+        <v>5542.02</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7662</v>
+        <v>7661.77</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>5832</v>
+        <v>5831.55</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>6718</v>
+        <v>6717.7</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>8917</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>515</v>
+        <v>514.6</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>60</v>
@@ -1889,25 +1889,25 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>1866</v>
+        <v>1866.23</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>5535</v>
+        <v>5534.8</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>14940</v>
+        <v>14939.62</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8410</v>
+        <v>8409.82</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>9620</v>
+        <v>9620.200000000001</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>9858</v>
+        <v>9857.780000000001</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>11137</v>
+        <v>11137.2</v>
       </c>
       <c r="I15" s="7">
         <f>SUM(B15:H15)</f>
@@ -1917,29 +1917,29 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other</t>
+          <t xml:space="preserve">  Utilities</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>0</v>
+        <v>964.5</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>649</v>
+        <v>763.55</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>325</v>
+        <v>1141.05</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>450</v>
+        <v>1623.09</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
+        <v>299.73</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>1301.43</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>750</v>
+        <v>991.53</v>
       </c>
       <c r="I16" s="7">
         <f>SUM(B16:H16)</f>
@@ -1947,153 +1947,185 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>649.45</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>325</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="I17" s="7">
+        <f>SUM(B17:H17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B17" s="26">
-        <f>SUM(B10:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="26">
-        <f>SUM(C10:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
-        <f>SUM(D10:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="26">
-        <f>SUM(E10:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="26">
-        <f>SUM(F10:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="26">
-        <f>SUM(G10:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="26">
-        <f>SUM(H10:H16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="26">
-        <f>SUM(B17:H17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="B18" s="26">
+        <f>SUM(B10:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>SUM(C10:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>SUM(D10:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>SUM(E10:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>SUM(F10:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>SUM(G10:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="26">
+        <f>SUM(H10:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="26">
+        <f>SUM(B18:H18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B19" s="28">
-        <f>B7-B17</f>
-        <v/>
-      </c>
-      <c r="C19" s="28">
-        <f>C7-C17</f>
-        <v/>
-      </c>
-      <c r="D19" s="28">
-        <f>D7-D17</f>
-        <v/>
-      </c>
-      <c r="E19" s="28">
-        <f>E7-E17</f>
-        <v/>
-      </c>
-      <c r="F19" s="28">
-        <f>F7-F17</f>
-        <v/>
-      </c>
-      <c r="G19" s="28">
-        <f>G7-G17</f>
-        <v/>
-      </c>
-      <c r="H19" s="28">
-        <f>H7-H17</f>
-        <v/>
-      </c>
-      <c r="I19" s="28">
-        <f>SUM(B19:H19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="B20" s="28">
+        <f>B7-B18</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>C7-C18</f>
+        <v/>
+      </c>
+      <c r="D20" s="28">
+        <f>D7-D18</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>E7-E18</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>F7-F18</f>
+        <v/>
+      </c>
+      <c r="G20" s="28">
+        <f>G7-G18</f>
+        <v/>
+      </c>
+      <c r="H20" s="28">
+        <f>H7-H18</f>
+        <v/>
+      </c>
+      <c r="I20" s="28">
+        <f>SUM(B20:H20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>Reconciliation check:</t>
         </is>
       </c>
-      <c r="B21" s="30">
-        <f>IF(ROUND(B7-B17-B19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="C21" s="30">
-        <f>IF(ROUND(C7-C17-C19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="D21" s="30">
-        <f>IF(ROUND(D7-D17-D19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="E21" s="30">
-        <f>IF(ROUND(E7-E17-E19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="F21" s="30">
-        <f>IF(ROUND(F7-F17-F19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="G21" s="30">
-        <f>IF(ROUND(G7-G17-G19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="H21" s="30">
-        <f>IF(ROUND(H7-H17-H19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-      <c r="I21" s="30">
-        <f>IF(ROUND(I7-I17-I19,0)=0,"OK","ERR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B22" s="30">
+        <f>IF(ROUND(B7-B18-B20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="C22" s="30">
+        <f>IF(ROUND(C7-C18-C20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="D22" s="30">
+        <f>IF(ROUND(D7-D18-D20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="E22" s="30">
+        <f>IF(ROUND(E7-E18-E20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="F22" s="30">
+        <f>IF(ROUND(F7-F18-F20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="G22" s="30">
+        <f>IF(ROUND(G7-G18-G20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="H22" s="30">
+        <f>IF(ROUND(H7-H18-H20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+      <c r="I22" s="30">
+        <f>IF(ROUND(I7-I18-I20,0)=0,"OK","ERR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>QBO RECONCILIATION</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>QBO YTD Rental Income (Jan 1 – Jul 31, 2026): $430,847</t>
-        </is>
-      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>QBO YTD Total Expenses: $190,570  |  QBO YTD NOI: $240,277</t>
+          <t>QBO YTD Rental Income (Jan 1 – Jul 31, 2026): $430,847</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>QBO YTD Total Expenses: $190,570  |  QBO YTD NOI: $240,277</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Note: Minor variances between PMS and QBO are expected due to cash vs accrual timing and partial-month cutoffs.</t>
         </is>
@@ -2104,72 +2136,72 @@
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A24:I24"/>
   </mergeCells>
-  <conditionalFormatting sqref="B21">
+  <conditionalFormatting sqref="B22">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B21="OK"</formula>
+      <formula>B22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>B21="ERR"</formula>
+      <formula>B22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
+  <conditionalFormatting sqref="C22">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>C21="OK"</formula>
+      <formula>C22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>C21="ERR"</formula>
+      <formula>C22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
+  <conditionalFormatting sqref="D22">
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>D21="OK"</formula>
+      <formula>D22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>D21="ERR"</formula>
+      <formula>D22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
+  <conditionalFormatting sqref="E22">
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>E21="OK"</formula>
+      <formula>E22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="1">
-      <formula>E21="ERR"</formula>
+      <formula>E22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
+  <conditionalFormatting sqref="F22">
     <cfRule type="expression" priority="9" dxfId="0">
-      <formula>F21="OK"</formula>
+      <formula>F22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="1">
-      <formula>F21="ERR"</formula>
+      <formula>F22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
+  <conditionalFormatting sqref="G22">
     <cfRule type="expression" priority="11" dxfId="0">
-      <formula>G21="OK"</formula>
+      <formula>G22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="1">
-      <formula>G21="ERR"</formula>
+      <formula>G22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+  <conditionalFormatting sqref="H22">
     <cfRule type="expression" priority="13" dxfId="0">
-      <formula>H21="OK"</formula>
+      <formula>H22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="1">
-      <formula>H21="ERR"</formula>
+      <formula>H22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
+  <conditionalFormatting sqref="I22">
     <cfRule type="expression" priority="15" dxfId="0">
-      <formula>I21="OK"</formula>
+      <formula>I22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="1">
-      <formula>I21="ERR"</formula>
+      <formula>I22="ERR"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -743,7 +743,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-08-04</t>
+          <t>Prepared 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>772304</v>
+        <v>795272</v>
       </c>
     </row>
     <row r="16">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>680765</v>
+        <v>700696</v>
       </c>
     </row>
     <row r="17">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>335069</v>
+        <v>339105</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>345696</v>
+        <v>361591</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>332196</v>
+        <v>348091</v>
       </c>
     </row>
     <row r="20">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.773</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="23">
@@ -999,7 +999,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>332196</v>
+        <v>348091</v>
       </c>
     </row>
     <row r="42">
@@ -2412,7 +2412,7 @@
         <v>52</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>54</v>
@@ -2459,7 +2459,7 @@
         <v>163</v>
       </c>
       <c r="I7" s="39" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="J7" s="39" t="n">
         <v>135</v>
@@ -2553,7 +2553,7 @@
         <v>0.8759999999999999</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>0.457</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="J9" s="41" t="n">
         <v>0.752</v>
@@ -2600,7 +2600,7 @@
         <v>653</v>
       </c>
       <c r="I10" s="43" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J10" s="43" t="n">
         <v>419</v>
@@ -2647,7 +2647,7 @@
         <v>572</v>
       </c>
       <c r="I11" s="45" t="n">
-        <v>275</v>
+        <v>398</v>
       </c>
       <c r="J11" s="45" t="n">
         <v>314</v>
@@ -2694,7 +2694,7 @@
         <v>106439</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>51115</v>
+        <v>74083</v>
       </c>
       <c r="J12" s="47" t="n">
         <v>56565</v>
@@ -2741,19 +2741,19 @@
         <v>92664</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>44789</v>
+        <v>64881</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49882</v>
+        <v>49841</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>46212</v>
+        <v>46174</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>46212</v>
+        <v>46174</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53577</v>
+        <v>53533</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2799,7 +2799,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-08-04. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-08-10. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2852,19 +2852,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>51115</v>
+        <v>74083</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>51115</v>
+        <v>74083</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>275</v>
+        <v>398</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>56565</v>
       </c>
       <c r="C6" s="56" t="n">
-        <v>26595</v>
+        <v>31844</v>
       </c>
       <c r="D6" s="57" t="n">
-        <v>0.47</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="F6" s="55" t="n">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>29970</v>
+        <v>24721</v>
       </c>
       <c r="H6" s="58" t="inlineStr">
         <is>
@@ -2906,32 +2906,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B7" s="59" t="n">
+      <c r="B7" s="55" t="n">
         <v>52404</v>
       </c>
-      <c r="C7" s="46" t="n">
-        <v>11258</v>
-      </c>
-      <c r="D7" s="42" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E7" s="59" t="n">
-        <v>593</v>
-      </c>
-      <c r="F7" s="59" t="n">
-        <v>61</v>
-      </c>
-      <c r="G7" s="59" t="n">
-        <v>41146</v>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Early</t>
+      <c r="C7" s="56" t="n">
+        <v>14658</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>543</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>79</v>
+      </c>
+      <c r="G7" s="55" t="n">
+        <v>37746</v>
+      </c>
+      <c r="H7" s="58" t="inlineStr">
+        <is>
+          <t>Building</t>
         </is>
       </c>
     </row>
@@ -2975,19 +2975,19 @@
         <v>60755</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>8473</v>
+        <v>10926</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0.139</v>
+        <v>0.18</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>52282</v>
+        <v>49829</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>772304</v>
+        <v>795272</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-86109</v>
+        <v>-89013</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5430</v>
+        <v>-5563</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-244499</v>
+        <v>-246238</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>345696</v>
+        <v>361591</v>
       </c>
     </row>
     <row r="25">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>332196</v>
+        <v>348091</v>
       </c>
     </row>
     <row r="27">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>74913</v>
+        <v>77141</v>
       </c>
     </row>
     <row r="44">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -3037,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3431,104 +3431,112 @@
       </c>
       <c r="B45" s="74" t="inlineStr">
         <is>
-          <t>see Cleaning expense</t>
+          <t>excluded from revenue</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Offset by Cleaning expense above; net-neutral pass-through</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+          <t xml:space="preserve">  Collected and retained by property manager for housekeeping; not included in</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  gross revenue, ADR, or owner P&amp;L. Cleaning expense above reflects full cost billed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>MODEL INPUTS</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Closed Months Used for Calibration</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>7</v>
-      </c>
+      <c r="B49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Baseline ADR (de-seasonalized)</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>441</v>
+          <t>Closed Months Used for Calibration</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Baseline Occupancy (de-seasonalized)</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>0.836</v>
+          <t>Baseline ADR (de-seasonalized)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Max Occupancy Cap</t>
+          <t>Baseline Occupancy (de-seasonalized)</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>0.92</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
+          <t>Max Occupancy Cap</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>Back-test MAPE (Gross Revenue)</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n">
+      <c r="B54" s="10" t="n">
         <v>0.128</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>METHODOLOGY</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="75" t="inlineStr">
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="75" t="inlineStr">
         <is>
           <t>REVENUE: Pro forma projections blend closed-month actuals (from PMS booking data) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. EXPENSES: Operating expenses flow directly from QuickBooks Online monthly P&amp;L for closed months (audited source of truth); future months use a trailing 3-month average by category. Management fee is calculated separately as 10% of gross revenue. Property tax second installment projected for November. Insurance is shown as a normalization adjustment (annual premium was prepaid in Dec 2025 and is not in the 2026 cash-basis books). The model recalibrates automatically as each month closes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2131,10 +2131,26 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Rental income is as remitted by booking channels and includes guest-paid cleaning fees (not separable per</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>property manager); the corresponding cleaning costs appear in operating expenses and approximately offset.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A3:I3"/>
@@ -3037,7 +3053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3426,105 +3442,119 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Cleaning fees collected from guests</t>
+          <t>Cleaning fees paid by guests</t>
         </is>
       </c>
       <c r="B45" s="74" t="inlineStr">
         <is>
-          <t>excluded from revenue</t>
+          <t>included in gross revenue</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Collected and retained by property manager for housekeeping; not included in</t>
+          <t xml:space="preserve">  Booking channels remit lump-sum payments, so guest-paid cleaning fees are included in</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  gross revenue, ADR, or owner P&amp;L. Cleaning expense above reflects full cost billed.</t>
+          <t xml:space="preserve">  gross revenue and ADR (per property manager; not separable). The offsetting cleaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  cost is in Operating Expenses; the two sides offset within ~3% YTD (approx. net-neutral).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOT is calculated on gross revenue including cleaning fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>MODEL INPUTS</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Closed Months Used for Calibration</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Baseline ADR (de-seasonalized)</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>441</v>
-      </c>
+      <c r="B51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Baseline Occupancy (de-seasonalized)</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n">
-        <v>0.836</v>
+          <t>Closed Months Used for Calibration</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Max Occupancy Cap</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="n">
-        <v>0.92</v>
+          <t>Baseline ADR (de-seasonalized)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>Baseline Occupancy (de-seasonalized)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>0.836</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Max Occupancy Cap</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
           <t>Back-test MAPE (Gross Revenue)</t>
         </is>
       </c>
-      <c r="B54" s="10" t="n">
+      <c r="B56" s="10" t="n">
         <v>0.128</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>METHODOLOGY</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="75" t="inlineStr">
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="75" t="inlineStr">
         <is>
           <t>REVENUE: Pro forma projections blend closed-month actuals (from PMS booking data) with a seasonal model for future months. The seasonal model de-seasonalizes actual ADR and occupancy performance to establish a baseline, then applies monthly seasonal indices derived from Santa Barbara STR demand patterns to project forward revenue. EXPENSES: Operating expenses flow directly from QuickBooks Online monthly P&amp;L for closed months (audited source of truth); future months use a trailing 3-month average by category. Management fee is calculated separately as 10% of gross revenue. Property tax second installment projected for November. Insurance is shown as a normalization adjustment (annual premium was prepaid in Dec 2025 and is not in the 2026 cash-basis books). The model recalibrates automatically as each month closes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A33:C33"/>
@@ -3534,9 +3564,11 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -743,7 +743,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-08-10</t>
+          <t>Prepared 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>239</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>795272</v>
+        <v>799826</v>
       </c>
     </row>
     <row r="16">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>700696</v>
+        <v>704713</v>
       </c>
     </row>
     <row r="17">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>339105</v>
+        <v>339995</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>361591</v>
+        <v>364718</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>348091</v>
+        <v>351218</v>
       </c>
     </row>
     <row r="20">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.79</v>
+        <v>0.7929999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -999,7 +999,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>348091</v>
+        <v>351218</v>
       </c>
     </row>
     <row r="42">
@@ -2428,7 +2428,7 @@
         <v>52</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>54</v>
@@ -2475,7 +2475,7 @@
         <v>163</v>
       </c>
       <c r="I7" s="39" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J7" s="39" t="n">
         <v>135</v>
@@ -2569,7 +2569,7 @@
         <v>0.8759999999999999</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>0.6609999999999999</v>
+        <v>0.6990000000000001</v>
       </c>
       <c r="J9" s="41" t="n">
         <v>0.752</v>
@@ -2616,7 +2616,7 @@
         <v>653</v>
       </c>
       <c r="I10" s="43" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="J10" s="43" t="n">
         <v>419</v>
@@ -2663,7 +2663,7 @@
         <v>572</v>
       </c>
       <c r="I11" s="45" t="n">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="J11" s="45" t="n">
         <v>314</v>
@@ -2710,7 +2710,7 @@
         <v>106439</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>74083</v>
+        <v>78637</v>
       </c>
       <c r="J12" s="47" t="n">
         <v>56565</v>
@@ -2757,19 +2757,19 @@
         <v>92664</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>64881</v>
+        <v>68810</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49841</v>
+        <v>49863</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53533</v>
+        <v>53557</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2815,7 +2815,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-08-10. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-08-14. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>74083</v>
+        <v>78637</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>74083</v>
+        <v>78637</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2892,32 +2892,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="50" t="n">
         <v>56565</v>
       </c>
-      <c r="C6" s="56" t="n">
-        <v>31844</v>
-      </c>
-      <c r="D6" s="57" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="E6" s="55" t="n">
-        <v>559</v>
-      </c>
-      <c r="F6" s="55" t="n">
-        <v>177</v>
-      </c>
-      <c r="G6" s="55" t="n">
-        <v>24721</v>
-      </c>
-      <c r="H6" s="58" t="inlineStr">
-        <is>
-          <t>Building</t>
+      <c r="C6" s="51" t="n">
+        <v>35243</v>
+      </c>
+      <c r="D6" s="52" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="E6" s="50" t="n">
+        <v>578</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>196</v>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>21322</v>
+      </c>
+      <c r="H6" s="53" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -2931,19 +2931,19 @@
         <v>52404</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>14658</v>
+        <v>19961</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.28</v>
+        <v>0.381</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>37746</v>
+        <v>32443</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>795272</v>
+        <v>799826</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-89013</v>
+        <v>-89471</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5563</v>
+        <v>-5642</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-246238</v>
+        <v>-246672</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>361591</v>
+        <v>364718</v>
       </c>
     </row>
     <row r="25">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>348091</v>
+        <v>351218</v>
       </c>
     </row>
     <row r="27">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>77141</v>
+        <v>77583</v>
       </c>
     </row>
     <row r="44">

--- a/Casa_Yano_Lender_Package.xlsx
+++ b/Casa_Yano_Lender_Package.xlsx
@@ -743,7 +743,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared 2026-08-14</t>
+          <t>Prepared 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>249</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>799826</v>
+        <v>807884</v>
       </c>
     </row>
     <row r="16">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>704713</v>
+        <v>711778</v>
       </c>
     </row>
     <row r="17">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>339995</v>
+        <v>341235</v>
       </c>
     </row>
     <row r="18">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>364718</v>
+        <v>370543</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>351218</v>
+        <v>357043</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.7929999999999999</v>
+        <v>0.8009999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -999,7 +999,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>•  Owner margin of 88.2% - efficient operations with low OTA commission rates</t>
+          <t>•  Owner margin of 88.1% - efficient operations with low OTA commission rates</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>351218</v>
+        <v>357043</v>
       </c>
     </row>
     <row r="42">
@@ -2428,19 +2428,19 @@
         <v>52</v>
       </c>
       <c r="I6" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" s="37" t="n">
+        <v>53</v>
+      </c>
+      <c r="K6" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="J6" s="37" t="n">
-        <v>54</v>
-      </c>
-      <c r="K6" s="37" t="n">
-        <v>53</v>
-      </c>
       <c r="L6" s="37" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M6" s="37" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N6" s="38">
         <f>SUM(B6:M6)</f>
@@ -2475,7 +2475,7 @@
         <v>163</v>
       </c>
       <c r="I7" s="39" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="J7" s="39" t="n">
         <v>135</v>
@@ -2569,7 +2569,7 @@
         <v>0.8759999999999999</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>0.6990000000000001</v>
+        <v>0.785</v>
       </c>
       <c r="J9" s="41" t="n">
         <v>0.752</v>
@@ -2616,7 +2616,7 @@
         <v>653</v>
       </c>
       <c r="I10" s="43" t="n">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="J10" s="43" t="n">
         <v>419</v>
@@ -2663,7 +2663,7 @@
         <v>572</v>
       </c>
       <c r="I11" s="45" t="n">
-        <v>423</v>
+        <v>466</v>
       </c>
       <c r="J11" s="45" t="n">
         <v>314</v>
@@ -2710,7 +2710,7 @@
         <v>106439</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>78637</v>
+        <v>86695</v>
       </c>
       <c r="J12" s="47" t="n">
         <v>56565</v>
@@ -2757,19 +2757,19 @@
         <v>92664</v>
       </c>
       <c r="I13" s="48" t="n">
-        <v>68810</v>
+        <v>76100</v>
       </c>
       <c r="J13" s="48" t="n">
-        <v>49863</v>
+        <v>49806</v>
       </c>
       <c r="K13" s="48" t="n">
-        <v>46195</v>
+        <v>46142</v>
       </c>
       <c r="L13" s="48" t="n">
-        <v>46195</v>
+        <v>46142</v>
       </c>
       <c r="M13" s="48" t="n">
-        <v>53557</v>
+        <v>53495</v>
       </c>
       <c r="N13" s="46">
         <f>SUM(B13:M13)</f>
@@ -2815,7 +2815,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-08-14. Confirmed reservations with deposits received.</t>
+          <t>As of 2026-08-24. Confirmed reservations with deposits received.</t>
         </is>
       </c>
     </row>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="B5" s="50" t="n">
-        <v>78637</v>
+        <v>86695</v>
       </c>
       <c r="C5" s="51" t="n">
-        <v>78637</v>
+        <v>86695</v>
       </c>
       <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="50" t="n">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F5" s="50" t="n">
-        <v>423</v>
+        <v>466</v>
       </c>
       <c r="G5" s="50" t="n">
         <v>0</v>
@@ -2901,23 +2901,23 @@
         <v>56565</v>
       </c>
       <c r="C6" s="51" t="n">
-        <v>35243</v>
+        <v>55029</v>
       </c>
       <c r="D6" s="52" t="n">
-        <v>0.623</v>
+        <v>0.973</v>
       </c>
       <c r="E6" s="50" t="n">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="F6" s="50" t="n">
-        <v>196</v>
+        <v>306</v>
       </c>
       <c r="G6" s="50" t="n">
-        <v>21322</v>
+        <v>1536</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Fully Booked</t>
         </is>
       </c>
     </row>
@@ -2931,19 +2931,19 @@
         <v>52404</v>
       </c>
       <c r="C7" s="56" t="n">
-        <v>19961</v>
+        <v>26462</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0.381</v>
+        <v>0.505</v>
       </c>
       <c r="E7" s="55" t="n">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="F7" s="55" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="G7" s="55" t="n">
-        <v>32443</v>
+        <v>25942</v>
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
@@ -2961,19 +2961,19 @@
         <v>52404</v>
       </c>
       <c r="C8" s="46" t="n">
-        <v>5528</v>
+        <v>7131</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0.105</v>
+        <v>0.136</v>
       </c>
       <c r="E8" s="59" t="n">
-        <v>503</v>
+        <v>549</v>
       </c>
       <c r="F8" s="59" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G8" s="59" t="n">
-        <v>46876</v>
+        <v>45273</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
@@ -2991,19 +2991,19 @@
         <v>60755</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>10926</v>
+        <v>12482</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0.18</v>
+        <v>0.205</v>
       </c>
       <c r="E9" s="59" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="F9" s="59" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G9" s="59" t="n">
-        <v>49829</v>
+        <v>48273</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>799826</v>
+        <v>807884</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>-89471</v>
+        <v>-90453</v>
       </c>
       <c r="C6" s="10">
         <f>B6/B5</f>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-5642</v>
+        <v>-5653</v>
       </c>
       <c r="C7" s="10">
         <f>B7/B5</f>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-246672</v>
+        <v>-247107</v>
       </c>
       <c r="C11" s="66">
         <f>B11/B5</f>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="B24" s="59" t="n">
-        <v>364718</v>
+        <v>370543</v>
       </c>
     </row>
     <row r="25">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="B26" s="59" t="n">
-        <v>351218</v>
+        <v>357043</v>
       </c>
     </row>
     <row r="27">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>77583</v>
+        <v>78365</v>
       </c>
     </row>
     <row r="44">
